--- a/testing/appium-tests/Test_Report.xlsx
+++ b/testing/appium-tests/Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1146">
   <si>
     <t>GROWMARK MOBILE APP - AUTOMATED TESTING REPORT</t>
   </si>
@@ -1391,7 +1391,7 @@
     <t>TestCase_Sales_15: Submit random sales variation 15</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 110, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 84, Date: Today</t>
   </si>
   <si>
     <t>Sales record saved and threshold check triggered</t>
@@ -1406,7 +1406,7 @@
     <t>TestCase_Sales_16: Submit random sales variation 16</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 26, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 97, Date: Today</t>
   </si>
   <si>
     <t>TC111</t>
@@ -1415,7 +1415,7 @@
     <t>TestCase_Sales_17: Submit random sales variation 17</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 58, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 124, Date: Today</t>
   </si>
   <si>
     <t>TC112</t>
@@ -1424,7 +1424,7 @@
     <t>TestCase_Sales_18: Submit random sales variation 18</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 198, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 139, Date: Today</t>
   </si>
   <si>
     <t>TC113</t>
@@ -1433,7 +1433,7 @@
     <t>TestCase_Sales_19: Submit random sales variation 19</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 185, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 61, Date: Today</t>
   </si>
   <si>
     <t>TC114</t>
@@ -1442,7 +1442,7 @@
     <t>TestCase_Sales_20: Submit random sales variation 20</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 109, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 192, Date: Today</t>
   </si>
   <si>
     <t>TC115</t>
@@ -1451,7 +1451,7 @@
     <t>TestCase_Sales_21: Submit random sales variation 21</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 104, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 114, Date: Today</t>
   </si>
   <si>
     <t>TC116</t>
@@ -1460,7 +1460,7 @@
     <t>TestCase_Sales_22: Submit random sales variation 22</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 85, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 81, Date: Today</t>
   </si>
   <si>
     <t>TC117</t>
@@ -1469,7 +1469,7 @@
     <t>TestCase_Sales_23: Submit random sales variation 23</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 32, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 75, Date: Today</t>
   </si>
   <si>
     <t>TC118</t>
@@ -1478,7 +1478,7 @@
     <t>TestCase_Sales_24: Submit random sales variation 24</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 69, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 54, Date: Today</t>
   </si>
   <si>
     <t>TC119</t>
@@ -1487,7 +1487,7 @@
     <t>TestCase_Sales_25: Submit random sales variation 25</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 146, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 135, Date: Today</t>
   </si>
   <si>
     <t>TC120</t>
@@ -1496,7 +1496,7 @@
     <t>TestCase_Sales_26: Submit random sales variation 26</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 72, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 62, Date: Today</t>
   </si>
   <si>
     <t>TC121</t>
@@ -1505,7 +1505,7 @@
     <t>TestCase_Sales_27: Submit random sales variation 27</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 177, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 80, Date: Today</t>
   </si>
   <si>
     <t>TC122</t>
@@ -1514,7 +1514,7 @@
     <t>TestCase_Sales_28: Submit random sales variation 28</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 55, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 179, Date: Today</t>
   </si>
   <si>
     <t>TC123</t>
@@ -1523,7 +1523,7 @@
     <t>TestCase_Sales_29: Submit random sales variation 29</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 26, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 58, Date: Today</t>
   </si>
   <si>
     <t>TC124</t>
@@ -1532,7 +1532,7 @@
     <t>TestCase_Sales_30: Submit random sales variation 30</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 79, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 95, Date: Today</t>
   </si>
   <si>
     <t>TC125</t>
@@ -1541,7 +1541,7 @@
     <t>TestCase_Sales_31: Submit random sales variation 31</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 52, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 85, Date: Today</t>
   </si>
   <si>
     <t>TC126</t>
@@ -1550,7 +1550,7 @@
     <t>TestCase_Sales_32: Submit random sales variation 32</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 26, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 190, Date: Today</t>
   </si>
   <si>
     <t>TC127</t>
@@ -1559,7 +1559,7 @@
     <t>TestCase_Sales_33: Submit random sales variation 33</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 5, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 14, Date: Today</t>
   </si>
   <si>
     <t>TC128</t>
@@ -1568,7 +1568,7 @@
     <t>TestCase_Sales_34: Submit random sales variation 34</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 189, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 72, Date: Today</t>
   </si>
   <si>
     <t>TC129</t>
@@ -1577,7 +1577,7 @@
     <t>TestCase_Sales_35: Submit random sales variation 35</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 45, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 44, Date: Today</t>
   </si>
   <si>
     <t>TC130</t>
@@ -1586,7 +1586,7 @@
     <t>TestCase_Sales_36: Submit random sales variation 36</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 168, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 149, Date: Today</t>
   </si>
   <si>
     <t>TC131</t>
@@ -1595,7 +1595,7 @@
     <t>TestCase_Sales_37: Submit random sales variation 37</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 78, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 158, Date: Today</t>
   </si>
   <si>
     <t>TC132</t>
@@ -1604,7 +1604,7 @@
     <t>TestCase_Sales_38: Submit random sales variation 38</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 101, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 107, Date: Today</t>
   </si>
   <si>
     <t>TC133</t>
@@ -1613,7 +1613,7 @@
     <t>TestCase_Sales_39: Submit random sales variation 39</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 165, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 179, Date: Today</t>
   </si>
   <si>
     <t>TC134</t>
@@ -1622,7 +1622,7 @@
     <t>TestCase_Sales_40: Submit random sales variation 40</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 153, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 155, Date: Today</t>
   </si>
   <si>
     <t>TC135</t>
@@ -1631,7 +1631,7 @@
     <t>TestCase_Sales_41: Submit random sales variation 41</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 79, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 172, Date: Today</t>
   </si>
   <si>
     <t>TC136</t>
@@ -1640,7 +1640,7 @@
     <t>TestCase_Sales_42: Submit random sales variation 42</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 8, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 189, Date: Today</t>
   </si>
   <si>
     <t>TC137</t>
@@ -1649,7 +1649,7 @@
     <t>TestCase_Sales_43: Submit random sales variation 43</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 19, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 191, Date: Today</t>
   </si>
   <si>
     <t>TC138</t>
@@ -1658,7 +1658,7 @@
     <t>TestCase_Sales_44: Submit random sales variation 44</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 144, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 114, Date: Today</t>
   </si>
   <si>
     <t>TC139</t>
@@ -1667,7 +1667,7 @@
     <t>TestCase_Sales_45: Submit random sales variation 45</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 171, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 136, Date: Today</t>
   </si>
   <si>
     <t>TC140</t>
@@ -1676,7 +1676,7 @@
     <t>TestCase_Sales_46: Submit random sales variation 46</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 37, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 87, Date: Today</t>
   </si>
   <si>
     <t>TC141</t>
@@ -1685,7 +1685,7 @@
     <t>TestCase_Sales_47: Submit random sales variation 47</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 107, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 110, Date: Today</t>
   </si>
   <si>
     <t>TC142</t>
@@ -1694,7 +1694,7 @@
     <t>TestCase_Sales_48: Submit random sales variation 48</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 40, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 86, Date: Today</t>
   </si>
   <si>
     <t>TC143</t>
@@ -1703,7 +1703,7 @@
     <t>TestCase_Sales_49: Submit random sales variation 49</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 45, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 68, Date: Today</t>
   </si>
   <si>
     <t>TC144</t>
@@ -1712,7 +1712,7 @@
     <t>TestCase_Sales_50: Submit random sales variation 50</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 70, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 194, Date: Today</t>
   </si>
   <si>
     <t>TC145</t>
@@ -2876,10 +2876,10 @@
     <t>TC251</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_09: Score 35 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 35</t>
+    <t>TestCase_HealthScore_09: Score 29 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 29</t>
   </si>
   <si>
     <t>Verdict: "Immediate Action Needed" displayed</t>
@@ -2891,133 +2891,139 @@
     <t>TC252</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_10: Score 9 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 9</t>
+    <t>TestCase_HealthScore_10: Score 98 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 98</t>
+  </si>
+  <si>
+    <t>Verdict: "Thriving" displayed</t>
   </si>
   <si>
     <t>TC253</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_11: Score 13 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 13</t>
+    <t>TestCase_HealthScore_11: Score 33 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 33</t>
   </si>
   <si>
     <t>TC254</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_12: Score 0 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 0</t>
+    <t>TestCase_HealthScore_12: Score 25 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 25</t>
   </si>
   <si>
     <t>TC255</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_13: Score 85 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 85</t>
-  </si>
-  <si>
-    <t>Verdict: "Thriving" displayed</t>
+    <t>TestCase_HealthScore_13: Score 16 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 16</t>
   </si>
   <si>
     <t>TC256</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_14: Score 36 shows "Immediate Action Needed" verdict</t>
+    <t>TestCase_HealthScore_14: Score 43 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 43</t>
+  </si>
+  <si>
+    <t>TC257</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_15: Score 44 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 44</t>
+  </si>
+  <si>
+    <t>TC258</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_16: Score 77 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 77</t>
+  </si>
+  <si>
+    <t>Verdict: "Work in Progress" displayed</t>
+  </si>
+  <si>
+    <t>TC259</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_17: Score 59 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 59</t>
+  </si>
+  <si>
+    <t>TC260</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_18: Score 18 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 18</t>
+  </si>
+  <si>
+    <t>TC261</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_19: Score 36 shows "Immediate Action Needed" verdict</t>
   </si>
   <si>
     <t>Simulated score: 36</t>
   </si>
   <si>
-    <t>TC257</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_15: Score 0 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>TC258</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_16: Score 94 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 94</t>
-  </si>
-  <si>
-    <t>TC259</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_17: Score 68 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 68</t>
-  </si>
-  <si>
-    <t>Verdict: "Work in Progress" displayed</t>
-  </si>
-  <si>
-    <t>TC260</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_18: Score 60 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 60</t>
-  </si>
-  <si>
-    <t>TC261</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_19: Score 68 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
     <t>TC262</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_20: Score 94 shows "Thriving" verdict</t>
+    <t>TestCase_HealthScore_20: Score 45 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 45</t>
   </si>
   <si>
     <t>TC263</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_21: Score 57 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 57</t>
+    <t>TestCase_HealthScore_21: Score 59 shows "Work in Progress" verdict</t>
   </si>
   <si>
     <t>TC264</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_22: Score 4 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 4</t>
+    <t>TestCase_HealthScore_22: Score 38 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 38</t>
   </si>
   <si>
     <t>TC265</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_23: Score 69 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 69</t>
+    <t>TestCase_HealthScore_23: Score 11 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 11</t>
   </si>
   <si>
     <t>TC266</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_24: Score 46 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 46</t>
+    <t>TestCase_HealthScore_24: Score 53 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 53</t>
   </si>
   <si>
     <t>TC267</t>
@@ -4499,7 +4505,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="11">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>1</v>
@@ -4528,7 +4534,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="13">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>1</v>
@@ -4557,7 +4563,7 @@
         <v>9</v>
       </c>
       <c r="H4" s="11">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>1</v>
@@ -4586,7 +4592,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="13">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>1</v>
@@ -4615,7 +4621,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="11">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>1</v>
@@ -4644,7 +4650,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="13">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>1</v>
@@ -4673,7 +4679,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="11">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>1</v>
@@ -4702,7 +4708,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="13">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>1</v>
@@ -4731,7 +4737,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="11">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>1</v>
@@ -4760,7 +4766,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="13">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>1</v>
@@ -4789,7 +4795,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="11">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>1</v>
@@ -4818,7 +4824,7 @@
         <v>9</v>
       </c>
       <c r="H13" s="13">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>1</v>
@@ -4847,7 +4853,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="11">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>1</v>
@@ -4876,7 +4882,7 @@
         <v>9</v>
       </c>
       <c r="H15" s="13">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>1</v>
@@ -4905,7 +4911,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="11">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>1</v>
@@ -4934,7 +4940,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="13">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>1</v>
@@ -4963,7 +4969,7 @@
         <v>9</v>
       </c>
       <c r="H18" s="11">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>1</v>
@@ -4992,7 +4998,7 @@
         <v>9</v>
       </c>
       <c r="H19" s="13">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>1</v>
@@ -5021,7 +5027,7 @@
         <v>9</v>
       </c>
       <c r="H20" s="11">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>1</v>
@@ -5050,7 +5056,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="13">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>1</v>
@@ -5079,7 +5085,7 @@
         <v>9</v>
       </c>
       <c r="H22" s="11">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>1</v>
@@ -5108,7 +5114,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="13">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>1</v>
@@ -5137,7 +5143,7 @@
         <v>9</v>
       </c>
       <c r="H24" s="11">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>1</v>
@@ -5166,7 +5172,7 @@
         <v>9</v>
       </c>
       <c r="H25" s="13">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>1</v>
@@ -5195,7 +5201,7 @@
         <v>9</v>
       </c>
       <c r="H26" s="11">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>1</v>
@@ -5224,7 +5230,7 @@
         <v>9</v>
       </c>
       <c r="H27" s="13">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>1</v>
@@ -5253,7 +5259,7 @@
         <v>9</v>
       </c>
       <c r="H28" s="11">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>1</v>
@@ -5282,7 +5288,7 @@
         <v>9</v>
       </c>
       <c r="H29" s="13">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>1</v>
@@ -5311,7 +5317,7 @@
         <v>9</v>
       </c>
       <c r="H30" s="11">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>1</v>
@@ -5340,7 +5346,7 @@
         <v>9</v>
       </c>
       <c r="H31" s="13">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>1</v>
@@ -5369,7 +5375,7 @@
         <v>9</v>
       </c>
       <c r="H32" s="11">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>1</v>
@@ -5398,7 +5404,7 @@
         <v>9</v>
       </c>
       <c r="H33" s="13">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>1</v>
@@ -5427,7 +5433,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="11">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>1</v>
@@ -5456,7 +5462,7 @@
         <v>9</v>
       </c>
       <c r="H35" s="13">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="I35" s="13" t="s">
         <v>1</v>
@@ -5485,7 +5491,7 @@
         <v>9</v>
       </c>
       <c r="H36" s="11">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>1</v>
@@ -5514,7 +5520,7 @@
         <v>9</v>
       </c>
       <c r="H37" s="13">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>1</v>
@@ -5543,7 +5549,7 @@
         <v>9</v>
       </c>
       <c r="H38" s="11">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>1</v>
@@ -5572,7 +5578,7 @@
         <v>9</v>
       </c>
       <c r="H39" s="13">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>1</v>
@@ -5601,7 +5607,7 @@
         <v>9</v>
       </c>
       <c r="H40" s="11">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>1</v>
@@ -5630,7 +5636,7 @@
         <v>9</v>
       </c>
       <c r="H41" s="13">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>1</v>
@@ -5659,7 +5665,7 @@
         <v>9</v>
       </c>
       <c r="H42" s="11">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>1</v>
@@ -5688,7 +5694,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="13">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>1</v>
@@ -5717,7 +5723,7 @@
         <v>9</v>
       </c>
       <c r="H44" s="11">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>1</v>
@@ -5746,7 +5752,7 @@
         <v>9</v>
       </c>
       <c r="H45" s="13">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>1</v>
@@ -5775,7 +5781,7 @@
         <v>9</v>
       </c>
       <c r="H46" s="11">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>1</v>
@@ -5804,7 +5810,7 @@
         <v>9</v>
       </c>
       <c r="H47" s="13">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>1</v>
@@ -5833,7 +5839,7 @@
         <v>9</v>
       </c>
       <c r="H48" s="11">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>1</v>
@@ -5862,7 +5868,7 @@
         <v>9</v>
       </c>
       <c r="H49" s="13">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>1</v>
@@ -5891,7 +5897,7 @@
         <v>9</v>
       </c>
       <c r="H50" s="11">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>1</v>
@@ -5920,7 +5926,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="13">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>1</v>
@@ -5949,7 +5955,7 @@
         <v>9</v>
       </c>
       <c r="H52" s="11">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>1</v>
@@ -5978,7 +5984,7 @@
         <v>9</v>
       </c>
       <c r="H53" s="13">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>1</v>
@@ -6007,7 +6013,7 @@
         <v>9</v>
       </c>
       <c r="H54" s="11">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>1</v>
@@ -6036,7 +6042,7 @@
         <v>9</v>
       </c>
       <c r="H55" s="13">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>1</v>
@@ -6065,7 +6071,7 @@
         <v>9</v>
       </c>
       <c r="H56" s="11">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>1</v>
@@ -6094,7 +6100,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="13">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>1</v>
@@ -6123,7 +6129,7 @@
         <v>9</v>
       </c>
       <c r="H58" s="11">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>1</v>
@@ -6152,7 +6158,7 @@
         <v>9</v>
       </c>
       <c r="H59" s="13">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>1</v>
@@ -6181,7 +6187,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="11">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>1</v>
@@ -6210,7 +6216,7 @@
         <v>9</v>
       </c>
       <c r="H61" s="13">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>1</v>
@@ -6239,7 +6245,7 @@
         <v>9</v>
       </c>
       <c r="H62" s="11">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>1</v>
@@ -6268,7 +6274,7 @@
         <v>9</v>
       </c>
       <c r="H63" s="13">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>1</v>
@@ -6326,7 +6332,7 @@
         <v>9</v>
       </c>
       <c r="H65" s="13">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>1</v>
@@ -6355,7 +6361,7 @@
         <v>9</v>
       </c>
       <c r="H66" s="11">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>1</v>
@@ -6384,7 +6390,7 @@
         <v>9</v>
       </c>
       <c r="H67" s="13">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>1</v>
@@ -6413,7 +6419,7 @@
         <v>9</v>
       </c>
       <c r="H68" s="11">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>1</v>
@@ -6442,7 +6448,7 @@
         <v>9</v>
       </c>
       <c r="H69" s="13">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>1</v>
@@ -6471,7 +6477,7 @@
         <v>9</v>
       </c>
       <c r="H70" s="11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>1</v>
@@ -6500,7 +6506,7 @@
         <v>9</v>
       </c>
       <c r="H71" s="13">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>1</v>
@@ -6529,7 +6535,7 @@
         <v>9</v>
       </c>
       <c r="H72" s="11">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>1</v>
@@ -6558,7 +6564,7 @@
         <v>9</v>
       </c>
       <c r="H73" s="13">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>1</v>
@@ -6587,7 +6593,7 @@
         <v>9</v>
       </c>
       <c r="H74" s="11">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>1</v>
@@ -6616,7 +6622,7 @@
         <v>9</v>
       </c>
       <c r="H75" s="13">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>1</v>
@@ -6645,7 +6651,7 @@
         <v>9</v>
       </c>
       <c r="H76" s="11">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>1</v>
@@ -6674,7 +6680,7 @@
         <v>9</v>
       </c>
       <c r="H77" s="13">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>1</v>
@@ -6703,7 +6709,7 @@
         <v>9</v>
       </c>
       <c r="H78" s="11">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>1</v>
@@ -6732,7 +6738,7 @@
         <v>9</v>
       </c>
       <c r="H79" s="13">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>1</v>
@@ -6761,7 +6767,7 @@
         <v>9</v>
       </c>
       <c r="H80" s="11">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>1</v>
@@ -6790,7 +6796,7 @@
         <v>9</v>
       </c>
       <c r="H81" s="13">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="I81" s="13" t="s">
         <v>1</v>
@@ -6819,7 +6825,7 @@
         <v>9</v>
       </c>
       <c r="H82" s="11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>1</v>
@@ -6848,7 +6854,7 @@
         <v>9</v>
       </c>
       <c r="H83" s="13">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I83" s="13" t="s">
         <v>1</v>
@@ -6877,7 +6883,7 @@
         <v>9</v>
       </c>
       <c r="H84" s="11">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>1</v>
@@ -6906,7 +6912,7 @@
         <v>9</v>
       </c>
       <c r="H85" s="13">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>1</v>
@@ -6935,7 +6941,7 @@
         <v>9</v>
       </c>
       <c r="H86" s="11">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>1</v>
@@ -6964,7 +6970,7 @@
         <v>9</v>
       </c>
       <c r="H87" s="13">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>1</v>
@@ -6993,7 +6999,7 @@
         <v>9</v>
       </c>
       <c r="H88" s="11">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>1</v>
@@ -7022,7 +7028,7 @@
         <v>9</v>
       </c>
       <c r="H89" s="13">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="I89" s="13" t="s">
         <v>1</v>
@@ -7051,7 +7057,7 @@
         <v>9</v>
       </c>
       <c r="H90" s="11">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="I90" s="11" t="s">
         <v>1</v>
@@ -7080,7 +7086,7 @@
         <v>9</v>
       </c>
       <c r="H91" s="13">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="I91" s="13" t="s">
         <v>1</v>
@@ -7109,7 +7115,7 @@
         <v>9</v>
       </c>
       <c r="H92" s="11">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I92" s="11" t="s">
         <v>1</v>
@@ -7138,7 +7144,7 @@
         <v>9</v>
       </c>
       <c r="H93" s="13">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I93" s="13" t="s">
         <v>1</v>
@@ -7167,7 +7173,7 @@
         <v>9</v>
       </c>
       <c r="H94" s="11">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>1</v>
@@ -7196,7 +7202,7 @@
         <v>9</v>
       </c>
       <c r="H95" s="13">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="I95" s="13" t="s">
         <v>1</v>
@@ -7225,7 +7231,7 @@
         <v>9</v>
       </c>
       <c r="H96" s="11">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>1</v>
@@ -7254,7 +7260,7 @@
         <v>9</v>
       </c>
       <c r="H97" s="13">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="I97" s="13" t="s">
         <v>1</v>
@@ -7283,7 +7289,7 @@
         <v>9</v>
       </c>
       <c r="H98" s="11">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>1</v>
@@ -7312,7 +7318,7 @@
         <v>9</v>
       </c>
       <c r="H99" s="13">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I99" s="13" t="s">
         <v>1</v>
@@ -7341,7 +7347,7 @@
         <v>9</v>
       </c>
       <c r="H100" s="11">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>1</v>
@@ -7370,7 +7376,7 @@
         <v>9</v>
       </c>
       <c r="H101" s="13">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="I101" s="13" t="s">
         <v>1</v>
@@ -7399,7 +7405,7 @@
         <v>9</v>
       </c>
       <c r="H102" s="11">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>1</v>
@@ -7428,7 +7434,7 @@
         <v>9</v>
       </c>
       <c r="H103" s="13">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I103" s="13" t="s">
         <v>1</v>
@@ -7457,7 +7463,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="11">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>1</v>
@@ -7486,7 +7492,7 @@
         <v>9</v>
       </c>
       <c r="H105" s="13">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="I105" s="13" t="s">
         <v>1</v>
@@ -7515,7 +7521,7 @@
         <v>9</v>
       </c>
       <c r="H106" s="11">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>1</v>
@@ -7544,7 +7550,7 @@
         <v>9</v>
       </c>
       <c r="H107" s="13">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I107" s="13" t="s">
         <v>1</v>
@@ -7573,7 +7579,7 @@
         <v>9</v>
       </c>
       <c r="H108" s="11">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>1</v>
@@ -7602,7 +7608,7 @@
         <v>9</v>
       </c>
       <c r="H109" s="13">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I109" s="13" t="s">
         <v>1</v>
@@ -7631,7 +7637,7 @@
         <v>9</v>
       </c>
       <c r="H110" s="11">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>1</v>
@@ -7660,7 +7666,7 @@
         <v>9</v>
       </c>
       <c r="H111" s="13">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="I111" s="13" t="s">
         <v>1</v>
@@ -7689,7 +7695,7 @@
         <v>9</v>
       </c>
       <c r="H112" s="11">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="I112" s="11" t="s">
         <v>1</v>
@@ -7718,7 +7724,7 @@
         <v>9</v>
       </c>
       <c r="H113" s="13">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="I113" s="13" t="s">
         <v>1</v>
@@ -7747,7 +7753,7 @@
         <v>9</v>
       </c>
       <c r="H114" s="11">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I114" s="11" t="s">
         <v>1</v>
@@ -7776,7 +7782,7 @@
         <v>9</v>
       </c>
       <c r="H115" s="13">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="I115" s="13" t="s">
         <v>1</v>
@@ -7805,7 +7811,7 @@
         <v>9</v>
       </c>
       <c r="H116" s="11">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="I116" s="11" t="s">
         <v>1</v>
@@ -7834,7 +7840,7 @@
         <v>9</v>
       </c>
       <c r="H117" s="13">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="I117" s="13" t="s">
         <v>1</v>
@@ -7863,7 +7869,7 @@
         <v>9</v>
       </c>
       <c r="H118" s="11">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>1</v>
@@ -7892,7 +7898,7 @@
         <v>9</v>
       </c>
       <c r="H119" s="13">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="I119" s="13" t="s">
         <v>1</v>
@@ -7921,7 +7927,7 @@
         <v>9</v>
       </c>
       <c r="H120" s="11">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>1</v>
@@ -7950,7 +7956,7 @@
         <v>9</v>
       </c>
       <c r="H121" s="13">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>1</v>
@@ -7979,7 +7985,7 @@
         <v>9</v>
       </c>
       <c r="H122" s="11">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I122" s="11" t="s">
         <v>1</v>
@@ -8008,7 +8014,7 @@
         <v>9</v>
       </c>
       <c r="H123" s="13">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>1</v>
@@ -8037,7 +8043,7 @@
         <v>9</v>
       </c>
       <c r="H124" s="11">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="I124" s="11" t="s">
         <v>1</v>
@@ -8066,7 +8072,7 @@
         <v>9</v>
       </c>
       <c r="H125" s="13">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>1</v>
@@ -8095,7 +8101,7 @@
         <v>9</v>
       </c>
       <c r="H126" s="11">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="I126" s="11" t="s">
         <v>1</v>
@@ -8124,7 +8130,7 @@
         <v>9</v>
       </c>
       <c r="H127" s="13">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>1</v>
@@ -8153,7 +8159,7 @@
         <v>9</v>
       </c>
       <c r="H128" s="11">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>1</v>
@@ -8182,7 +8188,7 @@
         <v>9</v>
       </c>
       <c r="H129" s="13">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>1</v>
@@ -8211,7 +8217,7 @@
         <v>9</v>
       </c>
       <c r="H130" s="11">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="I130" s="11" t="s">
         <v>1</v>
@@ -8240,7 +8246,7 @@
         <v>9</v>
       </c>
       <c r="H131" s="13">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>1</v>
@@ -8269,7 +8275,7 @@
         <v>9</v>
       </c>
       <c r="H132" s="11">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="I132" s="11" t="s">
         <v>1</v>
@@ -8298,7 +8304,7 @@
         <v>9</v>
       </c>
       <c r="H133" s="13">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>1</v>
@@ -8327,7 +8333,7 @@
         <v>9</v>
       </c>
       <c r="H134" s="11">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="I134" s="11" t="s">
         <v>1</v>
@@ -8356,7 +8362,7 @@
         <v>9</v>
       </c>
       <c r="H135" s="13">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>1</v>
@@ -8385,7 +8391,7 @@
         <v>9</v>
       </c>
       <c r="H136" s="11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I136" s="11" t="s">
         <v>1</v>
@@ -8414,7 +8420,7 @@
         <v>9</v>
       </c>
       <c r="H137" s="13">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I137" s="13" t="s">
         <v>1</v>
@@ -8443,7 +8449,7 @@
         <v>9</v>
       </c>
       <c r="H138" s="11">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I138" s="11" t="s">
         <v>1</v>
@@ -8472,7 +8478,7 @@
         <v>9</v>
       </c>
       <c r="H139" s="13">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I139" s="13" t="s">
         <v>1</v>
@@ -8501,7 +8507,7 @@
         <v>9</v>
       </c>
       <c r="H140" s="11">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="I140" s="11" t="s">
         <v>1</v>
@@ -8530,7 +8536,7 @@
         <v>9</v>
       </c>
       <c r="H141" s="13">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="I141" s="13" t="s">
         <v>1</v>
@@ -8559,7 +8565,7 @@
         <v>9</v>
       </c>
       <c r="H142" s="11">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="I142" s="11" t="s">
         <v>1</v>
@@ -8588,7 +8594,7 @@
         <v>9</v>
       </c>
       <c r="H143" s="13">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>1</v>
@@ -8617,7 +8623,7 @@
         <v>9</v>
       </c>
       <c r="H144" s="11">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I144" s="11" t="s">
         <v>1</v>
@@ -8646,7 +8652,7 @@
         <v>9</v>
       </c>
       <c r="H145" s="13">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="I145" s="13" t="s">
         <v>1</v>
@@ -8704,7 +8710,7 @@
         <v>9</v>
       </c>
       <c r="H147" s="13">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="I147" s="13" t="s">
         <v>1</v>
@@ -8733,7 +8739,7 @@
         <v>9</v>
       </c>
       <c r="H148" s="11">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="I148" s="11" t="s">
         <v>1</v>
@@ -8762,7 +8768,7 @@
         <v>9</v>
       </c>
       <c r="H149" s="13">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="I149" s="13" t="s">
         <v>1</v>
@@ -8791,7 +8797,7 @@
         <v>9</v>
       </c>
       <c r="H150" s="11">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="I150" s="11" t="s">
         <v>1</v>
@@ -8820,7 +8826,7 @@
         <v>9</v>
       </c>
       <c r="H151" s="13">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="I151" s="13" t="s">
         <v>1</v>
@@ -8849,7 +8855,7 @@
         <v>9</v>
       </c>
       <c r="H152" s="11">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="I152" s="11" t="s">
         <v>1</v>
@@ -8878,7 +8884,7 @@
         <v>9</v>
       </c>
       <c r="H153" s="13">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="I153" s="13" t="s">
         <v>1</v>
@@ -8907,7 +8913,7 @@
         <v>9</v>
       </c>
       <c r="H154" s="11">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="I154" s="11" t="s">
         <v>1</v>
@@ -8936,7 +8942,7 @@
         <v>9</v>
       </c>
       <c r="H155" s="13">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="I155" s="13" t="s">
         <v>1</v>
@@ -8965,7 +8971,7 @@
         <v>9</v>
       </c>
       <c r="H156" s="11">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="I156" s="11" t="s">
         <v>1</v>
@@ -8994,7 +9000,7 @@
         <v>9</v>
       </c>
       <c r="H157" s="13">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>1</v>
@@ -9023,7 +9029,7 @@
         <v>9</v>
       </c>
       <c r="H158" s="11">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="I158" s="11" t="s">
         <v>1</v>
@@ -9052,7 +9058,7 @@
         <v>9</v>
       </c>
       <c r="H159" s="13">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I159" s="13" t="s">
         <v>1</v>
@@ -9081,7 +9087,7 @@
         <v>9</v>
       </c>
       <c r="H160" s="11">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I160" s="11" t="s">
         <v>1</v>
@@ -9110,7 +9116,7 @@
         <v>9</v>
       </c>
       <c r="H161" s="13">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I161" s="13" t="s">
         <v>1</v>
@@ -9139,7 +9145,7 @@
         <v>9</v>
       </c>
       <c r="H162" s="11">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="I162" s="11" t="s">
         <v>1</v>
@@ -9168,7 +9174,7 @@
         <v>9</v>
       </c>
       <c r="H163" s="13">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>1</v>
@@ -9197,7 +9203,7 @@
         <v>9</v>
       </c>
       <c r="H164" s="11">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="I164" s="11" t="s">
         <v>1</v>
@@ -9226,7 +9232,7 @@
         <v>9</v>
       </c>
       <c r="H165" s="13">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="I165" s="13" t="s">
         <v>1</v>
@@ -9255,7 +9261,7 @@
         <v>9</v>
       </c>
       <c r="H166" s="11">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="I166" s="11" t="s">
         <v>1</v>
@@ -9284,7 +9290,7 @@
         <v>9</v>
       </c>
       <c r="H167" s="13">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="I167" s="13" t="s">
         <v>1</v>
@@ -9313,7 +9319,7 @@
         <v>9</v>
       </c>
       <c r="H168" s="11">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I168" s="11" t="s">
         <v>1</v>
@@ -9342,7 +9348,7 @@
         <v>9</v>
       </c>
       <c r="H169" s="13">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="I169" s="13" t="s">
         <v>1</v>
@@ -9371,7 +9377,7 @@
         <v>9</v>
       </c>
       <c r="H170" s="11">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="I170" s="11" t="s">
         <v>1</v>
@@ -9400,7 +9406,7 @@
         <v>9</v>
       </c>
       <c r="H171" s="13">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="I171" s="13" t="s">
         <v>1</v>
@@ -9429,7 +9435,7 @@
         <v>9</v>
       </c>
       <c r="H172" s="11">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I172" s="11" t="s">
         <v>1</v>
@@ -9458,7 +9464,7 @@
         <v>9</v>
       </c>
       <c r="H173" s="13">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I173" s="13" t="s">
         <v>1</v>
@@ -9487,7 +9493,7 @@
         <v>9</v>
       </c>
       <c r="H174" s="11">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I174" s="11" t="s">
         <v>1</v>
@@ -9516,7 +9522,7 @@
         <v>9</v>
       </c>
       <c r="H175" s="13">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I175" s="13" t="s">
         <v>1</v>
@@ -9545,7 +9551,7 @@
         <v>9</v>
       </c>
       <c r="H176" s="11">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="I176" s="11" t="s">
         <v>1</v>
@@ -9574,7 +9580,7 @@
         <v>9</v>
       </c>
       <c r="H177" s="13">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="I177" s="13" t="s">
         <v>1</v>
@@ -9603,7 +9609,7 @@
         <v>9</v>
       </c>
       <c r="H178" s="11">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="I178" s="11" t="s">
         <v>1</v>
@@ -9632,7 +9638,7 @@
         <v>9</v>
       </c>
       <c r="H179" s="13">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="I179" s="13" t="s">
         <v>1</v>
@@ -9661,7 +9667,7 @@
         <v>9</v>
       </c>
       <c r="H180" s="11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I180" s="11" t="s">
         <v>1</v>
@@ -9690,7 +9696,7 @@
         <v>9</v>
       </c>
       <c r="H181" s="13">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I181" s="13" t="s">
         <v>1</v>
@@ -9719,7 +9725,7 @@
         <v>9</v>
       </c>
       <c r="H182" s="11">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="I182" s="11" t="s">
         <v>1</v>
@@ -9748,7 +9754,7 @@
         <v>9</v>
       </c>
       <c r="H183" s="13">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="I183" s="13" t="s">
         <v>1</v>
@@ -9777,7 +9783,7 @@
         <v>9</v>
       </c>
       <c r="H184" s="11">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="I184" s="11" t="s">
         <v>1</v>
@@ -9806,7 +9812,7 @@
         <v>9</v>
       </c>
       <c r="H185" s="13">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="I185" s="13" t="s">
         <v>1</v>
@@ -9835,7 +9841,7 @@
         <v>9</v>
       </c>
       <c r="H186" s="11">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="I186" s="11" t="s">
         <v>1</v>
@@ -9864,7 +9870,7 @@
         <v>9</v>
       </c>
       <c r="H187" s="13">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="I187" s="13" t="s">
         <v>1</v>
@@ -9893,7 +9899,7 @@
         <v>9</v>
       </c>
       <c r="H188" s="11">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="I188" s="11" t="s">
         <v>1</v>
@@ -9922,7 +9928,7 @@
         <v>9</v>
       </c>
       <c r="H189" s="13">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="I189" s="13" t="s">
         <v>1</v>
@@ -9951,7 +9957,7 @@
         <v>9</v>
       </c>
       <c r="H190" s="11">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="I190" s="11" t="s">
         <v>1</v>
@@ -9980,7 +9986,7 @@
         <v>9</v>
       </c>
       <c r="H191" s="13">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I191" s="13" t="s">
         <v>1</v>
@@ -10009,7 +10015,7 @@
         <v>9</v>
       </c>
       <c r="H192" s="11">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="I192" s="11" t="s">
         <v>1</v>
@@ -10038,7 +10044,7 @@
         <v>9</v>
       </c>
       <c r="H193" s="13">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="I193" s="13" t="s">
         <v>1</v>
@@ -10067,7 +10073,7 @@
         <v>9</v>
       </c>
       <c r="H194" s="11">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="I194" s="11" t="s">
         <v>1</v>
@@ -10096,7 +10102,7 @@
         <v>9</v>
       </c>
       <c r="H195" s="13">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>1</v>
@@ -10125,7 +10131,7 @@
         <v>9</v>
       </c>
       <c r="H196" s="11">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="I196" s="11" t="s">
         <v>1</v>
@@ -10154,7 +10160,7 @@
         <v>9</v>
       </c>
       <c r="H197" s="13">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>1</v>
@@ -10183,7 +10189,7 @@
         <v>9</v>
       </c>
       <c r="H198" s="11">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="I198" s="11" t="s">
         <v>1</v>
@@ -10212,7 +10218,7 @@
         <v>9</v>
       </c>
       <c r="H199" s="13">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="I199" s="13" t="s">
         <v>1</v>
@@ -10241,7 +10247,7 @@
         <v>9</v>
       </c>
       <c r="H200" s="11">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I200" s="11" t="s">
         <v>1</v>
@@ -10270,7 +10276,7 @@
         <v>9</v>
       </c>
       <c r="H201" s="13">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="I201" s="13" t="s">
         <v>1</v>
@@ -10299,7 +10305,7 @@
         <v>9</v>
       </c>
       <c r="H202" s="11">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="I202" s="11" t="s">
         <v>1</v>
@@ -10328,7 +10334,7 @@
         <v>9</v>
       </c>
       <c r="H203" s="13">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I203" s="13" t="s">
         <v>1</v>
@@ -10357,7 +10363,7 @@
         <v>9</v>
       </c>
       <c r="H204" s="11">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="I204" s="11" t="s">
         <v>1</v>
@@ -10386,7 +10392,7 @@
         <v>9</v>
       </c>
       <c r="H205" s="13">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="I205" s="13" t="s">
         <v>1</v>
@@ -10415,7 +10421,7 @@
         <v>9</v>
       </c>
       <c r="H206" s="11">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="I206" s="11" t="s">
         <v>1</v>
@@ -10444,7 +10450,7 @@
         <v>9</v>
       </c>
       <c r="H207" s="13">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="I207" s="13" t="s">
         <v>1</v>
@@ -10473,7 +10479,7 @@
         <v>9</v>
       </c>
       <c r="H208" s="11">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I208" s="11" t="s">
         <v>1</v>
@@ -10502,7 +10508,7 @@
         <v>9</v>
       </c>
       <c r="H209" s="13">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="I209" s="13" t="s">
         <v>1</v>
@@ -10531,7 +10537,7 @@
         <v>9</v>
       </c>
       <c r="H210" s="11">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="I210" s="11" t="s">
         <v>1</v>
@@ -10560,7 +10566,7 @@
         <v>9</v>
       </c>
       <c r="H211" s="13">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="I211" s="13" t="s">
         <v>1</v>
@@ -10589,7 +10595,7 @@
         <v>9</v>
       </c>
       <c r="H212" s="11">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I212" s="11" t="s">
         <v>1</v>
@@ -10618,7 +10624,7 @@
         <v>9</v>
       </c>
       <c r="H213" s="13">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="I213" s="13" t="s">
         <v>1</v>
@@ -10647,7 +10653,7 @@
         <v>9</v>
       </c>
       <c r="H214" s="11">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I214" s="11" t="s">
         <v>1</v>
@@ -10676,7 +10682,7 @@
         <v>9</v>
       </c>
       <c r="H215" s="13">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="I215" s="13" t="s">
         <v>1</v>
@@ -10705,7 +10711,7 @@
         <v>9</v>
       </c>
       <c r="H216" s="11">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="I216" s="11" t="s">
         <v>1</v>
@@ -10734,7 +10740,7 @@
         <v>9</v>
       </c>
       <c r="H217" s="13">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I217" s="13" t="s">
         <v>1</v>
@@ -10763,7 +10769,7 @@
         <v>9</v>
       </c>
       <c r="H218" s="11">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="I218" s="11" t="s">
         <v>1</v>
@@ -10792,7 +10798,7 @@
         <v>9</v>
       </c>
       <c r="H219" s="13">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="I219" s="13" t="s">
         <v>1</v>
@@ -10821,7 +10827,7 @@
         <v>9</v>
       </c>
       <c r="H220" s="11">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I220" s="11" t="s">
         <v>1</v>
@@ -10850,7 +10856,7 @@
         <v>9</v>
       </c>
       <c r="H221" s="13">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="I221" s="13" t="s">
         <v>1</v>
@@ -10879,7 +10885,7 @@
         <v>9</v>
       </c>
       <c r="H222" s="11">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="I222" s="11" t="s">
         <v>1</v>
@@ -10908,7 +10914,7 @@
         <v>9</v>
       </c>
       <c r="H223" s="13">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="I223" s="13" t="s">
         <v>1</v>
@@ -10937,7 +10943,7 @@
         <v>9</v>
       </c>
       <c r="H224" s="11">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="I224" s="11" t="s">
         <v>1</v>
@@ -10966,7 +10972,7 @@
         <v>9</v>
       </c>
       <c r="H225" s="13">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="I225" s="13" t="s">
         <v>1</v>
@@ -10995,7 +11001,7 @@
         <v>9</v>
       </c>
       <c r="H226" s="11">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="I226" s="11" t="s">
         <v>1</v>
@@ -11024,7 +11030,7 @@
         <v>9</v>
       </c>
       <c r="H227" s="13">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I227" s="13" t="s">
         <v>1</v>
@@ -11053,7 +11059,7 @@
         <v>9</v>
       </c>
       <c r="H228" s="11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I228" s="11" t="s">
         <v>1</v>
@@ -11082,7 +11088,7 @@
         <v>9</v>
       </c>
       <c r="H229" s="13">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="I229" s="13" t="s">
         <v>1</v>
@@ -11111,7 +11117,7 @@
         <v>9</v>
       </c>
       <c r="H230" s="11">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="I230" s="11" t="s">
         <v>1</v>
@@ -11140,7 +11146,7 @@
         <v>9</v>
       </c>
       <c r="H231" s="13">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="I231" s="13" t="s">
         <v>1</v>
@@ -11169,7 +11175,7 @@
         <v>9</v>
       </c>
       <c r="H232" s="11">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="I232" s="11" t="s">
         <v>1</v>
@@ -11198,7 +11204,7 @@
         <v>9</v>
       </c>
       <c r="H233" s="13">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I233" s="13" t="s">
         <v>1</v>
@@ -11227,7 +11233,7 @@
         <v>9</v>
       </c>
       <c r="H234" s="11">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I234" s="11" t="s">
         <v>1</v>
@@ -11256,7 +11262,7 @@
         <v>9</v>
       </c>
       <c r="H235" s="13">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="I235" s="13" t="s">
         <v>1</v>
@@ -11285,7 +11291,7 @@
         <v>9</v>
       </c>
       <c r="H236" s="11">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I236" s="11" t="s">
         <v>1</v>
@@ -11314,7 +11320,7 @@
         <v>9</v>
       </c>
       <c r="H237" s="13">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I237" s="13" t="s">
         <v>1</v>
@@ -11343,7 +11349,7 @@
         <v>9</v>
       </c>
       <c r="H238" s="11">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>1</v>
@@ -11372,7 +11378,7 @@
         <v>9</v>
       </c>
       <c r="H239" s="13">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I239" s="13" t="s">
         <v>1</v>
@@ -11401,7 +11407,7 @@
         <v>9</v>
       </c>
       <c r="H240" s="11">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>1</v>
@@ -11430,7 +11436,7 @@
         <v>9</v>
       </c>
       <c r="H241" s="13">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="I241" s="13" t="s">
         <v>1</v>
@@ -11459,7 +11465,7 @@
         <v>9</v>
       </c>
       <c r="H242" s="11">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I242" s="11" t="s">
         <v>1</v>
@@ -11488,7 +11494,7 @@
         <v>9</v>
       </c>
       <c r="H243" s="13">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="I243" s="13" t="s">
         <v>1</v>
@@ -11517,7 +11523,7 @@
         <v>9</v>
       </c>
       <c r="H244" s="11">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="I244" s="11" t="s">
         <v>1</v>
@@ -11546,7 +11552,7 @@
         <v>9</v>
       </c>
       <c r="H245" s="13">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I245" s="13" t="s">
         <v>1</v>
@@ -11575,7 +11581,7 @@
         <v>9</v>
       </c>
       <c r="H246" s="11">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I246" s="11" t="s">
         <v>1</v>
@@ -11604,7 +11610,7 @@
         <v>9</v>
       </c>
       <c r="H247" s="13">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I247" s="13" t="s">
         <v>1</v>
@@ -11633,7 +11639,7 @@
         <v>9</v>
       </c>
       <c r="H248" s="11">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I248" s="11" t="s">
         <v>1</v>
@@ -11662,7 +11668,7 @@
         <v>9</v>
       </c>
       <c r="H249" s="13">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="I249" s="13" t="s">
         <v>1</v>
@@ -11691,7 +11697,7 @@
         <v>9</v>
       </c>
       <c r="H250" s="11">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I250" s="11" t="s">
         <v>1</v>
@@ -11720,7 +11726,7 @@
         <v>9</v>
       </c>
       <c r="H251" s="13">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I251" s="13" t="s">
         <v>1</v>
@@ -11749,7 +11755,7 @@
         <v>9</v>
       </c>
       <c r="H252" s="11">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="I252" s="11" t="s">
         <v>1</v>
@@ -11769,7 +11775,7 @@
         <v>960</v>
       </c>
       <c r="E253" s="13" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F253" s="13" t="s">
         <v>957</v>
@@ -11778,7 +11784,7 @@
         <v>9</v>
       </c>
       <c r="H253" s="13">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I253" s="13" t="s">
         <v>1</v>
@@ -11786,16 +11792,16 @@
     </row>
     <row r="254" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B254" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C254" s="11" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D254" s="11" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="E254" s="11" t="s">
         <v>956</v>
@@ -11807,7 +11813,7 @@
         <v>9</v>
       </c>
       <c r="H254" s="11">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="I254" s="11" t="s">
         <v>1</v>
@@ -11815,16 +11821,16 @@
     </row>
     <row r="255" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="13" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B255" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C255" s="13" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D255" s="13" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E255" s="13" t="s">
         <v>956</v>
@@ -11836,7 +11842,7 @@
         <v>9</v>
       </c>
       <c r="H255" s="13">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I255" s="13" t="s">
         <v>1</v>
@@ -11844,19 +11850,19 @@
     </row>
     <row r="256" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B256" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C256" s="11" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D256" s="11" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E256" s="11" t="s">
-        <v>970</v>
+        <v>956</v>
       </c>
       <c r="F256" s="11" t="s">
         <v>957</v>
@@ -11865,7 +11871,7 @@
         <v>9</v>
       </c>
       <c r="H256" s="11">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I256" s="11" t="s">
         <v>1</v>
@@ -11894,7 +11900,7 @@
         <v>9</v>
       </c>
       <c r="H257" s="13">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I257" s="13" t="s">
         <v>1</v>
@@ -11911,7 +11917,7 @@
         <v>975</v>
       </c>
       <c r="D258" s="11" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="E258" s="11" t="s">
         <v>956</v>
@@ -11923,7 +11929,7 @@
         <v>9</v>
       </c>
       <c r="H258" s="11">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="I258" s="11" t="s">
         <v>1</v>
@@ -11931,19 +11937,19 @@
     </row>
     <row r="259" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="13" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B259" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C259" s="13" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D259" s="13" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="E259" s="13" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="F259" s="13" t="s">
         <v>957</v>
@@ -11952,7 +11958,7 @@
         <v>9</v>
       </c>
       <c r="H259" s="13">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I259" s="13" t="s">
         <v>1</v>
@@ -11960,19 +11966,19 @@
     </row>
     <row r="260" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B260" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C260" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="D260" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="E260" s="11" t="s">
         <v>980</v>
-      </c>
-      <c r="D260" s="11" t="s">
-        <v>981</v>
-      </c>
-      <c r="E260" s="11" t="s">
-        <v>982</v>
       </c>
       <c r="F260" s="11" t="s">
         <v>957</v>
@@ -11981,7 +11987,7 @@
         <v>9</v>
       </c>
       <c r="H260" s="11">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="I260" s="11" t="s">
         <v>1</v>
@@ -11989,19 +11995,19 @@
     </row>
     <row r="261" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="13" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B261" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C261" s="13" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D261" s="13" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E261" s="13" t="s">
-        <v>982</v>
+        <v>956</v>
       </c>
       <c r="F261" s="13" t="s">
         <v>957</v>
@@ -12010,7 +12016,7 @@
         <v>9</v>
       </c>
       <c r="H261" s="13">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="I261" s="13" t="s">
         <v>1</v>
@@ -12018,19 +12024,19 @@
     </row>
     <row r="262" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="11" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C262" s="11" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D262" s="11" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>982</v>
+        <v>956</v>
       </c>
       <c r="F262" s="11" t="s">
         <v>957</v>
@@ -12039,7 +12045,7 @@
         <v>9</v>
       </c>
       <c r="H262" s="11">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="I262" s="11" t="s">
         <v>1</v>
@@ -12047,19 +12053,19 @@
     </row>
     <row r="263" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="13" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B263" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C263" s="13" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D263" s="13" t="s">
-        <v>978</v>
+        <v>992</v>
       </c>
       <c r="E263" s="13" t="s">
-        <v>970</v>
+        <v>956</v>
       </c>
       <c r="F263" s="13" t="s">
         <v>957</v>
@@ -12068,7 +12074,7 @@
         <v>9</v>
       </c>
       <c r="H263" s="13">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="I263" s="13" t="s">
         <v>1</v>
@@ -12076,19 +12082,19 @@
     </row>
     <row r="264" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="B264" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C264" s="11" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D264" s="11" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="E264" s="11" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="F264" s="11" t="s">
         <v>957</v>
@@ -12097,7 +12103,7 @@
         <v>9</v>
       </c>
       <c r="H264" s="11">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="I264" s="11" t="s">
         <v>1</v>
@@ -12105,16 +12111,16 @@
     </row>
     <row r="265" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="13" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B265" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C265" s="13" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D265" s="13" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="E265" s="13" t="s">
         <v>956</v>
@@ -12126,7 +12132,7 @@
         <v>9</v>
       </c>
       <c r="H265" s="13">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="I265" s="13" t="s">
         <v>1</v>
@@ -12134,19 +12140,19 @@
     </row>
     <row r="266" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C266" s="11" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D266" s="11" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="E266" s="11" t="s">
-        <v>982</v>
+        <v>956</v>
       </c>
       <c r="F266" s="11" t="s">
         <v>957</v>
@@ -12155,7 +12161,7 @@
         <v>9</v>
       </c>
       <c r="H266" s="11">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="I266" s="11" t="s">
         <v>1</v>
@@ -12163,19 +12169,19 @@
     </row>
     <row r="267" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="13" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B267" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C267" s="13" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D267" s="13" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="E267" s="13" t="s">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="F267" s="13" t="s">
         <v>957</v>
@@ -12184,7 +12190,7 @@
         <v>9</v>
       </c>
       <c r="H267" s="13">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I267" s="13" t="s">
         <v>1</v>
@@ -12192,28 +12198,28 @@
     </row>
     <row r="268" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="11" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C268" s="11" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="E268" s="11" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="G268" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H268" s="11">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="I268" s="11" t="s">
         <v>1</v>
@@ -12221,28 +12227,28 @@
     </row>
     <row r="269" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="13" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B269" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C269" s="13" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D269" s="13" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="E269" s="13" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="F269" s="13" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="G269" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H269" s="13">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="I269" s="13" t="s">
         <v>1</v>
@@ -12250,28 +12256,28 @@
     </row>
     <row r="270" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B270" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C270" s="11" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D270" s="11" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E270" s="11" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="G270" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H270" s="11">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="I270" s="11" t="s">
         <v>1</v>
@@ -12279,28 +12285,28 @@
     </row>
     <row r="271" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="13" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B271" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C271" s="13" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D271" s="13" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="E271" s="13" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="F271" s="13" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="G271" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H271" s="13">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I271" s="13" t="s">
         <v>1</v>
@@ -12308,28 +12314,28 @@
     </row>
     <row r="272" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C272" s="11" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="E272" s="11" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="G272" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H272" s="11">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="I272" s="11" t="s">
         <v>1</v>
@@ -12337,28 +12343,28 @@
     </row>
     <row r="273" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="13" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B273" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C273" s="13" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="D273" s="13" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="E273" s="13" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="F273" s="13" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="G273" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H273" s="13">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I273" s="13" t="s">
         <v>1</v>
@@ -12366,28 +12372,28 @@
     </row>
     <row r="274" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C274" s="11" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="E274" s="11" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="G274" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H274" s="11">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I274" s="11" t="s">
         <v>1</v>
@@ -12395,28 +12401,28 @@
     </row>
     <row r="275" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="13" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B275" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C275" s="13" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D275" s="13" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="E275" s="13" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="F275" s="13" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="G275" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H275" s="13">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="I275" s="13" t="s">
         <v>1</v>
@@ -12424,19 +12430,19 @@
     </row>
     <row r="276" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="11" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C276" s="11" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="D276" s="11" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="E276" s="11" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="F276" s="11" t="s">
         <v>48</v>
@@ -12453,28 +12459,28 @@
     </row>
     <row r="277" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="13" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B277" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C277" s="13" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="D277" s="13" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="E277" s="13" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="F277" s="13" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="G277" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H277" s="13">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="I277" s="13" t="s">
         <v>1</v>
@@ -12482,28 +12488,28 @@
     </row>
     <row r="278" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="D278" s="11" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="E278" s="11" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="G278" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H278" s="11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I278" s="11" t="s">
         <v>1</v>
@@ -12511,19 +12517,19 @@
     </row>
     <row r="279" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="13" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B279" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C279" s="13" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D279" s="13" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="E279" s="13" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="F279" s="13" t="s">
         <v>863</v>
@@ -12532,7 +12538,7 @@
         <v>9</v>
       </c>
       <c r="H279" s="13">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="I279" s="13" t="s">
         <v>1</v>
@@ -12540,28 +12546,28 @@
     </row>
     <row r="280" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C280" s="11" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D280" s="11" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="E280" s="11" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="G280" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H280" s="11">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="I280" s="11" t="s">
         <v>1</v>
@@ -12569,28 +12575,28 @@
     </row>
     <row r="281" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="13" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B281" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C281" s="13" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D281" s="13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E281" s="13" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F281" s="13" t="s">
         <v>1066</v>
       </c>
-      <c r="D281" s="13" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E281" s="13" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F281" s="13" t="s">
-        <v>1064</v>
-      </c>
       <c r="G281" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H281" s="13">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I281" s="13" t="s">
         <v>1</v>
@@ -12598,28 +12604,28 @@
     </row>
     <row r="282" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="11" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C282" s="11" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="D282" s="11" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="E282" s="11" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="G282" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H282" s="11">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I282" s="11" t="s">
         <v>1</v>
@@ -12627,28 +12633,28 @@
     </row>
     <row r="283" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="13" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B283" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C283" s="13" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D283" s="13" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E283" s="13" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F283" s="13" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G283" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H283" s="13">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="I283" s="13" t="s">
         <v>1</v>
@@ -12656,28 +12662,28 @@
     </row>
     <row r="284" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C284" s="11" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D284" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E284" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F284" s="11" t="s">
         <v>1079</v>
       </c>
-      <c r="D284" s="11" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E284" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F284" s="11" t="s">
-        <v>1077</v>
-      </c>
       <c r="G284" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H284" s="11">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="I284" s="11" t="s">
         <v>1</v>
@@ -12685,28 +12691,28 @@
     </row>
     <row r="285" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="13" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B285" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C285" s="13" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="D285" s="13" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="E285" s="13" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F285" s="13" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G285" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H285" s="13">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="I285" s="13" t="s">
         <v>1</v>
@@ -12714,28 +12720,28 @@
     </row>
     <row r="286" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C286" s="11" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="E286" s="11" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G286" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H286" s="11">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="I286" s="11" t="s">
         <v>1</v>
@@ -12743,28 +12749,28 @@
     </row>
     <row r="287" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="13" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B287" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C287" s="13" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D287" s="13" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="E287" s="13" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F287" s="13" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G287" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H287" s="13">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I287" s="13" t="s">
         <v>1</v>
@@ -12772,28 +12778,28 @@
     </row>
     <row r="288" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="11" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C288" s="11" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="D288" s="11" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="E288" s="11" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G288" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H288" s="11">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I288" s="11" t="s">
         <v>1</v>
@@ -12801,28 +12807,28 @@
     </row>
     <row r="289" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="13" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B289" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C289" s="13" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D289" s="13" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="E289" s="13" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F289" s="13" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G289" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H289" s="13">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I289" s="13" t="s">
         <v>1</v>
@@ -12830,28 +12836,28 @@
     </row>
     <row r="290" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C290" s="11" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="D290" s="11" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="E290" s="11" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G290" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H290" s="11">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I290" s="11" t="s">
         <v>1</v>
@@ -12859,28 +12865,28 @@
     </row>
     <row r="291" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="13" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B291" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C291" s="13" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D291" s="13" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="E291" s="13" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F291" s="13" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="G291" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H291" s="13">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="I291" s="13" t="s">
         <v>1</v>
@@ -12888,28 +12894,28 @@
     </row>
     <row r="292" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="11" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C292" s="11" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="D292" s="11" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="E292" s="11" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="G292" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H292" s="11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I292" s="11" t="s">
         <v>1</v>
@@ -12917,28 +12923,28 @@
     </row>
     <row r="293" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="13" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B293" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C293" s="13" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="D293" s="13" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="E293" s="13" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="F293" s="13" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="G293" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H293" s="13">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="I293" s="13" t="s">
         <v>1</v>
@@ -12946,28 +12952,28 @@
     </row>
     <row r="294" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="11" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B294" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C294" s="11" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D294" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="E294" s="11" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="G294" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H294" s="11">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I294" s="11" t="s">
         <v>1</v>
@@ -12975,28 +12981,28 @@
     </row>
     <row r="295" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="13" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B295" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C295" s="13" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="D295" s="13" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="E295" s="13" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="F295" s="13" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="G295" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H295" s="13">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I295" s="13" t="s">
         <v>1</v>
@@ -13004,28 +13010,28 @@
     </row>
     <row r="296" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="11" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D296" s="11" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E296" s="11" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="G296" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H296" s="11">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="I296" s="11" t="s">
         <v>1</v>
@@ -13033,28 +13039,28 @@
     </row>
     <row r="297" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="13" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B297" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C297" s="13" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="D297" s="13" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="E297" s="13" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="F297" s="13" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="G297" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H297" s="13">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="I297" s="13" t="s">
         <v>1</v>
@@ -13062,28 +13068,28 @@
     </row>
     <row r="298" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="11" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="D298" s="11" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E298" s="11" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="G298" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H298" s="11">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I298" s="11" t="s">
         <v>1</v>
@@ -13091,28 +13097,28 @@
     </row>
     <row r="299" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="13" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="B299" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C299" s="13" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="D299" s="13" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="E299" s="13" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="F299" s="13" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="G299" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H299" s="13">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I299" s="13" t="s">
         <v>1</v>
@@ -13120,28 +13126,28 @@
     </row>
     <row r="300" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>29</v>
       </c>
       <c r="C300" s="11" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D300" s="11" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="E300" s="11" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="G300" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H300" s="11">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="I300" s="11" t="s">
         <v>1</v>
@@ -13149,28 +13155,28 @@
     </row>
     <row r="301" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="13" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="B301" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C301" s="13" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="D301" s="13" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E301" s="13" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="F301" s="13" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="G301" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H301" s="13">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I301" s="13" t="s">
         <v>1</v>

--- a/testing/appium-tests/Test_Report.xlsx
+++ b/testing/appium-tests/Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1147">
   <si>
     <t>GROWMARK MOBILE APP - AUTOMATED TESTING REPORT</t>
   </si>
@@ -1391,7 +1391,7 @@
     <t>TestCase_Sales_15: Submit random sales variation 15</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 84, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 120, Date: Today</t>
   </si>
   <si>
     <t>Sales record saved and threshold check triggered</t>
@@ -1406,7 +1406,7 @@
     <t>TestCase_Sales_16: Submit random sales variation 16</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 97, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 125, Date: Today</t>
   </si>
   <si>
     <t>TC111</t>
@@ -1415,7 +1415,7 @@
     <t>TestCase_Sales_17: Submit random sales variation 17</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 124, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 97, Date: Today</t>
   </si>
   <si>
     <t>TC112</t>
@@ -1424,7 +1424,7 @@
     <t>TestCase_Sales_18: Submit random sales variation 18</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 139, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 111, Date: Today</t>
   </si>
   <si>
     <t>TC113</t>
@@ -1433,7 +1433,7 @@
     <t>TestCase_Sales_19: Submit random sales variation 19</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 61, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 167, Date: Today</t>
   </si>
   <si>
     <t>TC114</t>
@@ -1442,7 +1442,7 @@
     <t>TestCase_Sales_20: Submit random sales variation 20</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 192, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 59, Date: Today</t>
   </si>
   <si>
     <t>TC115</t>
@@ -1451,7 +1451,7 @@
     <t>TestCase_Sales_21: Submit random sales variation 21</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 114, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 70, Date: Today</t>
   </si>
   <si>
     <t>TC116</t>
@@ -1460,7 +1460,7 @@
     <t>TestCase_Sales_22: Submit random sales variation 22</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 81, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 116, Date: Today</t>
   </si>
   <si>
     <t>TC117</t>
@@ -1469,7 +1469,7 @@
     <t>TestCase_Sales_23: Submit random sales variation 23</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 75, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 24, Date: Today</t>
   </si>
   <si>
     <t>TC118</t>
@@ -1478,7 +1478,7 @@
     <t>TestCase_Sales_24: Submit random sales variation 24</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 54, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 9, Date: Today</t>
   </si>
   <si>
     <t>TC119</t>
@@ -1487,7 +1487,7 @@
     <t>TestCase_Sales_25: Submit random sales variation 25</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 135, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 95, Date: Today</t>
   </si>
   <si>
     <t>TC120</t>
@@ -1496,7 +1496,7 @@
     <t>TestCase_Sales_26: Submit random sales variation 26</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 62, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 43, Date: Today</t>
   </si>
   <si>
     <t>TC121</t>
@@ -1505,7 +1505,7 @@
     <t>TestCase_Sales_27: Submit random sales variation 27</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 80, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 169, Date: Today</t>
   </si>
   <si>
     <t>TC122</t>
@@ -1514,7 +1514,7 @@
     <t>TestCase_Sales_28: Submit random sales variation 28</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 179, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 40, Date: Today</t>
   </si>
   <si>
     <t>TC123</t>
@@ -1523,7 +1523,7 @@
     <t>TestCase_Sales_29: Submit random sales variation 29</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 58, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 11, Date: Today</t>
   </si>
   <si>
     <t>TC124</t>
@@ -1532,7 +1532,7 @@
     <t>TestCase_Sales_30: Submit random sales variation 30</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 95, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 185, Date: Today</t>
   </si>
   <si>
     <t>TC125</t>
@@ -1541,7 +1541,7 @@
     <t>TestCase_Sales_31: Submit random sales variation 31</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 85, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 111, Date: Today</t>
   </si>
   <si>
     <t>TC126</t>
@@ -1550,7 +1550,7 @@
     <t>TestCase_Sales_32: Submit random sales variation 32</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 190, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 53, Date: Today</t>
   </si>
   <si>
     <t>TC127</t>
@@ -1559,7 +1559,7 @@
     <t>TestCase_Sales_33: Submit random sales variation 33</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 14, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 129, Date: Today</t>
   </si>
   <si>
     <t>TC128</t>
@@ -1568,7 +1568,7 @@
     <t>TestCase_Sales_34: Submit random sales variation 34</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 72, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 30, Date: Today</t>
   </si>
   <si>
     <t>TC129</t>
@@ -1577,7 +1577,7 @@
     <t>TestCase_Sales_35: Submit random sales variation 35</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 44, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 74, Date: Today</t>
   </si>
   <si>
     <t>TC130</t>
@@ -1586,7 +1586,7 @@
     <t>TestCase_Sales_36: Submit random sales variation 36</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 149, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 59, Date: Today</t>
   </si>
   <si>
     <t>TC131</t>
@@ -1595,7 +1595,7 @@
     <t>TestCase_Sales_37: Submit random sales variation 37</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 158, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 75, Date: Today</t>
   </si>
   <si>
     <t>TC132</t>
@@ -1604,7 +1604,7 @@
     <t>TestCase_Sales_38: Submit random sales variation 38</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 107, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 28, Date: Today</t>
   </si>
   <si>
     <t>TC133</t>
@@ -1613,7 +1613,7 @@
     <t>TestCase_Sales_39: Submit random sales variation 39</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 179, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 188, Date: Today</t>
   </si>
   <si>
     <t>TC134</t>
@@ -1622,7 +1622,7 @@
     <t>TestCase_Sales_40: Submit random sales variation 40</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 155, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 149, Date: Today</t>
   </si>
   <si>
     <t>TC135</t>
@@ -1631,7 +1631,7 @@
     <t>TestCase_Sales_41: Submit random sales variation 41</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 172, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 168, Date: Today</t>
   </si>
   <si>
     <t>TC136</t>
@@ -1640,7 +1640,7 @@
     <t>TestCase_Sales_42: Submit random sales variation 42</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 189, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 182, Date: Today</t>
   </si>
   <si>
     <t>TC137</t>
@@ -1649,7 +1649,7 @@
     <t>TestCase_Sales_43: Submit random sales variation 43</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 191, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 38, Date: Today</t>
   </si>
   <si>
     <t>TC138</t>
@@ -1658,7 +1658,7 @@
     <t>TestCase_Sales_44: Submit random sales variation 44</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 114, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 119, Date: Today</t>
   </si>
   <si>
     <t>TC139</t>
@@ -1667,7 +1667,7 @@
     <t>TestCase_Sales_45: Submit random sales variation 45</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 136, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 152, Date: Today</t>
   </si>
   <si>
     <t>TC140</t>
@@ -1676,7 +1676,7 @@
     <t>TestCase_Sales_46: Submit random sales variation 46</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 87, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 5, Date: Today</t>
   </si>
   <si>
     <t>TC141</t>
@@ -1685,7 +1685,7 @@
     <t>TestCase_Sales_47: Submit random sales variation 47</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 110, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 83, Date: Today</t>
   </si>
   <si>
     <t>TC142</t>
@@ -1694,7 +1694,7 @@
     <t>TestCase_Sales_48: Submit random sales variation 48</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 86, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 124, Date: Today</t>
   </si>
   <si>
     <t>TC143</t>
@@ -1703,7 +1703,7 @@
     <t>TestCase_Sales_49: Submit random sales variation 49</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 68, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 128, Date: Today</t>
   </si>
   <si>
     <t>TC144</t>
@@ -1712,7 +1712,7 @@
     <t>TestCase_Sales_50: Submit random sales variation 50</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 194, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 175, Date: Today</t>
   </si>
   <si>
     <t>TC145</t>
@@ -2876,154 +2876,157 @@
     <t>TC251</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_09: Score 29 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 29</t>
+    <t>TestCase_HealthScore_09: Score 65 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 65</t>
+  </si>
+  <si>
+    <t>Verdict: "Work in Progress" displayed</t>
+  </si>
+  <si>
+    <t>Verdict matched expected business logic</t>
+  </si>
+  <si>
+    <t>TC252</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_10: Score 4 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 4</t>
   </si>
   <si>
     <t>Verdict: "Immediate Action Needed" displayed</t>
   </si>
   <si>
-    <t>Verdict matched expected business logic</t>
-  </si>
-  <si>
-    <t>TC252</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_10: Score 98 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 98</t>
+    <t>TC253</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_11: Score 46 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 46</t>
+  </si>
+  <si>
+    <t>TC254</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_12: Score 1 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 1</t>
+  </si>
+  <si>
+    <t>TC255</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_13: Score 8 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 8</t>
+  </si>
+  <si>
+    <t>TC256</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_14: Score 69 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 69</t>
+  </si>
+  <si>
+    <t>TC257</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_15: Score 3 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 3</t>
+  </si>
+  <si>
+    <t>TC258</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_16: Score 16 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 16</t>
+  </si>
+  <si>
+    <t>TC259</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_17: Score 42 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 42</t>
+  </si>
+  <si>
+    <t>TC260</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_18: Score 73 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 73</t>
+  </si>
+  <si>
+    <t>TC261</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_19: Score 6 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 6</t>
+  </si>
+  <si>
+    <t>TC262</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_20: Score 27 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 27</t>
+  </si>
+  <si>
+    <t>TC263</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_21: Score 64 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 64</t>
+  </si>
+  <si>
+    <t>TC264</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_22: Score 74 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 74</t>
+  </si>
+  <si>
+    <t>TC265</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_23: Score 91 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 91</t>
   </si>
   <si>
     <t>Verdict: "Thriving" displayed</t>
   </si>
   <si>
-    <t>TC253</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_11: Score 33 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 33</t>
-  </si>
-  <si>
-    <t>TC254</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_12: Score 25 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 25</t>
-  </si>
-  <si>
-    <t>TC255</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_13: Score 16 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 16</t>
-  </si>
-  <si>
-    <t>TC256</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_14: Score 43 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 43</t>
-  </si>
-  <si>
-    <t>TC257</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_15: Score 44 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 44</t>
-  </si>
-  <si>
-    <t>TC258</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_16: Score 77 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 77</t>
-  </si>
-  <si>
-    <t>Verdict: "Work in Progress" displayed</t>
-  </si>
-  <si>
-    <t>TC259</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_17: Score 59 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 59</t>
-  </si>
-  <si>
-    <t>TC260</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_18: Score 18 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 18</t>
-  </si>
-  <si>
-    <t>TC261</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_19: Score 36 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 36</t>
-  </si>
-  <si>
-    <t>TC262</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_20: Score 45 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 45</t>
-  </si>
-  <si>
-    <t>TC263</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_21: Score 59 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>TC264</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_22: Score 38 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 38</t>
-  </si>
-  <si>
-    <t>TC265</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_23: Score 11 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 11</t>
-  </si>
-  <si>
     <t>TC266</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_24: Score 53 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 53</t>
+    <t>TestCase_HealthScore_24: Score 39 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 39</t>
   </si>
   <si>
     <t>TC267</t>
@@ -4505,7 +4508,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="11">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>1</v>
@@ -4534,7 +4537,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="13">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>1</v>
@@ -4563,7 +4566,7 @@
         <v>9</v>
       </c>
       <c r="H4" s="11">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>1</v>
@@ -4592,7 +4595,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="13">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>1</v>
@@ -4621,7 +4624,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>1</v>
@@ -4650,7 +4653,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="13">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>1</v>
@@ -4679,7 +4682,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="11">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>1</v>
@@ -4708,7 +4711,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="13">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>1</v>
@@ -4737,7 +4740,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="11">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>1</v>
@@ -4766,7 +4769,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="13">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>1</v>
@@ -4795,7 +4798,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="11">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>1</v>
@@ -4824,7 +4827,7 @@
         <v>9</v>
       </c>
       <c r="H13" s="13">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>1</v>
@@ -4853,7 +4856,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="11">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>1</v>
@@ -4882,7 +4885,7 @@
         <v>9</v>
       </c>
       <c r="H15" s="13">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>1</v>
@@ -4911,7 +4914,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="11">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>1</v>
@@ -4940,7 +4943,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="13">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>1</v>
@@ -4969,7 +4972,7 @@
         <v>9</v>
       </c>
       <c r="H18" s="11">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>1</v>
@@ -4998,7 +5001,7 @@
         <v>9</v>
       </c>
       <c r="H19" s="13">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>1</v>
@@ -5027,7 +5030,7 @@
         <v>9</v>
       </c>
       <c r="H20" s="11">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>1</v>
@@ -5056,7 +5059,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="13">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>1</v>
@@ -5085,7 +5088,7 @@
         <v>9</v>
       </c>
       <c r="H22" s="11">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>1</v>
@@ -5114,7 +5117,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="13">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>1</v>
@@ -5143,7 +5146,7 @@
         <v>9</v>
       </c>
       <c r="H24" s="11">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>1</v>
@@ -5172,7 +5175,7 @@
         <v>9</v>
       </c>
       <c r="H25" s="13">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>1</v>
@@ -5201,7 +5204,7 @@
         <v>9</v>
       </c>
       <c r="H26" s="11">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>1</v>
@@ -5230,7 +5233,7 @@
         <v>9</v>
       </c>
       <c r="H27" s="13">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>1</v>
@@ -5259,7 +5262,7 @@
         <v>9</v>
       </c>
       <c r="H28" s="11">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>1</v>
@@ -5288,7 +5291,7 @@
         <v>9</v>
       </c>
       <c r="H29" s="13">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>1</v>
@@ -5317,7 +5320,7 @@
         <v>9</v>
       </c>
       <c r="H30" s="11">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>1</v>
@@ -5346,7 +5349,7 @@
         <v>9</v>
       </c>
       <c r="H31" s="13">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>1</v>
@@ -5375,7 +5378,7 @@
         <v>9</v>
       </c>
       <c r="H32" s="11">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>1</v>
@@ -5404,7 +5407,7 @@
         <v>9</v>
       </c>
       <c r="H33" s="13">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>1</v>
@@ -5433,7 +5436,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="11">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>1</v>
@@ -5462,7 +5465,7 @@
         <v>9</v>
       </c>
       <c r="H35" s="13">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="I35" s="13" t="s">
         <v>1</v>
@@ -5491,7 +5494,7 @@
         <v>9</v>
       </c>
       <c r="H36" s="11">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>1</v>
@@ -5520,7 +5523,7 @@
         <v>9</v>
       </c>
       <c r="H37" s="13">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>1</v>
@@ -5549,7 +5552,7 @@
         <v>9</v>
       </c>
       <c r="H38" s="11">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>1</v>
@@ -5578,7 +5581,7 @@
         <v>9</v>
       </c>
       <c r="H39" s="13">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>1</v>
@@ -5607,7 +5610,7 @@
         <v>9</v>
       </c>
       <c r="H40" s="11">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>1</v>
@@ -5636,7 +5639,7 @@
         <v>9</v>
       </c>
       <c r="H41" s="13">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>1</v>
@@ -5665,7 +5668,7 @@
         <v>9</v>
       </c>
       <c r="H42" s="11">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>1</v>
@@ -5694,7 +5697,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="13">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>1</v>
@@ -5723,7 +5726,7 @@
         <v>9</v>
       </c>
       <c r="H44" s="11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>1</v>
@@ -5752,7 +5755,7 @@
         <v>9</v>
       </c>
       <c r="H45" s="13">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>1</v>
@@ -5781,7 +5784,7 @@
         <v>9</v>
       </c>
       <c r="H46" s="11">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>1</v>
@@ -5810,7 +5813,7 @@
         <v>9</v>
       </c>
       <c r="H47" s="13">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>1</v>
@@ -5839,7 +5842,7 @@
         <v>9</v>
       </c>
       <c r="H48" s="11">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>1</v>
@@ -5868,7 +5871,7 @@
         <v>9</v>
       </c>
       <c r="H49" s="13">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>1</v>
@@ -5897,7 +5900,7 @@
         <v>9</v>
       </c>
       <c r="H50" s="11">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>1</v>
@@ -5926,7 +5929,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="13">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>1</v>
@@ -5955,7 +5958,7 @@
         <v>9</v>
       </c>
       <c r="H52" s="11">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>1</v>
@@ -5984,7 +5987,7 @@
         <v>9</v>
       </c>
       <c r="H53" s="13">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>1</v>
@@ -6013,7 +6016,7 @@
         <v>9</v>
       </c>
       <c r="H54" s="11">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>1</v>
@@ -6042,7 +6045,7 @@
         <v>9</v>
       </c>
       <c r="H55" s="13">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>1</v>
@@ -6071,7 +6074,7 @@
         <v>9</v>
       </c>
       <c r="H56" s="11">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>1</v>
@@ -6100,7 +6103,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="13">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>1</v>
@@ -6129,7 +6132,7 @@
         <v>9</v>
       </c>
       <c r="H58" s="11">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>1</v>
@@ -6158,7 +6161,7 @@
         <v>9</v>
       </c>
       <c r="H59" s="13">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>1</v>
@@ -6187,7 +6190,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="11">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>1</v>
@@ -6216,7 +6219,7 @@
         <v>9</v>
       </c>
       <c r="H61" s="13">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>1</v>
@@ -6245,7 +6248,7 @@
         <v>9</v>
       </c>
       <c r="H62" s="11">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>1</v>
@@ -6274,7 +6277,7 @@
         <v>9</v>
       </c>
       <c r="H63" s="13">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>1</v>
@@ -6303,7 +6306,7 @@
         <v>9</v>
       </c>
       <c r="H64" s="11">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>1</v>
@@ -6332,7 +6335,7 @@
         <v>9</v>
       </c>
       <c r="H65" s="13">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>1</v>
@@ -6361,7 +6364,7 @@
         <v>9</v>
       </c>
       <c r="H66" s="11">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>1</v>
@@ -6390,7 +6393,7 @@
         <v>9</v>
       </c>
       <c r="H67" s="13">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>1</v>
@@ -6419,7 +6422,7 @@
         <v>9</v>
       </c>
       <c r="H68" s="11">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>1</v>
@@ -6448,7 +6451,7 @@
         <v>9</v>
       </c>
       <c r="H69" s="13">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>1</v>
@@ -6477,7 +6480,7 @@
         <v>9</v>
       </c>
       <c r="H70" s="11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>1</v>
@@ -6506,7 +6509,7 @@
         <v>9</v>
       </c>
       <c r="H71" s="13">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>1</v>
@@ -6535,7 +6538,7 @@
         <v>9</v>
       </c>
       <c r="H72" s="11">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>1</v>
@@ -6564,7 +6567,7 @@
         <v>9</v>
       </c>
       <c r="H73" s="13">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>1</v>
@@ -6593,7 +6596,7 @@
         <v>9</v>
       </c>
       <c r="H74" s="11">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>1</v>
@@ -6622,7 +6625,7 @@
         <v>9</v>
       </c>
       <c r="H75" s="13">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>1</v>
@@ -6651,7 +6654,7 @@
         <v>9</v>
       </c>
       <c r="H76" s="11">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>1</v>
@@ -6680,7 +6683,7 @@
         <v>9</v>
       </c>
       <c r="H77" s="13">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>1</v>
@@ -6709,7 +6712,7 @@
         <v>9</v>
       </c>
       <c r="H78" s="11">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>1</v>
@@ -6738,7 +6741,7 @@
         <v>9</v>
       </c>
       <c r="H79" s="13">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>1</v>
@@ -6767,7 +6770,7 @@
         <v>9</v>
       </c>
       <c r="H80" s="11">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>1</v>
@@ -6825,7 +6828,7 @@
         <v>9</v>
       </c>
       <c r="H82" s="11">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>1</v>
@@ -6854,7 +6857,7 @@
         <v>9</v>
       </c>
       <c r="H83" s="13">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I83" s="13" t="s">
         <v>1</v>
@@ -6883,7 +6886,7 @@
         <v>9</v>
       </c>
       <c r="H84" s="11">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>1</v>
@@ -6912,7 +6915,7 @@
         <v>9</v>
       </c>
       <c r="H85" s="13">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>1</v>
@@ -6941,7 +6944,7 @@
         <v>9</v>
       </c>
       <c r="H86" s="11">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>1</v>
@@ -6970,7 +6973,7 @@
         <v>9</v>
       </c>
       <c r="H87" s="13">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>1</v>
@@ -6999,7 +7002,7 @@
         <v>9</v>
       </c>
       <c r="H88" s="11">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>1</v>
@@ -7028,7 +7031,7 @@
         <v>9</v>
       </c>
       <c r="H89" s="13">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I89" s="13" t="s">
         <v>1</v>
@@ -7086,7 +7089,7 @@
         <v>9</v>
       </c>
       <c r="H91" s="13">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="I91" s="13" t="s">
         <v>1</v>
@@ -7115,7 +7118,7 @@
         <v>9</v>
       </c>
       <c r="H92" s="11">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="I92" s="11" t="s">
         <v>1</v>
@@ -7144,7 +7147,7 @@
         <v>9</v>
       </c>
       <c r="H93" s="13">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="I93" s="13" t="s">
         <v>1</v>
@@ -7173,7 +7176,7 @@
         <v>9</v>
       </c>
       <c r="H94" s="11">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>1</v>
@@ -7202,7 +7205,7 @@
         <v>9</v>
       </c>
       <c r="H95" s="13">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I95" s="13" t="s">
         <v>1</v>
@@ -7231,7 +7234,7 @@
         <v>9</v>
       </c>
       <c r="H96" s="11">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>1</v>
@@ -7260,7 +7263,7 @@
         <v>9</v>
       </c>
       <c r="H97" s="13">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="I97" s="13" t="s">
         <v>1</v>
@@ -7289,7 +7292,7 @@
         <v>9</v>
       </c>
       <c r="H98" s="11">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>1</v>
@@ -7318,7 +7321,7 @@
         <v>9</v>
       </c>
       <c r="H99" s="13">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="I99" s="13" t="s">
         <v>1</v>
@@ -7347,7 +7350,7 @@
         <v>9</v>
       </c>
       <c r="H100" s="11">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>1</v>
@@ -7376,7 +7379,7 @@
         <v>9</v>
       </c>
       <c r="H101" s="13">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I101" s="13" t="s">
         <v>1</v>
@@ -7405,7 +7408,7 @@
         <v>9</v>
       </c>
       <c r="H102" s="11">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>1</v>
@@ -7434,7 +7437,7 @@
         <v>9</v>
       </c>
       <c r="H103" s="13">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I103" s="13" t="s">
         <v>1</v>
@@ -7463,7 +7466,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="11">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>1</v>
@@ -7492,7 +7495,7 @@
         <v>9</v>
       </c>
       <c r="H105" s="13">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I105" s="13" t="s">
         <v>1</v>
@@ -7521,7 +7524,7 @@
         <v>9</v>
       </c>
       <c r="H106" s="11">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>1</v>
@@ -7550,7 +7553,7 @@
         <v>9</v>
       </c>
       <c r="H107" s="13">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I107" s="13" t="s">
         <v>1</v>
@@ -7579,7 +7582,7 @@
         <v>9</v>
       </c>
       <c r="H108" s="11">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>1</v>
@@ -7608,7 +7611,7 @@
         <v>9</v>
       </c>
       <c r="H109" s="13">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I109" s="13" t="s">
         <v>1</v>
@@ -7637,7 +7640,7 @@
         <v>9</v>
       </c>
       <c r="H110" s="11">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>1</v>
@@ -7666,7 +7669,7 @@
         <v>9</v>
       </c>
       <c r="H111" s="13">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="I111" s="13" t="s">
         <v>1</v>
@@ -7695,7 +7698,7 @@
         <v>9</v>
       </c>
       <c r="H112" s="11">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="I112" s="11" t="s">
         <v>1</v>
@@ -7724,7 +7727,7 @@
         <v>9</v>
       </c>
       <c r="H113" s="13">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="I113" s="13" t="s">
         <v>1</v>
@@ -7753,7 +7756,7 @@
         <v>9</v>
       </c>
       <c r="H114" s="11">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="I114" s="11" t="s">
         <v>1</v>
@@ -7782,7 +7785,7 @@
         <v>9</v>
       </c>
       <c r="H115" s="13">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="I115" s="13" t="s">
         <v>1</v>
@@ -7811,7 +7814,7 @@
         <v>9</v>
       </c>
       <c r="H116" s="11">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="I116" s="11" t="s">
         <v>1</v>
@@ -7840,7 +7843,7 @@
         <v>9</v>
       </c>
       <c r="H117" s="13">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I117" s="13" t="s">
         <v>1</v>
@@ -7869,7 +7872,7 @@
         <v>9</v>
       </c>
       <c r="H118" s="11">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>1</v>
@@ -7898,7 +7901,7 @@
         <v>9</v>
       </c>
       <c r="H119" s="13">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="I119" s="13" t="s">
         <v>1</v>
@@ -7927,7 +7930,7 @@
         <v>9</v>
       </c>
       <c r="H120" s="11">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>1</v>
@@ -7956,7 +7959,7 @@
         <v>9</v>
       </c>
       <c r="H121" s="13">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>1</v>
@@ -7985,7 +7988,7 @@
         <v>9</v>
       </c>
       <c r="H122" s="11">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="I122" s="11" t="s">
         <v>1</v>
@@ -8014,7 +8017,7 @@
         <v>9</v>
       </c>
       <c r="H123" s="13">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>1</v>
@@ -8043,7 +8046,7 @@
         <v>9</v>
       </c>
       <c r="H124" s="11">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="I124" s="11" t="s">
         <v>1</v>
@@ -8072,7 +8075,7 @@
         <v>9</v>
       </c>
       <c r="H125" s="13">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>1</v>
@@ -8101,7 +8104,7 @@
         <v>9</v>
       </c>
       <c r="H126" s="11">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I126" s="11" t="s">
         <v>1</v>
@@ -8130,7 +8133,7 @@
         <v>9</v>
       </c>
       <c r="H127" s="13">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>1</v>
@@ -8159,7 +8162,7 @@
         <v>9</v>
       </c>
       <c r="H128" s="11">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>1</v>
@@ -8188,7 +8191,7 @@
         <v>9</v>
       </c>
       <c r="H129" s="13">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>1</v>
@@ -8217,7 +8220,7 @@
         <v>9</v>
       </c>
       <c r="H130" s="11">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="I130" s="11" t="s">
         <v>1</v>
@@ -8246,7 +8249,7 @@
         <v>9</v>
       </c>
       <c r="H131" s="13">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>1</v>
@@ -8275,7 +8278,7 @@
         <v>9</v>
       </c>
       <c r="H132" s="11">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I132" s="11" t="s">
         <v>1</v>
@@ -8304,7 +8307,7 @@
         <v>9</v>
       </c>
       <c r="H133" s="13">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>1</v>
@@ -8333,7 +8336,7 @@
         <v>9</v>
       </c>
       <c r="H134" s="11">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="I134" s="11" t="s">
         <v>1</v>
@@ -8362,7 +8365,7 @@
         <v>9</v>
       </c>
       <c r="H135" s="13">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>1</v>
@@ -8391,7 +8394,7 @@
         <v>9</v>
       </c>
       <c r="H136" s="11">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="I136" s="11" t="s">
         <v>1</v>
@@ -8420,7 +8423,7 @@
         <v>9</v>
       </c>
       <c r="H137" s="13">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I137" s="13" t="s">
         <v>1</v>
@@ -8449,7 +8452,7 @@
         <v>9</v>
       </c>
       <c r="H138" s="11">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I138" s="11" t="s">
         <v>1</v>
@@ -8478,7 +8481,7 @@
         <v>9</v>
       </c>
       <c r="H139" s="13">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="I139" s="13" t="s">
         <v>1</v>
@@ -8507,7 +8510,7 @@
         <v>9</v>
       </c>
       <c r="H140" s="11">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="I140" s="11" t="s">
         <v>1</v>
@@ -8536,7 +8539,7 @@
         <v>9</v>
       </c>
       <c r="H141" s="13">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="I141" s="13" t="s">
         <v>1</v>
@@ -8565,7 +8568,7 @@
         <v>9</v>
       </c>
       <c r="H142" s="11">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I142" s="11" t="s">
         <v>1</v>
@@ -8594,7 +8597,7 @@
         <v>9</v>
       </c>
       <c r="H143" s="13">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>1</v>
@@ -8623,7 +8626,7 @@
         <v>9</v>
       </c>
       <c r="H144" s="11">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="I144" s="11" t="s">
         <v>1</v>
@@ -8652,7 +8655,7 @@
         <v>9</v>
       </c>
       <c r="H145" s="13">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="I145" s="13" t="s">
         <v>1</v>
@@ -8681,7 +8684,7 @@
         <v>9</v>
       </c>
       <c r="H146" s="11">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I146" s="11" t="s">
         <v>1</v>
@@ -8710,7 +8713,7 @@
         <v>9</v>
       </c>
       <c r="H147" s="13">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="I147" s="13" t="s">
         <v>1</v>
@@ -8739,7 +8742,7 @@
         <v>9</v>
       </c>
       <c r="H148" s="11">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I148" s="11" t="s">
         <v>1</v>
@@ -8768,7 +8771,7 @@
         <v>9</v>
       </c>
       <c r="H149" s="13">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="I149" s="13" t="s">
         <v>1</v>
@@ -8797,7 +8800,7 @@
         <v>9</v>
       </c>
       <c r="H150" s="11">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I150" s="11" t="s">
         <v>1</v>
@@ -8826,7 +8829,7 @@
         <v>9</v>
       </c>
       <c r="H151" s="13">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="I151" s="13" t="s">
         <v>1</v>
@@ -8855,7 +8858,7 @@
         <v>9</v>
       </c>
       <c r="H152" s="11">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="I152" s="11" t="s">
         <v>1</v>
@@ -8884,7 +8887,7 @@
         <v>9</v>
       </c>
       <c r="H153" s="13">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="I153" s="13" t="s">
         <v>1</v>
@@ -8942,7 +8945,7 @@
         <v>9</v>
       </c>
       <c r="H155" s="13">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I155" s="13" t="s">
         <v>1</v>
@@ -8971,7 +8974,7 @@
         <v>9</v>
       </c>
       <c r="H156" s="11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I156" s="11" t="s">
         <v>1</v>
@@ -9000,7 +9003,7 @@
         <v>9</v>
       </c>
       <c r="H157" s="13">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>1</v>
@@ -9029,7 +9032,7 @@
         <v>9</v>
       </c>
       <c r="H158" s="11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I158" s="11" t="s">
         <v>1</v>
@@ -9058,7 +9061,7 @@
         <v>9</v>
       </c>
       <c r="H159" s="13">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I159" s="13" t="s">
         <v>1</v>
@@ -9087,7 +9090,7 @@
         <v>9</v>
       </c>
       <c r="H160" s="11">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="I160" s="11" t="s">
         <v>1</v>
@@ -9116,7 +9119,7 @@
         <v>9</v>
       </c>
       <c r="H161" s="13">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="I161" s="13" t="s">
         <v>1</v>
@@ -9145,7 +9148,7 @@
         <v>9</v>
       </c>
       <c r="H162" s="11">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="I162" s="11" t="s">
         <v>1</v>
@@ -9174,7 +9177,7 @@
         <v>9</v>
       </c>
       <c r="H163" s="13">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>1</v>
@@ -9203,7 +9206,7 @@
         <v>9</v>
       </c>
       <c r="H164" s="11">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="I164" s="11" t="s">
         <v>1</v>
@@ -9232,7 +9235,7 @@
         <v>9</v>
       </c>
       <c r="H165" s="13">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="I165" s="13" t="s">
         <v>1</v>
@@ -9261,7 +9264,7 @@
         <v>9</v>
       </c>
       <c r="H166" s="11">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="I166" s="11" t="s">
         <v>1</v>
@@ -9290,7 +9293,7 @@
         <v>9</v>
       </c>
       <c r="H167" s="13">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="I167" s="13" t="s">
         <v>1</v>
@@ -9319,7 +9322,7 @@
         <v>9</v>
       </c>
       <c r="H168" s="11">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I168" s="11" t="s">
         <v>1</v>
@@ -9348,7 +9351,7 @@
         <v>9</v>
       </c>
       <c r="H169" s="13">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I169" s="13" t="s">
         <v>1</v>
@@ -9377,7 +9380,7 @@
         <v>9</v>
       </c>
       <c r="H170" s="11">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I170" s="11" t="s">
         <v>1</v>
@@ -9406,7 +9409,7 @@
         <v>9</v>
       </c>
       <c r="H171" s="13">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="I171" s="13" t="s">
         <v>1</v>
@@ -9435,7 +9438,7 @@
         <v>9</v>
       </c>
       <c r="H172" s="11">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I172" s="11" t="s">
         <v>1</v>
@@ -9464,7 +9467,7 @@
         <v>9</v>
       </c>
       <c r="H173" s="13">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="I173" s="13" t="s">
         <v>1</v>
@@ -9493,7 +9496,7 @@
         <v>9</v>
       </c>
       <c r="H174" s="11">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I174" s="11" t="s">
         <v>1</v>
@@ -9522,7 +9525,7 @@
         <v>9</v>
       </c>
       <c r="H175" s="13">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="I175" s="13" t="s">
         <v>1</v>
@@ -9551,7 +9554,7 @@
         <v>9</v>
       </c>
       <c r="H176" s="11">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="I176" s="11" t="s">
         <v>1</v>
@@ -9580,7 +9583,7 @@
         <v>9</v>
       </c>
       <c r="H177" s="13">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I177" s="13" t="s">
         <v>1</v>
@@ -9609,7 +9612,7 @@
         <v>9</v>
       </c>
       <c r="H178" s="11">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="I178" s="11" t="s">
         <v>1</v>
@@ -9638,7 +9641,7 @@
         <v>9</v>
       </c>
       <c r="H179" s="13">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="I179" s="13" t="s">
         <v>1</v>
@@ -9667,7 +9670,7 @@
         <v>9</v>
       </c>
       <c r="H180" s="11">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="I180" s="11" t="s">
         <v>1</v>
@@ -9696,7 +9699,7 @@
         <v>9</v>
       </c>
       <c r="H181" s="13">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="I181" s="13" t="s">
         <v>1</v>
@@ -9725,7 +9728,7 @@
         <v>9</v>
       </c>
       <c r="H182" s="11">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I182" s="11" t="s">
         <v>1</v>
@@ -9754,7 +9757,7 @@
         <v>9</v>
       </c>
       <c r="H183" s="13">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="I183" s="13" t="s">
         <v>1</v>
@@ -9783,7 +9786,7 @@
         <v>9</v>
       </c>
       <c r="H184" s="11">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I184" s="11" t="s">
         <v>1</v>
@@ -9812,7 +9815,7 @@
         <v>9</v>
       </c>
       <c r="H185" s="13">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I185" s="13" t="s">
         <v>1</v>
@@ -9841,7 +9844,7 @@
         <v>9</v>
       </c>
       <c r="H186" s="11">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I186" s="11" t="s">
         <v>1</v>
@@ -9870,7 +9873,7 @@
         <v>9</v>
       </c>
       <c r="H187" s="13">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I187" s="13" t="s">
         <v>1</v>
@@ -9899,7 +9902,7 @@
         <v>9</v>
       </c>
       <c r="H188" s="11">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="I188" s="11" t="s">
         <v>1</v>
@@ -9928,7 +9931,7 @@
         <v>9</v>
       </c>
       <c r="H189" s="13">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="I189" s="13" t="s">
         <v>1</v>
@@ -9957,7 +9960,7 @@
         <v>9</v>
       </c>
       <c r="H190" s="11">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="I190" s="11" t="s">
         <v>1</v>
@@ -9986,7 +9989,7 @@
         <v>9</v>
       </c>
       <c r="H191" s="13">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="I191" s="13" t="s">
         <v>1</v>
@@ -10015,7 +10018,7 @@
         <v>9</v>
       </c>
       <c r="H192" s="11">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="I192" s="11" t="s">
         <v>1</v>
@@ -10044,7 +10047,7 @@
         <v>9</v>
       </c>
       <c r="H193" s="13">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="I193" s="13" t="s">
         <v>1</v>
@@ -10073,7 +10076,7 @@
         <v>9</v>
       </c>
       <c r="H194" s="11">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="I194" s="11" t="s">
         <v>1</v>
@@ -10102,7 +10105,7 @@
         <v>9</v>
       </c>
       <c r="H195" s="13">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>1</v>
@@ -10131,7 +10134,7 @@
         <v>9</v>
       </c>
       <c r="H196" s="11">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="I196" s="11" t="s">
         <v>1</v>
@@ -10160,7 +10163,7 @@
         <v>9</v>
       </c>
       <c r="H197" s="13">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>1</v>
@@ -10189,7 +10192,7 @@
         <v>9</v>
       </c>
       <c r="H198" s="11">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="I198" s="11" t="s">
         <v>1</v>
@@ -10218,7 +10221,7 @@
         <v>9</v>
       </c>
       <c r="H199" s="13">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="I199" s="13" t="s">
         <v>1</v>
@@ -10247,7 +10250,7 @@
         <v>9</v>
       </c>
       <c r="H200" s="11">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I200" s="11" t="s">
         <v>1</v>
@@ -10276,7 +10279,7 @@
         <v>9</v>
       </c>
       <c r="H201" s="13">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I201" s="13" t="s">
         <v>1</v>
@@ -10305,7 +10308,7 @@
         <v>9</v>
       </c>
       <c r="H202" s="11">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="I202" s="11" t="s">
         <v>1</v>
@@ -10334,7 +10337,7 @@
         <v>9</v>
       </c>
       <c r="H203" s="13">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I203" s="13" t="s">
         <v>1</v>
@@ -10363,7 +10366,7 @@
         <v>9</v>
       </c>
       <c r="H204" s="11">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="I204" s="11" t="s">
         <v>1</v>
@@ -10392,7 +10395,7 @@
         <v>9</v>
       </c>
       <c r="H205" s="13">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="I205" s="13" t="s">
         <v>1</v>
@@ -10421,7 +10424,7 @@
         <v>9</v>
       </c>
       <c r="H206" s="11">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="I206" s="11" t="s">
         <v>1</v>
@@ -10450,7 +10453,7 @@
         <v>9</v>
       </c>
       <c r="H207" s="13">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I207" s="13" t="s">
         <v>1</v>
@@ -10479,7 +10482,7 @@
         <v>9</v>
       </c>
       <c r="H208" s="11">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="I208" s="11" t="s">
         <v>1</v>
@@ -10508,7 +10511,7 @@
         <v>9</v>
       </c>
       <c r="H209" s="13">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="I209" s="13" t="s">
         <v>1</v>
@@ -10537,7 +10540,7 @@
         <v>9</v>
       </c>
       <c r="H210" s="11">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I210" s="11" t="s">
         <v>1</v>
@@ -10566,7 +10569,7 @@
         <v>9</v>
       </c>
       <c r="H211" s="13">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I211" s="13" t="s">
         <v>1</v>
@@ -10595,7 +10598,7 @@
         <v>9</v>
       </c>
       <c r="H212" s="11">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I212" s="11" t="s">
         <v>1</v>
@@ -10624,7 +10627,7 @@
         <v>9</v>
       </c>
       <c r="H213" s="13">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="I213" s="13" t="s">
         <v>1</v>
@@ -10653,7 +10656,7 @@
         <v>9</v>
       </c>
       <c r="H214" s="11">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="I214" s="11" t="s">
         <v>1</v>
@@ -10682,7 +10685,7 @@
         <v>9</v>
       </c>
       <c r="H215" s="13">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="I215" s="13" t="s">
         <v>1</v>
@@ -10711,7 +10714,7 @@
         <v>9</v>
       </c>
       <c r="H216" s="11">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="I216" s="11" t="s">
         <v>1</v>
@@ -10740,7 +10743,7 @@
         <v>9</v>
       </c>
       <c r="H217" s="13">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="I217" s="13" t="s">
         <v>1</v>
@@ -10769,7 +10772,7 @@
         <v>9</v>
       </c>
       <c r="H218" s="11">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I218" s="11" t="s">
         <v>1</v>
@@ -10798,7 +10801,7 @@
         <v>9</v>
       </c>
       <c r="H219" s="13">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="I219" s="13" t="s">
         <v>1</v>
@@ -10827,7 +10830,7 @@
         <v>9</v>
       </c>
       <c r="H220" s="11">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I220" s="11" t="s">
         <v>1</v>
@@ -10856,7 +10859,7 @@
         <v>9</v>
       </c>
       <c r="H221" s="13">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="I221" s="13" t="s">
         <v>1</v>
@@ -10885,7 +10888,7 @@
         <v>9</v>
       </c>
       <c r="H222" s="11">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I222" s="11" t="s">
         <v>1</v>
@@ -10914,7 +10917,7 @@
         <v>9</v>
       </c>
       <c r="H223" s="13">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="I223" s="13" t="s">
         <v>1</v>
@@ -10943,7 +10946,7 @@
         <v>9</v>
       </c>
       <c r="H224" s="11">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I224" s="11" t="s">
         <v>1</v>
@@ -10972,7 +10975,7 @@
         <v>9</v>
       </c>
       <c r="H225" s="13">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I225" s="13" t="s">
         <v>1</v>
@@ -11001,7 +11004,7 @@
         <v>9</v>
       </c>
       <c r="H226" s="11">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="I226" s="11" t="s">
         <v>1</v>
@@ -11030,7 +11033,7 @@
         <v>9</v>
       </c>
       <c r="H227" s="13">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="I227" s="13" t="s">
         <v>1</v>
@@ -11059,7 +11062,7 @@
         <v>9</v>
       </c>
       <c r="H228" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I228" s="11" t="s">
         <v>1</v>
@@ -11088,7 +11091,7 @@
         <v>9</v>
       </c>
       <c r="H229" s="13">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="I229" s="13" t="s">
         <v>1</v>
@@ -11117,7 +11120,7 @@
         <v>9</v>
       </c>
       <c r="H230" s="11">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="I230" s="11" t="s">
         <v>1</v>
@@ -11146,7 +11149,7 @@
         <v>9</v>
       </c>
       <c r="H231" s="13">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="I231" s="13" t="s">
         <v>1</v>
@@ -11175,7 +11178,7 @@
         <v>9</v>
       </c>
       <c r="H232" s="11">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I232" s="11" t="s">
         <v>1</v>
@@ -11204,7 +11207,7 @@
         <v>9</v>
       </c>
       <c r="H233" s="13">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="I233" s="13" t="s">
         <v>1</v>
@@ -11233,7 +11236,7 @@
         <v>9</v>
       </c>
       <c r="H234" s="11">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I234" s="11" t="s">
         <v>1</v>
@@ -11262,7 +11265,7 @@
         <v>9</v>
       </c>
       <c r="H235" s="13">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="I235" s="13" t="s">
         <v>1</v>
@@ -11291,7 +11294,7 @@
         <v>9</v>
       </c>
       <c r="H236" s="11">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="I236" s="11" t="s">
         <v>1</v>
@@ -11320,7 +11323,7 @@
         <v>9</v>
       </c>
       <c r="H237" s="13">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="I237" s="13" t="s">
         <v>1</v>
@@ -11349,7 +11352,7 @@
         <v>9</v>
       </c>
       <c r="H238" s="11">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>1</v>
@@ -11378,7 +11381,7 @@
         <v>9</v>
       </c>
       <c r="H239" s="13">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="I239" s="13" t="s">
         <v>1</v>
@@ -11407,7 +11410,7 @@
         <v>9</v>
       </c>
       <c r="H240" s="11">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>1</v>
@@ -11436,7 +11439,7 @@
         <v>9</v>
       </c>
       <c r="H241" s="13">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="I241" s="13" t="s">
         <v>1</v>
@@ -11465,7 +11468,7 @@
         <v>9</v>
       </c>
       <c r="H242" s="11">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I242" s="11" t="s">
         <v>1</v>
@@ -11494,7 +11497,7 @@
         <v>9</v>
       </c>
       <c r="H243" s="13">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="I243" s="13" t="s">
         <v>1</v>
@@ -11523,7 +11526,7 @@
         <v>9</v>
       </c>
       <c r="H244" s="11">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="I244" s="11" t="s">
         <v>1</v>
@@ -11552,7 +11555,7 @@
         <v>9</v>
       </c>
       <c r="H245" s="13">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="I245" s="13" t="s">
         <v>1</v>
@@ -11581,7 +11584,7 @@
         <v>9</v>
       </c>
       <c r="H246" s="11">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="I246" s="11" t="s">
         <v>1</v>
@@ -11610,7 +11613,7 @@
         <v>9</v>
       </c>
       <c r="H247" s="13">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="I247" s="13" t="s">
         <v>1</v>
@@ -11639,7 +11642,7 @@
         <v>9</v>
       </c>
       <c r="H248" s="11">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="I248" s="11" t="s">
         <v>1</v>
@@ -11668,7 +11671,7 @@
         <v>9</v>
       </c>
       <c r="H249" s="13">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I249" s="13" t="s">
         <v>1</v>
@@ -11697,7 +11700,7 @@
         <v>9</v>
       </c>
       <c r="H250" s="11">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="I250" s="11" t="s">
         <v>1</v>
@@ -11726,7 +11729,7 @@
         <v>9</v>
       </c>
       <c r="H251" s="13">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="I251" s="13" t="s">
         <v>1</v>
@@ -11755,7 +11758,7 @@
         <v>9</v>
       </c>
       <c r="H252" s="11">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="I252" s="11" t="s">
         <v>1</v>
@@ -11784,7 +11787,7 @@
         <v>9</v>
       </c>
       <c r="H253" s="13">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I253" s="13" t="s">
         <v>1</v>
@@ -11804,7 +11807,7 @@
         <v>964</v>
       </c>
       <c r="E254" s="11" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F254" s="11" t="s">
         <v>957</v>
@@ -11813,7 +11816,7 @@
         <v>9</v>
       </c>
       <c r="H254" s="11">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="I254" s="11" t="s">
         <v>1</v>
@@ -11833,7 +11836,7 @@
         <v>967</v>
       </c>
       <c r="E255" s="13" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F255" s="13" t="s">
         <v>957</v>
@@ -11842,7 +11845,7 @@
         <v>9</v>
       </c>
       <c r="H255" s="13">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="I255" s="13" t="s">
         <v>1</v>
@@ -11862,7 +11865,7 @@
         <v>970</v>
       </c>
       <c r="E256" s="11" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F256" s="11" t="s">
         <v>957</v>
@@ -11871,7 +11874,7 @@
         <v>9</v>
       </c>
       <c r="H256" s="11">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="I256" s="11" t="s">
         <v>1</v>
@@ -11900,7 +11903,7 @@
         <v>9</v>
       </c>
       <c r="H257" s="13">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="I257" s="13" t="s">
         <v>1</v>
@@ -11920,7 +11923,7 @@
         <v>976</v>
       </c>
       <c r="E258" s="11" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F258" s="11" t="s">
         <v>957</v>
@@ -11929,7 +11932,7 @@
         <v>9</v>
       </c>
       <c r="H258" s="11">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="I258" s="11" t="s">
         <v>1</v>
@@ -11949,7 +11952,7 @@
         <v>979</v>
       </c>
       <c r="E259" s="13" t="s">
-        <v>980</v>
+        <v>961</v>
       </c>
       <c r="F259" s="13" t="s">
         <v>957</v>
@@ -11958,7 +11961,7 @@
         <v>9</v>
       </c>
       <c r="H259" s="13">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="I259" s="13" t="s">
         <v>1</v>
@@ -11966,19 +11969,19 @@
     </row>
     <row r="260" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B260" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C260" s="11" t="s">
+        <v>981</v>
+      </c>
+      <c r="D260" s="11" t="s">
         <v>982</v>
       </c>
-      <c r="D260" s="11" t="s">
-        <v>983</v>
-      </c>
       <c r="E260" s="11" t="s">
-        <v>980</v>
+        <v>961</v>
       </c>
       <c r="F260" s="11" t="s">
         <v>957</v>
@@ -11987,7 +11990,7 @@
         <v>9</v>
       </c>
       <c r="H260" s="11">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I260" s="11" t="s">
         <v>1</v>
@@ -11995,16 +11998,16 @@
     </row>
     <row r="261" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="13" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B261" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C261" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="D261" s="13" t="s">
         <v>985</v>
-      </c>
-      <c r="D261" s="13" t="s">
-        <v>986</v>
       </c>
       <c r="E261" s="13" t="s">
         <v>956</v>
@@ -12016,7 +12019,7 @@
         <v>9</v>
       </c>
       <c r="H261" s="13">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="I261" s="13" t="s">
         <v>1</v>
@@ -12024,19 +12027,19 @@
     </row>
     <row r="262" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="11" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C262" s="11" t="s">
+        <v>987</v>
+      </c>
+      <c r="D262" s="11" t="s">
         <v>988</v>
       </c>
-      <c r="D262" s="11" t="s">
-        <v>989</v>
-      </c>
       <c r="E262" s="11" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F262" s="11" t="s">
         <v>957</v>
@@ -12045,7 +12048,7 @@
         <v>9</v>
       </c>
       <c r="H262" s="11">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="I262" s="11" t="s">
         <v>1</v>
@@ -12053,19 +12056,19 @@
     </row>
     <row r="263" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="13" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B263" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C263" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="D263" s="13" t="s">
         <v>991</v>
       </c>
-      <c r="D263" s="13" t="s">
-        <v>992</v>
-      </c>
       <c r="E263" s="13" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F263" s="13" t="s">
         <v>957</v>
@@ -12074,7 +12077,7 @@
         <v>9</v>
       </c>
       <c r="H263" s="13">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="I263" s="13" t="s">
         <v>1</v>
@@ -12082,19 +12085,19 @@
     </row>
     <row r="264" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B264" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C264" s="11" t="s">
+        <v>993</v>
+      </c>
+      <c r="D264" s="11" t="s">
         <v>994</v>
       </c>
-      <c r="D264" s="11" t="s">
-        <v>983</v>
-      </c>
       <c r="E264" s="11" t="s">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="F264" s="11" t="s">
         <v>957</v>
@@ -12103,7 +12106,7 @@
         <v>9</v>
       </c>
       <c r="H264" s="11">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="I264" s="11" t="s">
         <v>1</v>
@@ -12132,7 +12135,7 @@
         <v>9</v>
       </c>
       <c r="H265" s="13">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="I265" s="13" t="s">
         <v>1</v>
@@ -12152,7 +12155,7 @@
         <v>1000</v>
       </c>
       <c r="E266" s="11" t="s">
-        <v>956</v>
+        <v>1001</v>
       </c>
       <c r="F266" s="11" t="s">
         <v>957</v>
@@ -12161,7 +12164,7 @@
         <v>9</v>
       </c>
       <c r="H266" s="11">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="I266" s="11" t="s">
         <v>1</v>
@@ -12169,19 +12172,19 @@
     </row>
     <row r="267" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="13" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B267" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C267" s="13" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D267" s="13" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="E267" s="13" t="s">
-        <v>980</v>
+        <v>961</v>
       </c>
       <c r="F267" s="13" t="s">
         <v>957</v>
@@ -12190,7 +12193,7 @@
         <v>9</v>
       </c>
       <c r="H267" s="13">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="I267" s="13" t="s">
         <v>1</v>
@@ -12198,28 +12201,28 @@
     </row>
     <row r="268" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="11" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C268" s="11" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="E268" s="11" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G268" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H268" s="11">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="I268" s="11" t="s">
         <v>1</v>
@@ -12227,28 +12230,28 @@
     </row>
     <row r="269" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="13" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B269" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C269" s="13" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D269" s="13" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E269" s="13" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F269" s="13" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G269" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H269" s="13">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="I269" s="13" t="s">
         <v>1</v>
@@ -12256,28 +12259,28 @@
     </row>
     <row r="270" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B270" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C270" s="11" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D270" s="11" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E270" s="11" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="G270" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H270" s="11">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I270" s="11" t="s">
         <v>1</v>
@@ -12285,28 +12288,28 @@
     </row>
     <row r="271" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="13" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B271" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C271" s="13" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D271" s="13" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="E271" s="13" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F271" s="13" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="G271" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H271" s="13">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="I271" s="13" t="s">
         <v>1</v>
@@ -12314,28 +12317,28 @@
     </row>
     <row r="272" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C272" s="11" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E272" s="11" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="G272" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H272" s="11">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I272" s="11" t="s">
         <v>1</v>
@@ -12343,28 +12346,28 @@
     </row>
     <row r="273" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="13" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B273" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C273" s="13" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D273" s="13" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="E273" s="13" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F273" s="13" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="G273" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H273" s="13">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="I273" s="13" t="s">
         <v>1</v>
@@ -12372,28 +12375,28 @@
     </row>
     <row r="274" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C274" s="11" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="E274" s="11" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="G274" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H274" s="11">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="I274" s="11" t="s">
         <v>1</v>
@@ -12401,28 +12404,28 @@
     </row>
     <row r="275" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="13" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B275" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C275" s="13" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D275" s="13" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E275" s="13" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F275" s="13" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G275" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H275" s="13">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I275" s="13" t="s">
         <v>1</v>
@@ -12430,19 +12433,19 @@
     </row>
     <row r="276" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="11" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C276" s="11" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D276" s="11" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E276" s="11" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F276" s="11" t="s">
         <v>48</v>
@@ -12451,7 +12454,7 @@
         <v>9</v>
       </c>
       <c r="H276" s="11">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="I276" s="11" t="s">
         <v>1</v>
@@ -12459,28 +12462,28 @@
     </row>
     <row r="277" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="13" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B277" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C277" s="13" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D277" s="13" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="E277" s="13" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F277" s="13" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G277" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H277" s="13">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="I277" s="13" t="s">
         <v>1</v>
@@ -12488,28 +12491,28 @@
     </row>
     <row r="278" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D278" s="11" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="E278" s="11" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G278" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H278" s="11">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="I278" s="11" t="s">
         <v>1</v>
@@ -12517,19 +12520,19 @@
     </row>
     <row r="279" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="13" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B279" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C279" s="13" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D279" s="13" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="E279" s="13" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F279" s="13" t="s">
         <v>863</v>
@@ -12538,7 +12541,7 @@
         <v>9</v>
       </c>
       <c r="H279" s="13">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="I279" s="13" t="s">
         <v>1</v>
@@ -12546,28 +12549,28 @@
     </row>
     <row r="280" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C280" s="11" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D280" s="11" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E280" s="11" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G280" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H280" s="11">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I280" s="11" t="s">
         <v>1</v>
@@ -12575,28 +12578,28 @@
     </row>
     <row r="281" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="13" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B281" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C281" s="13" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D281" s="13" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E281" s="13" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F281" s="13" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G281" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H281" s="13">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="I281" s="13" t="s">
         <v>1</v>
@@ -12604,28 +12607,28 @@
     </row>
     <row r="282" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="11" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C282" s="11" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D282" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E282" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G282" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H282" s="11">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="I282" s="11" t="s">
         <v>1</v>
@@ -12633,28 +12636,28 @@
     </row>
     <row r="283" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="13" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B283" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C283" s="13" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D283" s="13" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="E283" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F283" s="13" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G283" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H283" s="13">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I283" s="13" t="s">
         <v>1</v>
@@ -12662,28 +12665,28 @@
     </row>
     <row r="284" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C284" s="11" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E284" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G284" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H284" s="11">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="I284" s="11" t="s">
         <v>1</v>
@@ -12691,28 +12694,28 @@
     </row>
     <row r="285" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="13" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B285" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C285" s="13" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D285" s="13" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="E285" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F285" s="13" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G285" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H285" s="13">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I285" s="13" t="s">
         <v>1</v>
@@ -12720,28 +12723,28 @@
     </row>
     <row r="286" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C286" s="11" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E286" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G286" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H286" s="11">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="I286" s="11" t="s">
         <v>1</v>
@@ -12749,28 +12752,28 @@
     </row>
     <row r="287" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="13" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B287" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C287" s="13" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D287" s="13" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E287" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F287" s="13" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G287" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H287" s="13">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I287" s="13" t="s">
         <v>1</v>
@@ -12778,28 +12781,28 @@
     </row>
     <row r="288" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="11" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C288" s="11" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D288" s="11" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E288" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G288" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H288" s="11">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I288" s="11" t="s">
         <v>1</v>
@@ -12807,28 +12810,28 @@
     </row>
     <row r="289" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="13" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B289" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C289" s="13" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D289" s="13" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="E289" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F289" s="13" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G289" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H289" s="13">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="I289" s="13" t="s">
         <v>1</v>
@@ -12836,28 +12839,28 @@
     </row>
     <row r="290" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C290" s="11" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D290" s="11" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="E290" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G290" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H290" s="11">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="I290" s="11" t="s">
         <v>1</v>
@@ -12865,28 +12868,28 @@
     </row>
     <row r="291" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="13" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B291" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C291" s="13" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D291" s="13" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="E291" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F291" s="13" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G291" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H291" s="13">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="I291" s="13" t="s">
         <v>1</v>
@@ -12894,28 +12897,28 @@
     </row>
     <row r="292" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="11" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C292" s="11" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D292" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E292" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="G292" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H292" s="11">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="I292" s="11" t="s">
         <v>1</v>
@@ -12923,28 +12926,28 @@
     </row>
     <row r="293" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="13" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B293" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C293" s="13" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D293" s="13" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="E293" s="13" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F293" s="13" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="G293" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H293" s="13">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="I293" s="13" t="s">
         <v>1</v>
@@ -12952,28 +12955,28 @@
     </row>
     <row r="294" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="11" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B294" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C294" s="11" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D294" s="11" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="E294" s="11" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="G294" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H294" s="11">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I294" s="11" t="s">
         <v>1</v>
@@ -12981,28 +12984,28 @@
     </row>
     <row r="295" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="13" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B295" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C295" s="13" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D295" s="13" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="E295" s="13" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F295" s="13" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="G295" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H295" s="13">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I295" s="13" t="s">
         <v>1</v>
@@ -13010,28 +13013,28 @@
     </row>
     <row r="296" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="11" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D296" s="11" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="E296" s="11" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="G296" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H296" s="11">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="I296" s="11" t="s">
         <v>1</v>
@@ -13039,28 +13042,28 @@
     </row>
     <row r="297" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="13" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B297" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C297" s="13" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D297" s="13" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E297" s="13" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="F297" s="13" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G297" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H297" s="13">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="I297" s="13" t="s">
         <v>1</v>
@@ -13068,28 +13071,28 @@
     </row>
     <row r="298" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="11" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D298" s="11" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="E298" s="11" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="G298" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H298" s="11">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="I298" s="11" t="s">
         <v>1</v>
@@ -13097,28 +13100,28 @@
     </row>
     <row r="299" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="13" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B299" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C299" s="13" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D299" s="13" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="E299" s="13" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="F299" s="13" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="G299" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H299" s="13">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="I299" s="13" t="s">
         <v>1</v>
@@ -13126,28 +13129,28 @@
     </row>
     <row r="300" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>29</v>
       </c>
       <c r="C300" s="11" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D300" s="11" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="E300" s="11" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G300" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H300" s="11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I300" s="11" t="s">
         <v>1</v>
@@ -13155,28 +13158,28 @@
     </row>
     <row r="301" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="13" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B301" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C301" s="13" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D301" s="13" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="E301" s="13" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="F301" s="13" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="G301" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H301" s="13">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="I301" s="13" t="s">
         <v>1</v>

--- a/testing/appium-tests/Test_Report.xlsx
+++ b/testing/appium-tests/Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1145">
   <si>
     <t>GROWMARK MOBILE APP - AUTOMATED TESTING REPORT</t>
   </si>
@@ -1391,7 +1391,7 @@
     <t>TestCase_Sales_15: Submit random sales variation 15</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 120, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 126, Date: Today</t>
   </si>
   <si>
     <t>Sales record saved and threshold check triggered</t>
@@ -1406,7 +1406,7 @@
     <t>TestCase_Sales_16: Submit random sales variation 16</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 125, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 131, Date: Today</t>
   </si>
   <si>
     <t>TC111</t>
@@ -1415,7 +1415,7 @@
     <t>TestCase_Sales_17: Submit random sales variation 17</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 97, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 111, Date: Today</t>
   </si>
   <si>
     <t>TC112</t>
@@ -1424,7 +1424,7 @@
     <t>TestCase_Sales_18: Submit random sales variation 18</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 111, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 53, Date: Today</t>
   </si>
   <si>
     <t>TC113</t>
@@ -1433,7 +1433,7 @@
     <t>TestCase_Sales_19: Submit random sales variation 19</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 167, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 73, Date: Today</t>
   </si>
   <si>
     <t>TC114</t>
@@ -1442,7 +1442,7 @@
     <t>TestCase_Sales_20: Submit random sales variation 20</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 59, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 100, Date: Today</t>
   </si>
   <si>
     <t>TC115</t>
@@ -1451,7 +1451,7 @@
     <t>TestCase_Sales_21: Submit random sales variation 21</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 70, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 112, Date: Today</t>
   </si>
   <si>
     <t>TC116</t>
@@ -1460,7 +1460,7 @@
     <t>TestCase_Sales_22: Submit random sales variation 22</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 116, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 180, Date: Today</t>
   </si>
   <si>
     <t>TC117</t>
@@ -1469,7 +1469,7 @@
     <t>TestCase_Sales_23: Submit random sales variation 23</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 24, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 29, Date: Today</t>
   </si>
   <si>
     <t>TC118</t>
@@ -1478,7 +1478,7 @@
     <t>TestCase_Sales_24: Submit random sales variation 24</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 9, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 110, Date: Today</t>
   </si>
   <si>
     <t>TC119</t>
@@ -1487,7 +1487,7 @@
     <t>TestCase_Sales_25: Submit random sales variation 25</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 95, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 68, Date: Today</t>
   </si>
   <si>
     <t>TC120</t>
@@ -1496,7 +1496,7 @@
     <t>TestCase_Sales_26: Submit random sales variation 26</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 43, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 87, Date: Today</t>
   </si>
   <si>
     <t>TC121</t>
@@ -1505,7 +1505,7 @@
     <t>TestCase_Sales_27: Submit random sales variation 27</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 169, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 17, Date: Today</t>
   </si>
   <si>
     <t>TC122</t>
@@ -1514,7 +1514,7 @@
     <t>TestCase_Sales_28: Submit random sales variation 28</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 40, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 178, Date: Today</t>
   </si>
   <si>
     <t>TC123</t>
@@ -1523,7 +1523,7 @@
     <t>TestCase_Sales_29: Submit random sales variation 29</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 11, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 52, Date: Today</t>
   </si>
   <si>
     <t>TC124</t>
@@ -1532,7 +1532,7 @@
     <t>TestCase_Sales_30: Submit random sales variation 30</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 185, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 78, Date: Today</t>
   </si>
   <si>
     <t>TC125</t>
@@ -1541,7 +1541,7 @@
     <t>TestCase_Sales_31: Submit random sales variation 31</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 111, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 88, Date: Today</t>
   </si>
   <si>
     <t>TC126</t>
@@ -1550,7 +1550,7 @@
     <t>TestCase_Sales_32: Submit random sales variation 32</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 53, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 80, Date: Today</t>
   </si>
   <si>
     <t>TC127</t>
@@ -1559,7 +1559,7 @@
     <t>TestCase_Sales_33: Submit random sales variation 33</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 129, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 46, Date: Today</t>
   </si>
   <si>
     <t>TC128</t>
@@ -1568,7 +1568,7 @@
     <t>TestCase_Sales_34: Submit random sales variation 34</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 30, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 12, Date: Today</t>
   </si>
   <si>
     <t>TC129</t>
@@ -1577,7 +1577,7 @@
     <t>TestCase_Sales_35: Submit random sales variation 35</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 74, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 4, Date: Today</t>
   </si>
   <si>
     <t>TC130</t>
@@ -1586,7 +1586,7 @@
     <t>TestCase_Sales_36: Submit random sales variation 36</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 59, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 143, Date: Today</t>
   </si>
   <si>
     <t>TC131</t>
@@ -1595,7 +1595,7 @@
     <t>TestCase_Sales_37: Submit random sales variation 37</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 75, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 133, Date: Today</t>
   </si>
   <si>
     <t>TC132</t>
@@ -1604,7 +1604,7 @@
     <t>TestCase_Sales_38: Submit random sales variation 38</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 28, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 32, Date: Today</t>
   </si>
   <si>
     <t>TC133</t>
@@ -1613,7 +1613,7 @@
     <t>TestCase_Sales_39: Submit random sales variation 39</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 188, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 24, Date: Today</t>
   </si>
   <si>
     <t>TC134</t>
@@ -1622,7 +1622,7 @@
     <t>TestCase_Sales_40: Submit random sales variation 40</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 149, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 39, Date: Today</t>
   </si>
   <si>
     <t>TC135</t>
@@ -1631,7 +1631,7 @@
     <t>TestCase_Sales_41: Submit random sales variation 41</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 168, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 79, Date: Today</t>
   </si>
   <si>
     <t>TC136</t>
@@ -1640,7 +1640,7 @@
     <t>TestCase_Sales_42: Submit random sales variation 42</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 182, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 188, Date: Today</t>
   </si>
   <si>
     <t>TC137</t>
@@ -1649,7 +1649,7 @@
     <t>TestCase_Sales_43: Submit random sales variation 43</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 38, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 159, Date: Today</t>
   </si>
   <si>
     <t>TC138</t>
@@ -1658,7 +1658,7 @@
     <t>TestCase_Sales_44: Submit random sales variation 44</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 119, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 48, Date: Today</t>
   </si>
   <si>
     <t>TC139</t>
@@ -1667,7 +1667,7 @@
     <t>TestCase_Sales_45: Submit random sales variation 45</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 152, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 55, Date: Today</t>
   </si>
   <si>
     <t>TC140</t>
@@ -1676,7 +1676,7 @@
     <t>TestCase_Sales_46: Submit random sales variation 46</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 5, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 65, Date: Today</t>
   </si>
   <si>
     <t>TC141</t>
@@ -1685,7 +1685,7 @@
     <t>TestCase_Sales_47: Submit random sales variation 47</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 83, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 140, Date: Today</t>
   </si>
   <si>
     <t>TC142</t>
@@ -1694,7 +1694,7 @@
     <t>TestCase_Sales_48: Submit random sales variation 48</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 124, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 192, Date: Today</t>
   </si>
   <si>
     <t>TC143</t>
@@ -1703,7 +1703,7 @@
     <t>TestCase_Sales_49: Submit random sales variation 49</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 128, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 164, Date: Today</t>
   </si>
   <si>
     <t>TC144</t>
@@ -1712,7 +1712,7 @@
     <t>TestCase_Sales_50: Submit random sales variation 50</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 175, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 60, Date: Today</t>
   </si>
   <si>
     <t>TC145</t>
@@ -2876,157 +2876,151 @@
     <t>TC251</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_09: Score 65 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 65</t>
+    <t>TestCase_HealthScore_09: Score 21 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 21</t>
+  </si>
+  <si>
+    <t>Verdict: "Immediate Action Needed" displayed</t>
+  </si>
+  <si>
+    <t>Verdict matched expected business logic</t>
+  </si>
+  <si>
+    <t>TC252</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_10: Score 16 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 16</t>
+  </si>
+  <si>
+    <t>TC253</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_11: Score 94 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 94</t>
+  </si>
+  <si>
+    <t>Verdict: "Thriving" displayed</t>
+  </si>
+  <si>
+    <t>TC254</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_12: Score 54 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 54</t>
   </si>
   <si>
     <t>Verdict: "Work in Progress" displayed</t>
   </si>
   <si>
-    <t>Verdict matched expected business logic</t>
-  </si>
-  <si>
-    <t>TC252</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_10: Score 4 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 4</t>
-  </si>
-  <si>
-    <t>Verdict: "Immediate Action Needed" displayed</t>
-  </si>
-  <si>
-    <t>TC253</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_11: Score 46 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 46</t>
-  </si>
-  <si>
-    <t>TC254</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_12: Score 1 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 1</t>
-  </si>
-  <si>
     <t>TC255</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_13: Score 8 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 8</t>
+    <t>TestCase_HealthScore_13: Score 86 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 86</t>
   </si>
   <si>
     <t>TC256</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_14: Score 69 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 69</t>
+    <t>TestCase_HealthScore_14: Score 24 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 24</t>
   </si>
   <si>
     <t>TC257</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_15: Score 3 shows "Immediate Action Needed" verdict</t>
+    <t>TestCase_HealthScore_15: Score 72 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 72</t>
+  </si>
+  <si>
+    <t>TC258</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_16: Score 15 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 15</t>
+  </si>
+  <si>
+    <t>TC259</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_17: Score 16 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>TC260</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_18: Score 16 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>TC261</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_19: Score 81 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 81</t>
+  </si>
+  <si>
+    <t>TC262</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_20: Score 89 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 89</t>
+  </si>
+  <si>
+    <t>TC263</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_21: Score 3 shows "Immediate Action Needed" verdict</t>
   </si>
   <si>
     <t>Simulated score: 3</t>
   </si>
   <si>
-    <t>TC258</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_16: Score 16 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 16</t>
-  </si>
-  <si>
-    <t>TC259</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_17: Score 42 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 42</t>
-  </si>
-  <si>
-    <t>TC260</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_18: Score 73 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 73</t>
-  </si>
-  <si>
-    <t>TC261</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_19: Score 6 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 6</t>
-  </si>
-  <si>
-    <t>TC262</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_20: Score 27 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 27</t>
-  </si>
-  <si>
-    <t>TC263</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_21: Score 64 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 64</t>
-  </si>
-  <si>
     <t>TC264</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_22: Score 74 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 74</t>
+    <t>TestCase_HealthScore_22: Score 88 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 88</t>
   </si>
   <si>
     <t>TC265</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_23: Score 91 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 91</t>
-  </si>
-  <si>
-    <t>Verdict: "Thriving" displayed</t>
+    <t>TestCase_HealthScore_23: Score 5 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 5</t>
   </si>
   <si>
     <t>TC266</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_24: Score 39 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 39</t>
+    <t>TestCase_HealthScore_24: Score 37 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 37</t>
   </si>
   <si>
     <t>TC267</t>
@@ -4508,7 +4502,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="11">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>1</v>
@@ -4537,7 +4531,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="13">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>1</v>
@@ -4566,7 +4560,7 @@
         <v>9</v>
       </c>
       <c r="H4" s="11">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>1</v>
@@ -4595,7 +4589,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="13">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>1</v>
@@ -4624,7 +4618,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="11">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>1</v>
@@ -4653,7 +4647,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="13">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>1</v>
@@ -4682,7 +4676,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="11">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>1</v>
@@ -4711,7 +4705,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="13">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>1</v>
@@ -4740,7 +4734,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="11">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>1</v>
@@ -4769,7 +4763,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="13">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>1</v>
@@ -4798,7 +4792,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="11">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>1</v>
@@ -4827,7 +4821,7 @@
         <v>9</v>
       </c>
       <c r="H13" s="13">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>1</v>
@@ -4856,7 +4850,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="11">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>1</v>
@@ -4885,7 +4879,7 @@
         <v>9</v>
       </c>
       <c r="H15" s="13">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>1</v>
@@ -4914,7 +4908,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="11">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>1</v>
@@ -4943,7 +4937,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="13">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>1</v>
@@ -4972,7 +4966,7 @@
         <v>9</v>
       </c>
       <c r="H18" s="11">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>1</v>
@@ -5001,7 +4995,7 @@
         <v>9</v>
       </c>
       <c r="H19" s="13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>1</v>
@@ -5030,7 +5024,7 @@
         <v>9</v>
       </c>
       <c r="H20" s="11">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>1</v>
@@ -5059,7 +5053,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="13">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>1</v>
@@ -5088,7 +5082,7 @@
         <v>9</v>
       </c>
       <c r="H22" s="11">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>1</v>
@@ -5117,7 +5111,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="13">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>1</v>
@@ -5146,7 +5140,7 @@
         <v>9</v>
       </c>
       <c r="H24" s="11">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>1</v>
@@ -5175,7 +5169,7 @@
         <v>9</v>
       </c>
       <c r="H25" s="13">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>1</v>
@@ -5204,7 +5198,7 @@
         <v>9</v>
       </c>
       <c r="H26" s="11">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>1</v>
@@ -5233,7 +5227,7 @@
         <v>9</v>
       </c>
       <c r="H27" s="13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>1</v>
@@ -5262,7 +5256,7 @@
         <v>9</v>
       </c>
       <c r="H28" s="11">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>1</v>
@@ -5291,7 +5285,7 @@
         <v>9</v>
       </c>
       <c r="H29" s="13">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>1</v>
@@ -5320,7 +5314,7 @@
         <v>9</v>
       </c>
       <c r="H30" s="11">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>1</v>
@@ -5349,7 +5343,7 @@
         <v>9</v>
       </c>
       <c r="H31" s="13">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>1</v>
@@ -5378,7 +5372,7 @@
         <v>9</v>
       </c>
       <c r="H32" s="11">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>1</v>
@@ -5407,7 +5401,7 @@
         <v>9</v>
       </c>
       <c r="H33" s="13">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>1</v>
@@ -5436,7 +5430,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="11">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>1</v>
@@ -5465,7 +5459,7 @@
         <v>9</v>
       </c>
       <c r="H35" s="13">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I35" s="13" t="s">
         <v>1</v>
@@ -5494,7 +5488,7 @@
         <v>9</v>
       </c>
       <c r="H36" s="11">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>1</v>
@@ -5523,7 +5517,7 @@
         <v>9</v>
       </c>
       <c r="H37" s="13">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>1</v>
@@ -5552,7 +5546,7 @@
         <v>9</v>
       </c>
       <c r="H38" s="11">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>1</v>
@@ -5610,7 +5604,7 @@
         <v>9</v>
       </c>
       <c r="H40" s="11">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>1</v>
@@ -5639,7 +5633,7 @@
         <v>9</v>
       </c>
       <c r="H41" s="13">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>1</v>
@@ -5668,7 +5662,7 @@
         <v>9</v>
       </c>
       <c r="H42" s="11">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>1</v>
@@ -5697,7 +5691,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="13">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>1</v>
@@ -5726,7 +5720,7 @@
         <v>9</v>
       </c>
       <c r="H44" s="11">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>1</v>
@@ -5755,7 +5749,7 @@
         <v>9</v>
       </c>
       <c r="H45" s="13">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>1</v>
@@ -5784,7 +5778,7 @@
         <v>9</v>
       </c>
       <c r="H46" s="11">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>1</v>
@@ -5813,7 +5807,7 @@
         <v>9</v>
       </c>
       <c r="H47" s="13">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>1</v>
@@ -5842,7 +5836,7 @@
         <v>9</v>
       </c>
       <c r="H48" s="11">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>1</v>
@@ -5871,7 +5865,7 @@
         <v>9</v>
       </c>
       <c r="H49" s="13">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>1</v>
@@ -5900,7 +5894,7 @@
         <v>9</v>
       </c>
       <c r="H50" s="11">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>1</v>
@@ -5929,7 +5923,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="13">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>1</v>
@@ -5958,7 +5952,7 @@
         <v>9</v>
       </c>
       <c r="H52" s="11">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>1</v>
@@ -5987,7 +5981,7 @@
         <v>9</v>
       </c>
       <c r="H53" s="13">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>1</v>
@@ -6016,7 +6010,7 @@
         <v>9</v>
       </c>
       <c r="H54" s="11">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>1</v>
@@ -6045,7 +6039,7 @@
         <v>9</v>
       </c>
       <c r="H55" s="13">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>1</v>
@@ -6074,7 +6068,7 @@
         <v>9</v>
       </c>
       <c r="H56" s="11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>1</v>
@@ -6103,7 +6097,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="13">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>1</v>
@@ -6132,7 +6126,7 @@
         <v>9</v>
       </c>
       <c r="H58" s="11">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>1</v>
@@ -6161,7 +6155,7 @@
         <v>9</v>
       </c>
       <c r="H59" s="13">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>1</v>
@@ -6190,7 +6184,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="11">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>1</v>
@@ -6219,7 +6213,7 @@
         <v>9</v>
       </c>
       <c r="H61" s="13">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>1</v>
@@ -6248,7 +6242,7 @@
         <v>9</v>
       </c>
       <c r="H62" s="11">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>1</v>
@@ -6277,7 +6271,7 @@
         <v>9</v>
       </c>
       <c r="H63" s="13">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>1</v>
@@ -6306,7 +6300,7 @@
         <v>9</v>
       </c>
       <c r="H64" s="11">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>1</v>
@@ -6335,7 +6329,7 @@
         <v>9</v>
       </c>
       <c r="H65" s="13">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>1</v>
@@ -6364,7 +6358,7 @@
         <v>9</v>
       </c>
       <c r="H66" s="11">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>1</v>
@@ -6393,7 +6387,7 @@
         <v>9</v>
       </c>
       <c r="H67" s="13">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>1</v>
@@ -6422,7 +6416,7 @@
         <v>9</v>
       </c>
       <c r="H68" s="11">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>1</v>
@@ -6451,7 +6445,7 @@
         <v>9</v>
       </c>
       <c r="H69" s="13">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>1</v>
@@ -6480,7 +6474,7 @@
         <v>9</v>
       </c>
       <c r="H70" s="11">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>1</v>
@@ -6509,7 +6503,7 @@
         <v>9</v>
       </c>
       <c r="H71" s="13">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>1</v>
@@ -6538,7 +6532,7 @@
         <v>9</v>
       </c>
       <c r="H72" s="11">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>1</v>
@@ -6567,7 +6561,7 @@
         <v>9</v>
       </c>
       <c r="H73" s="13">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>1</v>
@@ -6596,7 +6590,7 @@
         <v>9</v>
       </c>
       <c r="H74" s="11">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>1</v>
@@ -6625,7 +6619,7 @@
         <v>9</v>
       </c>
       <c r="H75" s="13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>1</v>
@@ -6654,7 +6648,7 @@
         <v>9</v>
       </c>
       <c r="H76" s="11">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>1</v>
@@ -6683,7 +6677,7 @@
         <v>9</v>
       </c>
       <c r="H77" s="13">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>1</v>
@@ -6712,7 +6706,7 @@
         <v>9</v>
       </c>
       <c r="H78" s="11">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>1</v>
@@ -6741,7 +6735,7 @@
         <v>9</v>
       </c>
       <c r="H79" s="13">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>1</v>
@@ -6770,7 +6764,7 @@
         <v>9</v>
       </c>
       <c r="H80" s="11">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>1</v>
@@ -6799,7 +6793,7 @@
         <v>9</v>
       </c>
       <c r="H81" s="13">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="I81" s="13" t="s">
         <v>1</v>
@@ -6828,7 +6822,7 @@
         <v>9</v>
       </c>
       <c r="H82" s="11">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>1</v>
@@ -6857,7 +6851,7 @@
         <v>9</v>
       </c>
       <c r="H83" s="13">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I83" s="13" t="s">
         <v>1</v>
@@ -6886,7 +6880,7 @@
         <v>9</v>
       </c>
       <c r="H84" s="11">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>1</v>
@@ -6915,7 +6909,7 @@
         <v>9</v>
       </c>
       <c r="H85" s="13">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>1</v>
@@ -6944,7 +6938,7 @@
         <v>9</v>
       </c>
       <c r="H86" s="11">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>1</v>
@@ -6973,7 +6967,7 @@
         <v>9</v>
       </c>
       <c r="H87" s="13">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>1</v>
@@ -7002,7 +6996,7 @@
         <v>9</v>
       </c>
       <c r="H88" s="11">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>1</v>
@@ -7031,7 +7025,7 @@
         <v>9</v>
       </c>
       <c r="H89" s="13">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="I89" s="13" t="s">
         <v>1</v>
@@ -7060,7 +7054,7 @@
         <v>9</v>
       </c>
       <c r="H90" s="11">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I90" s="11" t="s">
         <v>1</v>
@@ -7089,7 +7083,7 @@
         <v>9</v>
       </c>
       <c r="H91" s="13">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I91" s="13" t="s">
         <v>1</v>
@@ -7118,7 +7112,7 @@
         <v>9</v>
       </c>
       <c r="H92" s="11">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="I92" s="11" t="s">
         <v>1</v>
@@ -7147,7 +7141,7 @@
         <v>9</v>
       </c>
       <c r="H93" s="13">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="I93" s="13" t="s">
         <v>1</v>
@@ -7176,7 +7170,7 @@
         <v>9</v>
       </c>
       <c r="H94" s="11">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>1</v>
@@ -7205,7 +7199,7 @@
         <v>9</v>
       </c>
       <c r="H95" s="13">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="I95" s="13" t="s">
         <v>1</v>
@@ -7234,7 +7228,7 @@
         <v>9</v>
       </c>
       <c r="H96" s="11">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>1</v>
@@ -7263,7 +7257,7 @@
         <v>9</v>
       </c>
       <c r="H97" s="13">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="I97" s="13" t="s">
         <v>1</v>
@@ -7292,7 +7286,7 @@
         <v>9</v>
       </c>
       <c r="H98" s="11">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>1</v>
@@ -7321,7 +7315,7 @@
         <v>9</v>
       </c>
       <c r="H99" s="13">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="I99" s="13" t="s">
         <v>1</v>
@@ -7350,7 +7344,7 @@
         <v>9</v>
       </c>
       <c r="H100" s="11">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>1</v>
@@ -7379,7 +7373,7 @@
         <v>9</v>
       </c>
       <c r="H101" s="13">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I101" s="13" t="s">
         <v>1</v>
@@ -7408,7 +7402,7 @@
         <v>9</v>
       </c>
       <c r="H102" s="11">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>1</v>
@@ -7437,7 +7431,7 @@
         <v>9</v>
       </c>
       <c r="H103" s="13">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="I103" s="13" t="s">
         <v>1</v>
@@ -7466,7 +7460,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="11">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>1</v>
@@ -7495,7 +7489,7 @@
         <v>9</v>
       </c>
       <c r="H105" s="13">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="I105" s="13" t="s">
         <v>1</v>
@@ -7524,7 +7518,7 @@
         <v>9</v>
       </c>
       <c r="H106" s="11">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>1</v>
@@ -7553,7 +7547,7 @@
         <v>9</v>
       </c>
       <c r="H107" s="13">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="I107" s="13" t="s">
         <v>1</v>
@@ -7611,7 +7605,7 @@
         <v>9</v>
       </c>
       <c r="H109" s="13">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I109" s="13" t="s">
         <v>1</v>
@@ -7640,7 +7634,7 @@
         <v>9</v>
       </c>
       <c r="H110" s="11">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>1</v>
@@ -7669,7 +7663,7 @@
         <v>9</v>
       </c>
       <c r="H111" s="13">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I111" s="13" t="s">
         <v>1</v>
@@ -7698,7 +7692,7 @@
         <v>9</v>
       </c>
       <c r="H112" s="11">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="I112" s="11" t="s">
         <v>1</v>
@@ -7727,7 +7721,7 @@
         <v>9</v>
       </c>
       <c r="H113" s="13">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="I113" s="13" t="s">
         <v>1</v>
@@ -7756,7 +7750,7 @@
         <v>9</v>
       </c>
       <c r="H114" s="11">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="I114" s="11" t="s">
         <v>1</v>
@@ -7785,7 +7779,7 @@
         <v>9</v>
       </c>
       <c r="H115" s="13">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I115" s="13" t="s">
         <v>1</v>
@@ -7814,7 +7808,7 @@
         <v>9</v>
       </c>
       <c r="H116" s="11">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="I116" s="11" t="s">
         <v>1</v>
@@ -7843,7 +7837,7 @@
         <v>9</v>
       </c>
       <c r="H117" s="13">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="I117" s="13" t="s">
         <v>1</v>
@@ -7872,7 +7866,7 @@
         <v>9</v>
       </c>
       <c r="H118" s="11">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>1</v>
@@ -7901,7 +7895,7 @@
         <v>9</v>
       </c>
       <c r="H119" s="13">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I119" s="13" t="s">
         <v>1</v>
@@ -7930,7 +7924,7 @@
         <v>9</v>
       </c>
       <c r="H120" s="11">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>1</v>
@@ -7959,7 +7953,7 @@
         <v>9</v>
       </c>
       <c r="H121" s="13">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>1</v>
@@ -7988,7 +7982,7 @@
         <v>9</v>
       </c>
       <c r="H122" s="11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I122" s="11" t="s">
         <v>1</v>
@@ -8017,7 +8011,7 @@
         <v>9</v>
       </c>
       <c r="H123" s="13">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>1</v>
@@ -8046,7 +8040,7 @@
         <v>9</v>
       </c>
       <c r="H124" s="11">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="I124" s="11" t="s">
         <v>1</v>
@@ -8075,7 +8069,7 @@
         <v>9</v>
       </c>
       <c r="H125" s="13">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>1</v>
@@ -8104,7 +8098,7 @@
         <v>9</v>
       </c>
       <c r="H126" s="11">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I126" s="11" t="s">
         <v>1</v>
@@ -8133,7 +8127,7 @@
         <v>9</v>
       </c>
       <c r="H127" s="13">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>1</v>
@@ -8162,7 +8156,7 @@
         <v>9</v>
       </c>
       <c r="H128" s="11">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>1</v>
@@ -8191,7 +8185,7 @@
         <v>9</v>
       </c>
       <c r="H129" s="13">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>1</v>
@@ -8220,7 +8214,7 @@
         <v>9</v>
       </c>
       <c r="H130" s="11">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I130" s="11" t="s">
         <v>1</v>
@@ -8249,7 +8243,7 @@
         <v>9</v>
       </c>
       <c r="H131" s="13">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>1</v>
@@ -8278,7 +8272,7 @@
         <v>9</v>
       </c>
       <c r="H132" s="11">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="I132" s="11" t="s">
         <v>1</v>
@@ -8307,7 +8301,7 @@
         <v>9</v>
       </c>
       <c r="H133" s="13">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>1</v>
@@ -8336,7 +8330,7 @@
         <v>9</v>
       </c>
       <c r="H134" s="11">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I134" s="11" t="s">
         <v>1</v>
@@ -8365,7 +8359,7 @@
         <v>9</v>
       </c>
       <c r="H135" s="13">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>1</v>
@@ -8394,7 +8388,7 @@
         <v>9</v>
       </c>
       <c r="H136" s="11">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="I136" s="11" t="s">
         <v>1</v>
@@ -8452,7 +8446,7 @@
         <v>9</v>
       </c>
       <c r="H138" s="11">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="I138" s="11" t="s">
         <v>1</v>
@@ -8481,7 +8475,7 @@
         <v>9</v>
       </c>
       <c r="H139" s="13">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I139" s="13" t="s">
         <v>1</v>
@@ -8510,7 +8504,7 @@
         <v>9</v>
       </c>
       <c r="H140" s="11">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="I140" s="11" t="s">
         <v>1</v>
@@ -8539,7 +8533,7 @@
         <v>9</v>
       </c>
       <c r="H141" s="13">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="I141" s="13" t="s">
         <v>1</v>
@@ -8597,7 +8591,7 @@
         <v>9</v>
       </c>
       <c r="H143" s="13">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>1</v>
@@ -8626,7 +8620,7 @@
         <v>9</v>
       </c>
       <c r="H144" s="11">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I144" s="11" t="s">
         <v>1</v>
@@ -8655,7 +8649,7 @@
         <v>9</v>
       </c>
       <c r="H145" s="13">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I145" s="13" t="s">
         <v>1</v>
@@ -8684,7 +8678,7 @@
         <v>9</v>
       </c>
       <c r="H146" s="11">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="I146" s="11" t="s">
         <v>1</v>
@@ -8713,7 +8707,7 @@
         <v>9</v>
       </c>
       <c r="H147" s="13">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I147" s="13" t="s">
         <v>1</v>
@@ -8742,7 +8736,7 @@
         <v>9</v>
       </c>
       <c r="H148" s="11">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I148" s="11" t="s">
         <v>1</v>
@@ -8771,7 +8765,7 @@
         <v>9</v>
       </c>
       <c r="H149" s="13">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="I149" s="13" t="s">
         <v>1</v>
@@ -8800,7 +8794,7 @@
         <v>9</v>
       </c>
       <c r="H150" s="11">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="I150" s="11" t="s">
         <v>1</v>
@@ -8829,7 +8823,7 @@
         <v>9</v>
       </c>
       <c r="H151" s="13">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="I151" s="13" t="s">
         <v>1</v>
@@ -8858,7 +8852,7 @@
         <v>9</v>
       </c>
       <c r="H152" s="11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I152" s="11" t="s">
         <v>1</v>
@@ -8887,7 +8881,7 @@
         <v>9</v>
       </c>
       <c r="H153" s="13">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I153" s="13" t="s">
         <v>1</v>
@@ -8916,7 +8910,7 @@
         <v>9</v>
       </c>
       <c r="H154" s="11">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="I154" s="11" t="s">
         <v>1</v>
@@ -8945,7 +8939,7 @@
         <v>9</v>
       </c>
       <c r="H155" s="13">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I155" s="13" t="s">
         <v>1</v>
@@ -8974,7 +8968,7 @@
         <v>9</v>
       </c>
       <c r="H156" s="11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I156" s="11" t="s">
         <v>1</v>
@@ -9003,7 +8997,7 @@
         <v>9</v>
       </c>
       <c r="H157" s="13">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>1</v>
@@ -9032,7 +9026,7 @@
         <v>9</v>
       </c>
       <c r="H158" s="11">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="I158" s="11" t="s">
         <v>1</v>
@@ -9061,7 +9055,7 @@
         <v>9</v>
       </c>
       <c r="H159" s="13">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="I159" s="13" t="s">
         <v>1</v>
@@ -9090,7 +9084,7 @@
         <v>9</v>
       </c>
       <c r="H160" s="11">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="I160" s="11" t="s">
         <v>1</v>
@@ -9119,7 +9113,7 @@
         <v>9</v>
       </c>
       <c r="H161" s="13">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="I161" s="13" t="s">
         <v>1</v>
@@ -9148,7 +9142,7 @@
         <v>9</v>
       </c>
       <c r="H162" s="11">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="I162" s="11" t="s">
         <v>1</v>
@@ -9177,7 +9171,7 @@
         <v>9</v>
       </c>
       <c r="H163" s="13">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>1</v>
@@ -9206,7 +9200,7 @@
         <v>9</v>
       </c>
       <c r="H164" s="11">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I164" s="11" t="s">
         <v>1</v>
@@ -9235,7 +9229,7 @@
         <v>9</v>
       </c>
       <c r="H165" s="13">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I165" s="13" t="s">
         <v>1</v>
@@ -9264,7 +9258,7 @@
         <v>9</v>
       </c>
       <c r="H166" s="11">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I166" s="11" t="s">
         <v>1</v>
@@ -9293,7 +9287,7 @@
         <v>9</v>
       </c>
       <c r="H167" s="13">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I167" s="13" t="s">
         <v>1</v>
@@ -9322,7 +9316,7 @@
         <v>9</v>
       </c>
       <c r="H168" s="11">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="I168" s="11" t="s">
         <v>1</v>
@@ -9351,7 +9345,7 @@
         <v>9</v>
       </c>
       <c r="H169" s="13">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="I169" s="13" t="s">
         <v>1</v>
@@ -9380,7 +9374,7 @@
         <v>9</v>
       </c>
       <c r="H170" s="11">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="I170" s="11" t="s">
         <v>1</v>
@@ -9409,7 +9403,7 @@
         <v>9</v>
       </c>
       <c r="H171" s="13">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I171" s="13" t="s">
         <v>1</v>
@@ -9438,7 +9432,7 @@
         <v>9</v>
       </c>
       <c r="H172" s="11">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="I172" s="11" t="s">
         <v>1</v>
@@ -9467,7 +9461,7 @@
         <v>9</v>
       </c>
       <c r="H173" s="13">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I173" s="13" t="s">
         <v>1</v>
@@ -9496,7 +9490,7 @@
         <v>9</v>
       </c>
       <c r="H174" s="11">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="I174" s="11" t="s">
         <v>1</v>
@@ -9525,7 +9519,7 @@
         <v>9</v>
       </c>
       <c r="H175" s="13">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="I175" s="13" t="s">
         <v>1</v>
@@ -9554,7 +9548,7 @@
         <v>9</v>
       </c>
       <c r="H176" s="11">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="I176" s="11" t="s">
         <v>1</v>
@@ -9583,7 +9577,7 @@
         <v>9</v>
       </c>
       <c r="H177" s="13">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="I177" s="13" t="s">
         <v>1</v>
@@ -9612,7 +9606,7 @@
         <v>9</v>
       </c>
       <c r="H178" s="11">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I178" s="11" t="s">
         <v>1</v>
@@ -9641,7 +9635,7 @@
         <v>9</v>
       </c>
       <c r="H179" s="13">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="I179" s="13" t="s">
         <v>1</v>
@@ -9670,7 +9664,7 @@
         <v>9</v>
       </c>
       <c r="H180" s="11">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="I180" s="11" t="s">
         <v>1</v>
@@ -9699,7 +9693,7 @@
         <v>9</v>
       </c>
       <c r="H181" s="13">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="I181" s="13" t="s">
         <v>1</v>
@@ -9728,7 +9722,7 @@
         <v>9</v>
       </c>
       <c r="H182" s="11">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="I182" s="11" t="s">
         <v>1</v>
@@ -9757,7 +9751,7 @@
         <v>9</v>
       </c>
       <c r="H183" s="13">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I183" s="13" t="s">
         <v>1</v>
@@ -9786,7 +9780,7 @@
         <v>9</v>
       </c>
       <c r="H184" s="11">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="I184" s="11" t="s">
         <v>1</v>
@@ -9815,7 +9809,7 @@
         <v>9</v>
       </c>
       <c r="H185" s="13">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I185" s="13" t="s">
         <v>1</v>
@@ -9844,7 +9838,7 @@
         <v>9</v>
       </c>
       <c r="H186" s="11">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I186" s="11" t="s">
         <v>1</v>
@@ -9873,7 +9867,7 @@
         <v>9</v>
       </c>
       <c r="H187" s="13">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I187" s="13" t="s">
         <v>1</v>
@@ -9902,7 +9896,7 @@
         <v>9</v>
       </c>
       <c r="H188" s="11">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I188" s="11" t="s">
         <v>1</v>
@@ -9931,7 +9925,7 @@
         <v>9</v>
       </c>
       <c r="H189" s="13">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I189" s="13" t="s">
         <v>1</v>
@@ -9960,7 +9954,7 @@
         <v>9</v>
       </c>
       <c r="H190" s="11">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I190" s="11" t="s">
         <v>1</v>
@@ -9989,7 +9983,7 @@
         <v>9</v>
       </c>
       <c r="H191" s="13">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="I191" s="13" t="s">
         <v>1</v>
@@ -10018,7 +10012,7 @@
         <v>9</v>
       </c>
       <c r="H192" s="11">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I192" s="11" t="s">
         <v>1</v>
@@ -10047,7 +10041,7 @@
         <v>9</v>
       </c>
       <c r="H193" s="13">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="I193" s="13" t="s">
         <v>1</v>
@@ -10076,7 +10070,7 @@
         <v>9</v>
       </c>
       <c r="H194" s="11">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I194" s="11" t="s">
         <v>1</v>
@@ -10105,7 +10099,7 @@
         <v>9</v>
       </c>
       <c r="H195" s="13">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>1</v>
@@ -10134,7 +10128,7 @@
         <v>9</v>
       </c>
       <c r="H196" s="11">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I196" s="11" t="s">
         <v>1</v>
@@ -10163,7 +10157,7 @@
         <v>9</v>
       </c>
       <c r="H197" s="13">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>1</v>
@@ -10192,7 +10186,7 @@
         <v>9</v>
       </c>
       <c r="H198" s="11">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="I198" s="11" t="s">
         <v>1</v>
@@ -10221,7 +10215,7 @@
         <v>9</v>
       </c>
       <c r="H199" s="13">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="I199" s="13" t="s">
         <v>1</v>
@@ -10250,7 +10244,7 @@
         <v>9</v>
       </c>
       <c r="H200" s="11">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="I200" s="11" t="s">
         <v>1</v>
@@ -10279,7 +10273,7 @@
         <v>9</v>
       </c>
       <c r="H201" s="13">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I201" s="13" t="s">
         <v>1</v>
@@ -10308,7 +10302,7 @@
         <v>9</v>
       </c>
       <c r="H202" s="11">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I202" s="11" t="s">
         <v>1</v>
@@ -10337,7 +10331,7 @@
         <v>9</v>
       </c>
       <c r="H203" s="13">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I203" s="13" t="s">
         <v>1</v>
@@ -10366,7 +10360,7 @@
         <v>9</v>
       </c>
       <c r="H204" s="11">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="I204" s="11" t="s">
         <v>1</v>
@@ -10395,7 +10389,7 @@
         <v>9</v>
       </c>
       <c r="H205" s="13">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I205" s="13" t="s">
         <v>1</v>
@@ -10424,7 +10418,7 @@
         <v>9</v>
       </c>
       <c r="H206" s="11">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="I206" s="11" t="s">
         <v>1</v>
@@ -10453,7 +10447,7 @@
         <v>9</v>
       </c>
       <c r="H207" s="13">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I207" s="13" t="s">
         <v>1</v>
@@ -10482,7 +10476,7 @@
         <v>9</v>
       </c>
       <c r="H208" s="11">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="I208" s="11" t="s">
         <v>1</v>
@@ -10511,7 +10505,7 @@
         <v>9</v>
       </c>
       <c r="H209" s="13">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I209" s="13" t="s">
         <v>1</v>
@@ -10540,7 +10534,7 @@
         <v>9</v>
       </c>
       <c r="H210" s="11">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="I210" s="11" t="s">
         <v>1</v>
@@ -10569,7 +10563,7 @@
         <v>9</v>
       </c>
       <c r="H211" s="13">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="I211" s="13" t="s">
         <v>1</v>
@@ -10598,7 +10592,7 @@
         <v>9</v>
       </c>
       <c r="H212" s="11">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="I212" s="11" t="s">
         <v>1</v>
@@ -10627,7 +10621,7 @@
         <v>9</v>
       </c>
       <c r="H213" s="13">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="I213" s="13" t="s">
         <v>1</v>
@@ -10656,7 +10650,7 @@
         <v>9</v>
       </c>
       <c r="H214" s="11">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I214" s="11" t="s">
         <v>1</v>
@@ -10685,7 +10679,7 @@
         <v>9</v>
       </c>
       <c r="H215" s="13">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I215" s="13" t="s">
         <v>1</v>
@@ -10714,7 +10708,7 @@
         <v>9</v>
       </c>
       <c r="H216" s="11">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="I216" s="11" t="s">
         <v>1</v>
@@ -10743,7 +10737,7 @@
         <v>9</v>
       </c>
       <c r="H217" s="13">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I217" s="13" t="s">
         <v>1</v>
@@ -10772,7 +10766,7 @@
         <v>9</v>
       </c>
       <c r="H218" s="11">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I218" s="11" t="s">
         <v>1</v>
@@ -10801,7 +10795,7 @@
         <v>9</v>
       </c>
       <c r="H219" s="13">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="I219" s="13" t="s">
         <v>1</v>
@@ -10830,7 +10824,7 @@
         <v>9</v>
       </c>
       <c r="H220" s="11">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="I220" s="11" t="s">
         <v>1</v>
@@ -10859,7 +10853,7 @@
         <v>9</v>
       </c>
       <c r="H221" s="13">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I221" s="13" t="s">
         <v>1</v>
@@ -10888,7 +10882,7 @@
         <v>9</v>
       </c>
       <c r="H222" s="11">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="I222" s="11" t="s">
         <v>1</v>
@@ -10917,7 +10911,7 @@
         <v>9</v>
       </c>
       <c r="H223" s="13">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="I223" s="13" t="s">
         <v>1</v>
@@ -10946,7 +10940,7 @@
         <v>9</v>
       </c>
       <c r="H224" s="11">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="I224" s="11" t="s">
         <v>1</v>
@@ -10975,7 +10969,7 @@
         <v>9</v>
       </c>
       <c r="H225" s="13">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="I225" s="13" t="s">
         <v>1</v>
@@ -11004,7 +10998,7 @@
         <v>9</v>
       </c>
       <c r="H226" s="11">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I226" s="11" t="s">
         <v>1</v>
@@ -11033,7 +11027,7 @@
         <v>9</v>
       </c>
       <c r="H227" s="13">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="I227" s="13" t="s">
         <v>1</v>
@@ -11062,7 +11056,7 @@
         <v>9</v>
       </c>
       <c r="H228" s="11">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="I228" s="11" t="s">
         <v>1</v>
@@ -11091,7 +11085,7 @@
         <v>9</v>
       </c>
       <c r="H229" s="13">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="I229" s="13" t="s">
         <v>1</v>
@@ -11120,7 +11114,7 @@
         <v>9</v>
       </c>
       <c r="H230" s="11">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="I230" s="11" t="s">
         <v>1</v>
@@ -11149,7 +11143,7 @@
         <v>9</v>
       </c>
       <c r="H231" s="13">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I231" s="13" t="s">
         <v>1</v>
@@ -11178,7 +11172,7 @@
         <v>9</v>
       </c>
       <c r="H232" s="11">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I232" s="11" t="s">
         <v>1</v>
@@ -11207,7 +11201,7 @@
         <v>9</v>
       </c>
       <c r="H233" s="13">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I233" s="13" t="s">
         <v>1</v>
@@ -11236,7 +11230,7 @@
         <v>9</v>
       </c>
       <c r="H234" s="11">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I234" s="11" t="s">
         <v>1</v>
@@ -11265,7 +11259,7 @@
         <v>9</v>
       </c>
       <c r="H235" s="13">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I235" s="13" t="s">
         <v>1</v>
@@ -11294,7 +11288,7 @@
         <v>9</v>
       </c>
       <c r="H236" s="11">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="I236" s="11" t="s">
         <v>1</v>
@@ -11323,7 +11317,7 @@
         <v>9</v>
       </c>
       <c r="H237" s="13">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="I237" s="13" t="s">
         <v>1</v>
@@ -11352,7 +11346,7 @@
         <v>9</v>
       </c>
       <c r="H238" s="11">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>1</v>
@@ -11381,7 +11375,7 @@
         <v>9</v>
       </c>
       <c r="H239" s="13">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="I239" s="13" t="s">
         <v>1</v>
@@ -11410,7 +11404,7 @@
         <v>9</v>
       </c>
       <c r="H240" s="11">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>1</v>
@@ -11439,7 +11433,7 @@
         <v>9</v>
       </c>
       <c r="H241" s="13">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="I241" s="13" t="s">
         <v>1</v>
@@ -11468,7 +11462,7 @@
         <v>9</v>
       </c>
       <c r="H242" s="11">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="I242" s="11" t="s">
         <v>1</v>
@@ -11497,7 +11491,7 @@
         <v>9</v>
       </c>
       <c r="H243" s="13">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I243" s="13" t="s">
         <v>1</v>
@@ -11526,7 +11520,7 @@
         <v>9</v>
       </c>
       <c r="H244" s="11">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="I244" s="11" t="s">
         <v>1</v>
@@ -11555,7 +11549,7 @@
         <v>9</v>
       </c>
       <c r="H245" s="13">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="I245" s="13" t="s">
         <v>1</v>
@@ -11584,7 +11578,7 @@
         <v>9</v>
       </c>
       <c r="H246" s="11">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="I246" s="11" t="s">
         <v>1</v>
@@ -11613,7 +11607,7 @@
         <v>9</v>
       </c>
       <c r="H247" s="13">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I247" s="13" t="s">
         <v>1</v>
@@ -11642,7 +11636,7 @@
         <v>9</v>
       </c>
       <c r="H248" s="11">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I248" s="11" t="s">
         <v>1</v>
@@ -11671,7 +11665,7 @@
         <v>9</v>
       </c>
       <c r="H249" s="13">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="I249" s="13" t="s">
         <v>1</v>
@@ -11700,7 +11694,7 @@
         <v>9</v>
       </c>
       <c r="H250" s="11">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="I250" s="11" t="s">
         <v>1</v>
@@ -11729,7 +11723,7 @@
         <v>9</v>
       </c>
       <c r="H251" s="13">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="I251" s="13" t="s">
         <v>1</v>
@@ -11758,7 +11752,7 @@
         <v>9</v>
       </c>
       <c r="H252" s="11">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I252" s="11" t="s">
         <v>1</v>
@@ -11778,7 +11772,7 @@
         <v>960</v>
       </c>
       <c r="E253" s="13" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="F253" s="13" t="s">
         <v>957</v>
@@ -11787,7 +11781,7 @@
         <v>9</v>
       </c>
       <c r="H253" s="13">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="I253" s="13" t="s">
         <v>1</v>
@@ -11795,19 +11789,19 @@
     </row>
     <row r="254" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B254" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C254" s="11" t="s">
+        <v>962</v>
+      </c>
+      <c r="D254" s="11" t="s">
         <v>963</v>
       </c>
-      <c r="D254" s="11" t="s">
+      <c r="E254" s="11" t="s">
         <v>964</v>
-      </c>
-      <c r="E254" s="11" t="s">
-        <v>961</v>
       </c>
       <c r="F254" s="11" t="s">
         <v>957</v>
@@ -11816,7 +11810,7 @@
         <v>9</v>
       </c>
       <c r="H254" s="11">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="I254" s="11" t="s">
         <v>1</v>
@@ -11836,7 +11830,7 @@
         <v>967</v>
       </c>
       <c r="E255" s="13" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="F255" s="13" t="s">
         <v>957</v>
@@ -11845,7 +11839,7 @@
         <v>9</v>
       </c>
       <c r="H255" s="13">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="I255" s="13" t="s">
         <v>1</v>
@@ -11853,19 +11847,19 @@
     </row>
     <row r="256" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B256" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C256" s="11" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D256" s="11" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="E256" s="11" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="F256" s="11" t="s">
         <v>957</v>
@@ -11874,7 +11868,7 @@
         <v>9</v>
       </c>
       <c r="H256" s="11">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I256" s="11" t="s">
         <v>1</v>
@@ -11882,16 +11876,16 @@
     </row>
     <row r="257" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="13" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B257" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C257" s="13" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D257" s="13" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E257" s="13" t="s">
         <v>956</v>
@@ -11903,7 +11897,7 @@
         <v>9</v>
       </c>
       <c r="H257" s="13">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="I257" s="13" t="s">
         <v>1</v>
@@ -11911,19 +11905,19 @@
     </row>
     <row r="258" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B258" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C258" s="11" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D258" s="11" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="E258" s="11" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="F258" s="11" t="s">
         <v>957</v>
@@ -11932,7 +11926,7 @@
         <v>9</v>
       </c>
       <c r="H258" s="11">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="I258" s="11" t="s">
         <v>1</v>
@@ -11940,19 +11934,19 @@
     </row>
     <row r="259" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="13" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B259" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C259" s="13" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D259" s="13" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="E259" s="13" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="F259" s="13" t="s">
         <v>957</v>
@@ -11961,7 +11955,7 @@
         <v>9</v>
       </c>
       <c r="H259" s="13">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="I259" s="13" t="s">
         <v>1</v>
@@ -11969,19 +11963,19 @@
     </row>
     <row r="260" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B260" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C260" s="11" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D260" s="11" t="s">
-        <v>982</v>
+        <v>960</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="F260" s="11" t="s">
         <v>957</v>
@@ -11990,7 +11984,7 @@
         <v>9</v>
       </c>
       <c r="H260" s="11">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="I260" s="11" t="s">
         <v>1</v>
@@ -12007,7 +12001,7 @@
         <v>984</v>
       </c>
       <c r="D261" s="13" t="s">
-        <v>985</v>
+        <v>960</v>
       </c>
       <c r="E261" s="13" t="s">
         <v>956</v>
@@ -12019,7 +12013,7 @@
         <v>9</v>
       </c>
       <c r="H261" s="13">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="I261" s="13" t="s">
         <v>1</v>
@@ -12027,19 +12021,19 @@
     </row>
     <row r="262" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C262" s="11" t="s">
+        <v>986</v>
+      </c>
+      <c r="D262" s="11" t="s">
         <v>987</v>
       </c>
-      <c r="D262" s="11" t="s">
-        <v>988</v>
-      </c>
       <c r="E262" s="11" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="F262" s="11" t="s">
         <v>957</v>
@@ -12048,7 +12042,7 @@
         <v>9</v>
       </c>
       <c r="H262" s="11">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I262" s="11" t="s">
         <v>1</v>
@@ -12056,19 +12050,19 @@
     </row>
     <row r="263" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="13" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B263" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C263" s="13" t="s">
+        <v>989</v>
+      </c>
+      <c r="D263" s="13" t="s">
         <v>990</v>
       </c>
-      <c r="D263" s="13" t="s">
-        <v>991</v>
-      </c>
       <c r="E263" s="13" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="F263" s="13" t="s">
         <v>957</v>
@@ -12077,7 +12071,7 @@
         <v>9</v>
       </c>
       <c r="H263" s="13">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="I263" s="13" t="s">
         <v>1</v>
@@ -12085,16 +12079,16 @@
     </row>
     <row r="264" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B264" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C264" s="11" t="s">
+        <v>992</v>
+      </c>
+      <c r="D264" s="11" t="s">
         <v>993</v>
-      </c>
-      <c r="D264" s="11" t="s">
-        <v>994</v>
       </c>
       <c r="E264" s="11" t="s">
         <v>956</v>
@@ -12106,7 +12100,7 @@
         <v>9</v>
       </c>
       <c r="H264" s="11">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="I264" s="11" t="s">
         <v>1</v>
@@ -12114,19 +12108,19 @@
     </row>
     <row r="265" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="13" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B265" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C265" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="D265" s="13" t="s">
         <v>996</v>
       </c>
-      <c r="D265" s="13" t="s">
-        <v>997</v>
-      </c>
       <c r="E265" s="13" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="F265" s="13" t="s">
         <v>957</v>
@@ -12135,7 +12129,7 @@
         <v>9</v>
       </c>
       <c r="H265" s="13">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="I265" s="13" t="s">
         <v>1</v>
@@ -12143,19 +12137,19 @@
     </row>
     <row r="266" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C266" s="11" t="s">
+        <v>998</v>
+      </c>
+      <c r="D266" s="11" t="s">
         <v>999</v>
       </c>
-      <c r="D266" s="11" t="s">
-        <v>1000</v>
-      </c>
       <c r="E266" s="11" t="s">
-        <v>1001</v>
+        <v>956</v>
       </c>
       <c r="F266" s="11" t="s">
         <v>957</v>
@@ -12164,7 +12158,7 @@
         <v>9</v>
       </c>
       <c r="H266" s="11">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="I266" s="11" t="s">
         <v>1</v>
@@ -12172,19 +12166,19 @@
     </row>
     <row r="267" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="13" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B267" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C267" s="13" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D267" s="13" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E267" s="13" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="F267" s="13" t="s">
         <v>957</v>
@@ -12193,7 +12187,7 @@
         <v>9</v>
       </c>
       <c r="H267" s="13">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="I267" s="13" t="s">
         <v>1</v>
@@ -12201,28 +12195,28 @@
     </row>
     <row r="268" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="11" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C268" s="11" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D268" s="11" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E268" s="11" t="s">
         <v>1006</v>
       </c>
-      <c r="D268" s="11" t="s">
+      <c r="F268" s="11" t="s">
         <v>1007</v>
       </c>
-      <c r="E268" s="11" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F268" s="11" t="s">
-        <v>1009</v>
-      </c>
       <c r="G268" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H268" s="11">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="I268" s="11" t="s">
         <v>1</v>
@@ -12230,28 +12224,28 @@
     </row>
     <row r="269" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="13" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B269" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C269" s="13" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D269" s="13" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E269" s="13" t="s">
         <v>1011</v>
       </c>
-      <c r="D269" s="13" t="s">
+      <c r="F269" s="13" t="s">
         <v>1012</v>
       </c>
-      <c r="E269" s="13" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F269" s="13" t="s">
-        <v>1014</v>
-      </c>
       <c r="G269" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H269" s="13">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="I269" s="13" t="s">
         <v>1</v>
@@ -12259,28 +12253,28 @@
     </row>
     <row r="270" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B270" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C270" s="11" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D270" s="11" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E270" s="11" t="s">
         <v>1016</v>
       </c>
-      <c r="D270" s="11" t="s">
+      <c r="F270" s="11" t="s">
         <v>1017</v>
       </c>
-      <c r="E270" s="11" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F270" s="11" t="s">
-        <v>1019</v>
-      </c>
       <c r="G270" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H270" s="11">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="I270" s="11" t="s">
         <v>1</v>
@@ -12288,28 +12282,28 @@
     </row>
     <row r="271" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="13" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B271" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C271" s="13" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D271" s="13" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E271" s="13" t="s">
         <v>1021</v>
       </c>
-      <c r="D271" s="13" t="s">
+      <c r="F271" s="13" t="s">
         <v>1022</v>
       </c>
-      <c r="E271" s="13" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F271" s="13" t="s">
-        <v>1024</v>
-      </c>
       <c r="G271" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H271" s="13">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="I271" s="13" t="s">
         <v>1</v>
@@ -12317,28 +12311,28 @@
     </row>
     <row r="272" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C272" s="11" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D272" s="11" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E272" s="11" t="s">
         <v>1026</v>
       </c>
-      <c r="D272" s="11" t="s">
+      <c r="F272" s="11" t="s">
         <v>1027</v>
       </c>
-      <c r="E272" s="11" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F272" s="11" t="s">
-        <v>1029</v>
-      </c>
       <c r="G272" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H272" s="11">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="I272" s="11" t="s">
         <v>1</v>
@@ -12346,28 +12340,28 @@
     </row>
     <row r="273" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="13" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B273" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C273" s="13" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D273" s="13" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E273" s="13" t="s">
         <v>1031</v>
       </c>
-      <c r="D273" s="13" t="s">
+      <c r="F273" s="13" t="s">
         <v>1032</v>
       </c>
-      <c r="E273" s="13" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F273" s="13" t="s">
-        <v>1034</v>
-      </c>
       <c r="G273" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H273" s="13">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="I273" s="13" t="s">
         <v>1</v>
@@ -12375,28 +12369,28 @@
     </row>
     <row r="274" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C274" s="11" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D274" s="11" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E274" s="11" t="s">
         <v>1036</v>
       </c>
-      <c r="D274" s="11" t="s">
+      <c r="F274" s="11" t="s">
         <v>1037</v>
       </c>
-      <c r="E274" s="11" t="s">
-        <v>1038</v>
-      </c>
-      <c r="F274" s="11" t="s">
-        <v>1039</v>
-      </c>
       <c r="G274" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H274" s="11">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="I274" s="11" t="s">
         <v>1</v>
@@ -12404,28 +12398,28 @@
     </row>
     <row r="275" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="13" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B275" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C275" s="13" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D275" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E275" s="13" t="s">
         <v>1041</v>
       </c>
-      <c r="D275" s="13" t="s">
+      <c r="F275" s="13" t="s">
         <v>1042</v>
       </c>
-      <c r="E275" s="13" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F275" s="13" t="s">
-        <v>1044</v>
-      </c>
       <c r="G275" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H275" s="13">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I275" s="13" t="s">
         <v>1</v>
@@ -12433,19 +12427,19 @@
     </row>
     <row r="276" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="11" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C276" s="11" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D276" s="11" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E276" s="11" t="s">
         <v>1046</v>
-      </c>
-      <c r="D276" s="11" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E276" s="11" t="s">
-        <v>1048</v>
       </c>
       <c r="F276" s="11" t="s">
         <v>48</v>
@@ -12454,7 +12448,7 @@
         <v>9</v>
       </c>
       <c r="H276" s="11">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I276" s="11" t="s">
         <v>1</v>
@@ -12462,28 +12456,28 @@
     </row>
     <row r="277" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="13" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B277" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C277" s="13" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D277" s="13" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E277" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="D277" s="13" t="s">
+      <c r="F277" s="13" t="s">
         <v>1051</v>
       </c>
-      <c r="E277" s="13" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F277" s="13" t="s">
-        <v>1053</v>
-      </c>
       <c r="G277" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H277" s="13">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="I277" s="13" t="s">
         <v>1</v>
@@ -12491,28 +12485,28 @@
     </row>
     <row r="278" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C278" s="11" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D278" s="11" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E278" s="11" t="s">
         <v>1055</v>
       </c>
-      <c r="D278" s="11" t="s">
+      <c r="F278" s="11" t="s">
         <v>1056</v>
       </c>
-      <c r="E278" s="11" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F278" s="11" t="s">
-        <v>1058</v>
-      </c>
       <c r="G278" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H278" s="11">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="I278" s="11" t="s">
         <v>1</v>
@@ -12520,19 +12514,19 @@
     </row>
     <row r="279" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="13" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B279" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C279" s="13" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D279" s="13" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E279" s="13" t="s">
         <v>1060</v>
-      </c>
-      <c r="D279" s="13" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E279" s="13" t="s">
-        <v>1062</v>
       </c>
       <c r="F279" s="13" t="s">
         <v>863</v>
@@ -12541,7 +12535,7 @@
         <v>9</v>
       </c>
       <c r="H279" s="13">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="I279" s="13" t="s">
         <v>1</v>
@@ -12549,28 +12543,28 @@
     </row>
     <row r="280" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C280" s="11" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D280" s="11" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E280" s="11" t="s">
         <v>1064</v>
       </c>
-      <c r="D280" s="11" t="s">
+      <c r="F280" s="11" t="s">
         <v>1065</v>
       </c>
-      <c r="E280" s="11" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F280" s="11" t="s">
-        <v>1067</v>
-      </c>
       <c r="G280" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H280" s="11">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="I280" s="11" t="s">
         <v>1</v>
@@ -12578,28 +12572,28 @@
     </row>
     <row r="281" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="13" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B281" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C281" s="13" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D281" s="13" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E281" s="13" t="s">
         <v>1069</v>
       </c>
-      <c r="D281" s="13" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E281" s="13" t="s">
-        <v>1071</v>
-      </c>
       <c r="F281" s="13" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G281" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H281" s="13">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="I281" s="13" t="s">
         <v>1</v>
@@ -12607,28 +12601,28 @@
     </row>
     <row r="282" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="11" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C282" s="11" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D282" s="11" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E282" s="11" t="s">
         <v>1073</v>
       </c>
-      <c r="D282" s="11" t="s">
-        <v>1074</v>
-      </c>
-      <c r="E282" s="11" t="s">
-        <v>1075</v>
-      </c>
       <c r="F282" s="11" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G282" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H282" s="11">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="I282" s="11" t="s">
         <v>1</v>
@@ -12636,28 +12630,28 @@
     </row>
     <row r="283" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="13" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B283" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C283" s="13" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D283" s="13" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E283" s="13" t="s">
         <v>1077</v>
       </c>
-      <c r="D283" s="13" t="s">
+      <c r="F283" s="13" t="s">
         <v>1078</v>
       </c>
-      <c r="E283" s="13" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F283" s="13" t="s">
-        <v>1080</v>
-      </c>
       <c r="G283" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H283" s="13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I283" s="13" t="s">
         <v>1</v>
@@ -12665,28 +12659,28 @@
     </row>
     <row r="284" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C284" s="11" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="E284" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G284" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H284" s="11">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I284" s="11" t="s">
         <v>1</v>
@@ -12694,28 +12688,28 @@
     </row>
     <row r="285" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="13" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B285" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C285" s="13" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D285" s="13" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E285" s="13" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F285" s="13" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G285" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H285" s="13">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="I285" s="13" t="s">
         <v>1</v>
@@ -12723,28 +12717,28 @@
     </row>
     <row r="286" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C286" s="11" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="E286" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G286" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H286" s="11">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="I286" s="11" t="s">
         <v>1</v>
@@ -12752,28 +12746,28 @@
     </row>
     <row r="287" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="13" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B287" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C287" s="13" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="D287" s="13" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="E287" s="13" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F287" s="13" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G287" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H287" s="13">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I287" s="13" t="s">
         <v>1</v>
@@ -12781,28 +12775,28 @@
     </row>
     <row r="288" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="11" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C288" s="11" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="D288" s="11" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E288" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G288" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H288" s="11">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="I288" s="11" t="s">
         <v>1</v>
@@ -12810,28 +12804,28 @@
     </row>
     <row r="289" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="13" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B289" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C289" s="13" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="D289" s="13" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="E289" s="13" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F289" s="13" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G289" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H289" s="13">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="I289" s="13" t="s">
         <v>1</v>
@@ -12839,28 +12833,28 @@
     </row>
     <row r="290" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C290" s="11" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="D290" s="11" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="E290" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G290" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H290" s="11">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="I290" s="11" t="s">
         <v>1</v>
@@ -12868,28 +12862,28 @@
     </row>
     <row r="291" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="13" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="B291" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C291" s="13" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D291" s="13" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="E291" s="13" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F291" s="13" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G291" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H291" s="13">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="I291" s="13" t="s">
         <v>1</v>
@@ -12897,28 +12891,28 @@
     </row>
     <row r="292" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="11" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C292" s="11" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D292" s="11" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E292" s="11" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F292" s="11" t="s">
         <v>1106</v>
       </c>
-      <c r="D292" s="11" t="s">
-        <v>1075</v>
-      </c>
-      <c r="E292" s="11" t="s">
-        <v>1107</v>
-      </c>
-      <c r="F292" s="11" t="s">
-        <v>1108</v>
-      </c>
       <c r="G292" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H292" s="11">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I292" s="11" t="s">
         <v>1</v>
@@ -12926,28 +12920,28 @@
     </row>
     <row r="293" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="13" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B293" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C293" s="13" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D293" s="13" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E293" s="13" t="s">
         <v>1110</v>
       </c>
-      <c r="D293" s="13" t="s">
+      <c r="F293" s="13" t="s">
         <v>1111</v>
       </c>
-      <c r="E293" s="13" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F293" s="13" t="s">
-        <v>1113</v>
-      </c>
       <c r="G293" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H293" s="13">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="I293" s="13" t="s">
         <v>1</v>
@@ -12955,28 +12949,28 @@
     </row>
     <row r="294" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="11" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B294" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C294" s="11" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D294" s="11" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E294" s="11" t="s">
         <v>1115</v>
       </c>
-      <c r="D294" s="11" t="s">
+      <c r="F294" s="11" t="s">
         <v>1116</v>
       </c>
-      <c r="E294" s="11" t="s">
-        <v>1117</v>
-      </c>
-      <c r="F294" s="11" t="s">
-        <v>1118</v>
-      </c>
       <c r="G294" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H294" s="11">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="I294" s="11" t="s">
         <v>1</v>
@@ -12984,28 +12978,28 @@
     </row>
     <row r="295" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="13" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B295" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C295" s="13" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D295" s="13" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E295" s="13" t="s">
         <v>1120</v>
       </c>
-      <c r="D295" s="13" t="s">
+      <c r="F295" s="13" t="s">
         <v>1121</v>
       </c>
-      <c r="E295" s="13" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F295" s="13" t="s">
-        <v>1123</v>
-      </c>
       <c r="G295" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H295" s="13">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="I295" s="13" t="s">
         <v>1</v>
@@ -13013,28 +13007,28 @@
     </row>
     <row r="296" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="11" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C296" s="11" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D296" s="11" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E296" s="11" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F296" s="11" t="s">
         <v>1125</v>
       </c>
-      <c r="D296" s="11" t="s">
-        <v>1066</v>
-      </c>
-      <c r="E296" s="11" t="s">
-        <v>1126</v>
-      </c>
-      <c r="F296" s="11" t="s">
-        <v>1127</v>
-      </c>
       <c r="G296" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H296" s="11">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="I296" s="11" t="s">
         <v>1</v>
@@ -13042,28 +13036,28 @@
     </row>
     <row r="297" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="13" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B297" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C297" s="13" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D297" s="13" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E297" s="13" t="s">
         <v>1129</v>
       </c>
-      <c r="D297" s="13" t="s">
+      <c r="F297" s="13" t="s">
         <v>1130</v>
       </c>
-      <c r="E297" s="13" t="s">
-        <v>1131</v>
-      </c>
-      <c r="F297" s="13" t="s">
-        <v>1132</v>
-      </c>
       <c r="G297" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H297" s="13">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="I297" s="13" t="s">
         <v>1</v>
@@ -13071,28 +13065,28 @@
     </row>
     <row r="298" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="11" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C298" s="11" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D298" s="11" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E298" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="D298" s="11" t="s">
+      <c r="F298" s="11" t="s">
         <v>1135</v>
       </c>
-      <c r="E298" s="11" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F298" s="11" t="s">
-        <v>1137</v>
-      </c>
       <c r="G298" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H298" s="11">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="I298" s="11" t="s">
         <v>1</v>
@@ -13100,28 +13094,28 @@
     </row>
     <row r="299" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="13" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B299" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C299" s="13" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="D299" s="13" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="E299" s="13" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="F299" s="13" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="G299" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H299" s="13">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I299" s="13" t="s">
         <v>1</v>
@@ -13129,28 +13123,28 @@
     </row>
     <row r="300" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>29</v>
       </c>
       <c r="C300" s="11" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D300" s="11" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E300" s="11" t="s">
         <v>1142</v>
       </c>
-      <c r="D300" s="11" t="s">
-        <v>1143</v>
-      </c>
-      <c r="E300" s="11" t="s">
-        <v>1144</v>
-      </c>
       <c r="F300" s="11" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="G300" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H300" s="11">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="I300" s="11" t="s">
         <v>1</v>
@@ -13158,28 +13152,28 @@
     </row>
     <row r="301" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="13" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="B301" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C301" s="13" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="D301" s="13" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E301" s="13" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F301" s="13" t="s">
         <v>1135</v>
       </c>
-      <c r="E301" s="13" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F301" s="13" t="s">
-        <v>1137</v>
-      </c>
       <c r="G301" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H301" s="13">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="I301" s="13" t="s">
         <v>1</v>

--- a/testing/appium-tests/Test_Report.xlsx
+++ b/testing/appium-tests/Test_Report.xlsx
@@ -1391,7 +1391,7 @@
     <t>TestCase_Sales_15: Submit random sales variation 15</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 126, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 148, Date: Today</t>
   </si>
   <si>
     <t>Sales record saved and threshold check triggered</t>
@@ -1406,7 +1406,7 @@
     <t>TestCase_Sales_16: Submit random sales variation 16</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 131, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 79, Date: Today</t>
   </si>
   <si>
     <t>TC111</t>
@@ -1415,7 +1415,7 @@
     <t>TestCase_Sales_17: Submit random sales variation 17</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 111, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 153, Date: Today</t>
   </si>
   <si>
     <t>TC112</t>
@@ -1424,7 +1424,7 @@
     <t>TestCase_Sales_18: Submit random sales variation 18</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 53, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 105, Date: Today</t>
   </si>
   <si>
     <t>TC113</t>
@@ -1433,7 +1433,7 @@
     <t>TestCase_Sales_19: Submit random sales variation 19</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 73, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 192, Date: Today</t>
   </si>
   <si>
     <t>TC114</t>
@@ -1442,7 +1442,7 @@
     <t>TestCase_Sales_20: Submit random sales variation 20</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 100, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 191, Date: Today</t>
   </si>
   <si>
     <t>TC115</t>
@@ -1451,7 +1451,7 @@
     <t>TestCase_Sales_21: Submit random sales variation 21</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 112, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 113, Date: Today</t>
   </si>
   <si>
     <t>TC116</t>
@@ -1460,7 +1460,7 @@
     <t>TestCase_Sales_22: Submit random sales variation 22</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 180, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 78, Date: Today</t>
   </si>
   <si>
     <t>TC117</t>
@@ -1469,7 +1469,7 @@
     <t>TestCase_Sales_23: Submit random sales variation 23</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 29, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 161, Date: Today</t>
   </si>
   <si>
     <t>TC118</t>
@@ -1478,7 +1478,7 @@
     <t>TestCase_Sales_24: Submit random sales variation 24</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 110, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 182, Date: Today</t>
   </si>
   <si>
     <t>TC119</t>
@@ -1487,7 +1487,7 @@
     <t>TestCase_Sales_25: Submit random sales variation 25</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 68, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 194, Date: Today</t>
   </si>
   <si>
     <t>TC120</t>
@@ -1496,7 +1496,7 @@
     <t>TestCase_Sales_26: Submit random sales variation 26</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 87, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 139, Date: Today</t>
   </si>
   <si>
     <t>TC121</t>
@@ -1505,7 +1505,7 @@
     <t>TestCase_Sales_27: Submit random sales variation 27</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 17, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 20, Date: Today</t>
   </si>
   <si>
     <t>TC122</t>
@@ -1514,196 +1514,196 @@
     <t>TestCase_Sales_28: Submit random sales variation 28</t>
   </si>
   <si>
+    <t>Item: "Item 4", Quantity: 110, Date: Today</t>
+  </si>
+  <si>
+    <t>TC123</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_29: Submit random sales variation 29</t>
+  </si>
+  <si>
+    <t>Item: "Item 5", Quantity: 93, Date: Today</t>
+  </si>
+  <si>
+    <t>TC124</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_30: Submit random sales variation 30</t>
+  </si>
+  <si>
+    <t>Item: "Item 1", Quantity: 105, Date: Today</t>
+  </si>
+  <si>
+    <t>TC125</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_31: Submit random sales variation 31</t>
+  </si>
+  <si>
+    <t>Item: "Item 2", Quantity: 23, Date: Today</t>
+  </si>
+  <si>
+    <t>TC126</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_32: Submit random sales variation 32</t>
+  </si>
+  <si>
+    <t>Item: "Item 3", Quantity: 65, Date: Today</t>
+  </si>
+  <si>
+    <t>TC127</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_33: Submit random sales variation 33</t>
+  </si>
+  <si>
+    <t>Item: "Item 4", Quantity: 135, Date: Today</t>
+  </si>
+  <si>
+    <t>TC128</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_34: Submit random sales variation 34</t>
+  </si>
+  <si>
+    <t>Item: "Item 5", Quantity: 156, Date: Today</t>
+  </si>
+  <si>
+    <t>TC129</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_35: Submit random sales variation 35</t>
+  </si>
+  <si>
+    <t>Item: "Item 1", Quantity: 70, Date: Today</t>
+  </si>
+  <si>
+    <t>TC130</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_36: Submit random sales variation 36</t>
+  </si>
+  <si>
+    <t>Item: "Item 2", Quantity: 143, Date: Today</t>
+  </si>
+  <si>
+    <t>TC131</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_37: Submit random sales variation 37</t>
+  </si>
+  <si>
+    <t>Item: "Item 3", Quantity: 105, Date: Today</t>
+  </si>
+  <si>
+    <t>TC132</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_38: Submit random sales variation 38</t>
+  </si>
+  <si>
+    <t>Item: "Item 4", Quantity: 198, Date: Today</t>
+  </si>
+  <si>
+    <t>TC133</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_39: Submit random sales variation 39</t>
+  </si>
+  <si>
+    <t>Item: "Item 5", Quantity: 108, Date: Today</t>
+  </si>
+  <si>
+    <t>TC134</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_40: Submit random sales variation 40</t>
+  </si>
+  <si>
+    <t>Item: "Item 1", Quantity: 5, Date: Today</t>
+  </si>
+  <si>
+    <t>TC135</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_41: Submit random sales variation 41</t>
+  </si>
+  <si>
+    <t>Item: "Item 2", Quantity: 25, Date: Today</t>
+  </si>
+  <si>
+    <t>TC136</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_42: Submit random sales variation 42</t>
+  </si>
+  <si>
+    <t>Item: "Item 3", Quantity: 173, Date: Today</t>
+  </si>
+  <si>
+    <t>TC137</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_43: Submit random sales variation 43</t>
+  </si>
+  <si>
+    <t>Item: "Item 4", Quantity: 14, Date: Today</t>
+  </si>
+  <si>
+    <t>TC138</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_44: Submit random sales variation 44</t>
+  </si>
+  <si>
+    <t>Item: "Item 5", Quantity: 91, Date: Today</t>
+  </si>
+  <si>
+    <t>TC139</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_45: Submit random sales variation 45</t>
+  </si>
+  <si>
+    <t>Item: "Item 1", Quantity: 152, Date: Today</t>
+  </si>
+  <si>
+    <t>TC140</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_46: Submit random sales variation 46</t>
+  </si>
+  <si>
+    <t>Item: "Item 2", Quantity: 47, Date: Today</t>
+  </si>
+  <si>
+    <t>TC141</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_47: Submit random sales variation 47</t>
+  </si>
+  <si>
+    <t>Item: "Item 3", Quantity: 161, Date: Today</t>
+  </si>
+  <si>
+    <t>TC142</t>
+  </si>
+  <si>
+    <t>TestCase_Sales_48: Submit random sales variation 48</t>
+  </si>
+  <si>
     <t>Item: "Item 4", Quantity: 178, Date: Today</t>
   </si>
   <si>
-    <t>TC123</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_29: Submit random sales variation 29</t>
-  </si>
-  <si>
-    <t>Item: "Item 5", Quantity: 52, Date: Today</t>
-  </si>
-  <si>
-    <t>TC124</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_30: Submit random sales variation 30</t>
-  </si>
-  <si>
-    <t>Item: "Item 1", Quantity: 78, Date: Today</t>
-  </si>
-  <si>
-    <t>TC125</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_31: Submit random sales variation 31</t>
-  </si>
-  <si>
-    <t>Item: "Item 2", Quantity: 88, Date: Today</t>
-  </si>
-  <si>
-    <t>TC126</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_32: Submit random sales variation 32</t>
-  </si>
-  <si>
-    <t>Item: "Item 3", Quantity: 80, Date: Today</t>
-  </si>
-  <si>
-    <t>TC127</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_33: Submit random sales variation 33</t>
-  </si>
-  <si>
-    <t>Item: "Item 4", Quantity: 46, Date: Today</t>
-  </si>
-  <si>
-    <t>TC128</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_34: Submit random sales variation 34</t>
-  </si>
-  <si>
-    <t>Item: "Item 5", Quantity: 12, Date: Today</t>
-  </si>
-  <si>
-    <t>TC129</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_35: Submit random sales variation 35</t>
-  </si>
-  <si>
-    <t>Item: "Item 1", Quantity: 4, Date: Today</t>
-  </si>
-  <si>
-    <t>TC130</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_36: Submit random sales variation 36</t>
-  </si>
-  <si>
-    <t>Item: "Item 2", Quantity: 143, Date: Today</t>
-  </si>
-  <si>
-    <t>TC131</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_37: Submit random sales variation 37</t>
-  </si>
-  <si>
-    <t>Item: "Item 3", Quantity: 133, Date: Today</t>
-  </si>
-  <si>
-    <t>TC132</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_38: Submit random sales variation 38</t>
-  </si>
-  <si>
-    <t>Item: "Item 4", Quantity: 32, Date: Today</t>
-  </si>
-  <si>
-    <t>TC133</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_39: Submit random sales variation 39</t>
-  </si>
-  <si>
-    <t>Item: "Item 5", Quantity: 24, Date: Today</t>
-  </si>
-  <si>
-    <t>TC134</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_40: Submit random sales variation 40</t>
-  </si>
-  <si>
-    <t>Item: "Item 1", Quantity: 39, Date: Today</t>
-  </si>
-  <si>
-    <t>TC135</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_41: Submit random sales variation 41</t>
-  </si>
-  <si>
-    <t>Item: "Item 2", Quantity: 79, Date: Today</t>
-  </si>
-  <si>
-    <t>TC136</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_42: Submit random sales variation 42</t>
-  </si>
-  <si>
-    <t>Item: "Item 3", Quantity: 188, Date: Today</t>
-  </si>
-  <si>
-    <t>TC137</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_43: Submit random sales variation 43</t>
-  </si>
-  <si>
-    <t>Item: "Item 4", Quantity: 159, Date: Today</t>
-  </si>
-  <si>
-    <t>TC138</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_44: Submit random sales variation 44</t>
-  </si>
-  <si>
-    <t>Item: "Item 5", Quantity: 48, Date: Today</t>
-  </si>
-  <si>
-    <t>TC139</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_45: Submit random sales variation 45</t>
-  </si>
-  <si>
-    <t>Item: "Item 1", Quantity: 55, Date: Today</t>
-  </si>
-  <si>
-    <t>TC140</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_46: Submit random sales variation 46</t>
-  </si>
-  <si>
-    <t>Item: "Item 2", Quantity: 65, Date: Today</t>
-  </si>
-  <si>
-    <t>TC141</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_47: Submit random sales variation 47</t>
-  </si>
-  <si>
-    <t>Item: "Item 3", Quantity: 140, Date: Today</t>
-  </si>
-  <si>
-    <t>TC142</t>
-  </si>
-  <si>
-    <t>TestCase_Sales_48: Submit random sales variation 48</t>
-  </si>
-  <si>
-    <t>Item: "Item 4", Quantity: 192, Date: Today</t>
-  </si>
-  <si>
     <t>TC143</t>
   </si>
   <si>
     <t>TestCase_Sales_49: Submit random sales variation 49</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 164, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 131, Date: Today</t>
   </si>
   <si>
     <t>TC144</t>
@@ -1712,7 +1712,7 @@
     <t>TestCase_Sales_50: Submit random sales variation 50</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 60, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 37, Date: Today</t>
   </si>
   <si>
     <t>TC145</t>
@@ -2876,151 +2876,151 @@
     <t>TC251</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_09: Score 21 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 21</t>
+    <t>TestCase_HealthScore_09: Score 97 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 97</t>
+  </si>
+  <si>
+    <t>Verdict: "Thriving" displayed</t>
+  </si>
+  <si>
+    <t>Verdict matched expected business logic</t>
+  </si>
+  <si>
+    <t>TC252</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_10: Score 75 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 75</t>
+  </si>
+  <si>
+    <t>Verdict: "Work in Progress" displayed</t>
+  </si>
+  <si>
+    <t>TC253</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_11: Score 92 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 92</t>
+  </si>
+  <si>
+    <t>TC254</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_12: Score 49 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 49</t>
   </si>
   <si>
     <t>Verdict: "Immediate Action Needed" displayed</t>
   </si>
   <si>
-    <t>Verdict matched expected business logic</t>
-  </si>
-  <si>
-    <t>TC252</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_10: Score 16 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 16</t>
-  </si>
-  <si>
-    <t>TC253</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_11: Score 94 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 94</t>
-  </si>
-  <si>
-    <t>Verdict: "Thriving" displayed</t>
-  </si>
-  <si>
-    <t>TC254</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_12: Score 54 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 54</t>
-  </si>
-  <si>
-    <t>Verdict: "Work in Progress" displayed</t>
-  </si>
-  <si>
     <t>TC255</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_13: Score 86 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 86</t>
+    <t>TestCase_HealthScore_13: Score 82 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 82</t>
   </si>
   <si>
     <t>TC256</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_14: Score 24 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 24</t>
+    <t>TestCase_HealthScore_14: Score 10 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 10</t>
   </si>
   <si>
     <t>TC257</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_15: Score 72 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 72</t>
+    <t>TestCase_HealthScore_15: Score 42 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 42</t>
   </si>
   <si>
     <t>TC258</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_16: Score 15 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 15</t>
+    <t>TestCase_HealthScore_16: Score 49 shows "Immediate Action Needed" verdict</t>
   </si>
   <si>
     <t>TC259</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_17: Score 16 shows "Immediate Action Needed" verdict</t>
+    <t>TestCase_HealthScore_17: Score 31 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 31</t>
   </si>
   <si>
     <t>TC260</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_18: Score 16 shows "Immediate Action Needed" verdict</t>
+    <t>TestCase_HealthScore_18: Score 41 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 41</t>
   </si>
   <si>
     <t>TC261</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_19: Score 81 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 81</t>
+    <t>TestCase_HealthScore_19: Score 5 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 5</t>
   </si>
   <si>
     <t>TC262</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_20: Score 89 shows "Thriving" verdict</t>
+    <t>TestCase_HealthScore_20: Score 82 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>TC263</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_21: Score 83 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 83</t>
+  </si>
+  <si>
+    <t>TC264</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_22: Score 89 shows "Thriving" verdict</t>
   </si>
   <si>
     <t>Simulated score: 89</t>
   </si>
   <si>
-    <t>TC263</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_21: Score 3 shows "Immediate Action Needed" verdict</t>
+    <t>TC265</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_23: Score 14 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 14</t>
+  </si>
+  <si>
+    <t>TC266</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_24: Score 3 shows "Immediate Action Needed" verdict</t>
   </si>
   <si>
     <t>Simulated score: 3</t>
-  </si>
-  <si>
-    <t>TC264</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_22: Score 88 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 88</t>
-  </si>
-  <si>
-    <t>TC265</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_23: Score 5 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 5</t>
-  </si>
-  <si>
-    <t>TC266</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_24: Score 37 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 37</t>
   </si>
   <si>
     <t>TC267</t>
@@ -4502,7 +4502,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="11">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>1</v>
@@ -4531,7 +4531,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="13">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>1</v>
@@ -4560,7 +4560,7 @@
         <v>9</v>
       </c>
       <c r="H4" s="11">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>1</v>
@@ -4589,7 +4589,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="13">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>1</v>
@@ -4618,7 +4618,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="11">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>1</v>
@@ -4647,7 +4647,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="13">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>1</v>
@@ -4705,7 +4705,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="13">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>1</v>
@@ -4734,7 +4734,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="11">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>1</v>
@@ -4763,7 +4763,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="13">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>1</v>
@@ -4792,7 +4792,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="11">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>9</v>
       </c>
       <c r="H13" s="13">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>1</v>
@@ -4850,7 +4850,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="11">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>1</v>
@@ -4879,7 +4879,7 @@
         <v>9</v>
       </c>
       <c r="H15" s="13">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>1</v>
@@ -4908,7 +4908,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="11">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>1</v>
@@ -4937,7 +4937,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="13">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>1</v>
@@ -4966,7 +4966,7 @@
         <v>9</v>
       </c>
       <c r="H18" s="11">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         <v>9</v>
       </c>
       <c r="H19" s="13">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>1</v>
@@ -5024,7 +5024,7 @@
         <v>9</v>
       </c>
       <c r="H20" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>1</v>
@@ -5053,7 +5053,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="13">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>1</v>
@@ -5082,7 +5082,7 @@
         <v>9</v>
       </c>
       <c r="H22" s="11">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>1</v>
@@ -5111,7 +5111,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="13">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>1</v>
@@ -5140,7 +5140,7 @@
         <v>9</v>
       </c>
       <c r="H24" s="11">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>1</v>
@@ -5169,7 +5169,7 @@
         <v>9</v>
       </c>
       <c r="H25" s="13">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>1</v>
@@ -5198,7 +5198,7 @@
         <v>9</v>
       </c>
       <c r="H26" s="11">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>1</v>
@@ -5227,7 +5227,7 @@
         <v>9</v>
       </c>
       <c r="H27" s="13">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>1</v>
@@ -5256,7 +5256,7 @@
         <v>9</v>
       </c>
       <c r="H28" s="11">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>1</v>
@@ -5285,7 +5285,7 @@
         <v>9</v>
       </c>
       <c r="H29" s="13">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>1</v>
@@ -5314,7 +5314,7 @@
         <v>9</v>
       </c>
       <c r="H30" s="11">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>1</v>
@@ -5343,7 +5343,7 @@
         <v>9</v>
       </c>
       <c r="H31" s="13">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>1</v>
@@ -5372,7 +5372,7 @@
         <v>9</v>
       </c>
       <c r="H32" s="11">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>1</v>
@@ -5401,7 +5401,7 @@
         <v>9</v>
       </c>
       <c r="H33" s="13">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>1</v>
@@ -5430,7 +5430,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="11">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>1</v>
@@ -5459,7 +5459,7 @@
         <v>9</v>
       </c>
       <c r="H35" s="13">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="I35" s="13" t="s">
         <v>1</v>
@@ -5488,7 +5488,7 @@
         <v>9</v>
       </c>
       <c r="H36" s="11">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>1</v>
@@ -5517,7 +5517,7 @@
         <v>9</v>
       </c>
       <c r="H37" s="13">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>1</v>
@@ -5546,7 +5546,7 @@
         <v>9</v>
       </c>
       <c r="H38" s="11">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>1</v>
@@ -5575,7 +5575,7 @@
         <v>9</v>
       </c>
       <c r="H39" s="13">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>1</v>
@@ -5604,7 +5604,7 @@
         <v>9</v>
       </c>
       <c r="H40" s="11">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>1</v>
@@ -5633,7 +5633,7 @@
         <v>9</v>
       </c>
       <c r="H41" s="13">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>1</v>
@@ -5662,7 +5662,7 @@
         <v>9</v>
       </c>
       <c r="H42" s="11">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>1</v>
@@ -5691,7 +5691,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="13">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>1</v>
@@ -5720,7 +5720,7 @@
         <v>9</v>
       </c>
       <c r="H44" s="11">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>1</v>
@@ -5749,7 +5749,7 @@
         <v>9</v>
       </c>
       <c r="H45" s="13">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>1</v>
@@ -5778,7 +5778,7 @@
         <v>9</v>
       </c>
       <c r="H46" s="11">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>1</v>
@@ -5807,7 +5807,7 @@
         <v>9</v>
       </c>
       <c r="H47" s="13">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>1</v>
@@ -5836,7 +5836,7 @@
         <v>9</v>
       </c>
       <c r="H48" s="11">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>1</v>
@@ -5865,7 +5865,7 @@
         <v>9</v>
       </c>
       <c r="H49" s="13">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>1</v>
@@ -5894,7 +5894,7 @@
         <v>9</v>
       </c>
       <c r="H50" s="11">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>1</v>
@@ -5923,7 +5923,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="13">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>1</v>
@@ -5952,7 +5952,7 @@
         <v>9</v>
       </c>
       <c r="H52" s="11">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>1</v>
@@ -5981,7 +5981,7 @@
         <v>9</v>
       </c>
       <c r="H53" s="13">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>1</v>
@@ -6010,7 +6010,7 @@
         <v>9</v>
       </c>
       <c r="H54" s="11">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>1</v>
@@ -6039,7 +6039,7 @@
         <v>9</v>
       </c>
       <c r="H55" s="13">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>1</v>
@@ -6097,7 +6097,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="13">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>1</v>
@@ -6126,7 +6126,7 @@
         <v>9</v>
       </c>
       <c r="H58" s="11">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>1</v>
@@ -6155,7 +6155,7 @@
         <v>9</v>
       </c>
       <c r="H59" s="13">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>1</v>
@@ -6184,7 +6184,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="11">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>1</v>
@@ -6213,7 +6213,7 @@
         <v>9</v>
       </c>
       <c r="H61" s="13">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>1</v>
@@ -6242,7 +6242,7 @@
         <v>9</v>
       </c>
       <c r="H62" s="11">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>1</v>
@@ -6271,7 +6271,7 @@
         <v>9</v>
       </c>
       <c r="H63" s="13">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>1</v>
@@ -6300,7 +6300,7 @@
         <v>9</v>
       </c>
       <c r="H64" s="11">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>1</v>
@@ -6329,7 +6329,7 @@
         <v>9</v>
       </c>
       <c r="H65" s="13">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>1</v>
@@ -6358,7 +6358,7 @@
         <v>9</v>
       </c>
       <c r="H66" s="11">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>1</v>
@@ -6387,7 +6387,7 @@
         <v>9</v>
       </c>
       <c r="H67" s="13">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>1</v>
@@ -6416,7 +6416,7 @@
         <v>9</v>
       </c>
       <c r="H68" s="11">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>1</v>
@@ -6445,7 +6445,7 @@
         <v>9</v>
       </c>
       <c r="H69" s="13">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>1</v>
@@ -6474,7 +6474,7 @@
         <v>9</v>
       </c>
       <c r="H70" s="11">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>1</v>
@@ -6503,7 +6503,7 @@
         <v>9</v>
       </c>
       <c r="H71" s="13">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>1</v>
@@ -6532,7 +6532,7 @@
         <v>9</v>
       </c>
       <c r="H72" s="11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>1</v>
@@ -6561,7 +6561,7 @@
         <v>9</v>
       </c>
       <c r="H73" s="13">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>1</v>
@@ -6590,7 +6590,7 @@
         <v>9</v>
       </c>
       <c r="H74" s="11">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>1</v>
@@ -6619,7 +6619,7 @@
         <v>9</v>
       </c>
       <c r="H75" s="13">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>1</v>
@@ -6648,7 +6648,7 @@
         <v>9</v>
       </c>
       <c r="H76" s="11">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>1</v>
@@ -6677,7 +6677,7 @@
         <v>9</v>
       </c>
       <c r="H77" s="13">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>1</v>
@@ -6706,7 +6706,7 @@
         <v>9</v>
       </c>
       <c r="H78" s="11">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>1</v>
@@ -6735,7 +6735,7 @@
         <v>9</v>
       </c>
       <c r="H79" s="13">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>1</v>
@@ -6764,7 +6764,7 @@
         <v>9</v>
       </c>
       <c r="H80" s="11">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>1</v>
@@ -6793,7 +6793,7 @@
         <v>9</v>
       </c>
       <c r="H81" s="13">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="I81" s="13" t="s">
         <v>1</v>
@@ -6822,7 +6822,7 @@
         <v>9</v>
       </c>
       <c r="H82" s="11">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>1</v>
@@ -6851,7 +6851,7 @@
         <v>9</v>
       </c>
       <c r="H83" s="13">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="I83" s="13" t="s">
         <v>1</v>
@@ -6880,7 +6880,7 @@
         <v>9</v>
       </c>
       <c r="H84" s="11">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>1</v>
@@ -6909,7 +6909,7 @@
         <v>9</v>
       </c>
       <c r="H85" s="13">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>1</v>
@@ -6938,7 +6938,7 @@
         <v>9</v>
       </c>
       <c r="H86" s="11">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>1</v>
@@ -6967,7 +6967,7 @@
         <v>9</v>
       </c>
       <c r="H87" s="13">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>1</v>
@@ -6996,7 +6996,7 @@
         <v>9</v>
       </c>
       <c r="H88" s="11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>1</v>
@@ -7025,7 +7025,7 @@
         <v>9</v>
       </c>
       <c r="H89" s="13">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="I89" s="13" t="s">
         <v>1</v>
@@ -7054,7 +7054,7 @@
         <v>9</v>
       </c>
       <c r="H90" s="11">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I90" s="11" t="s">
         <v>1</v>
@@ -7083,7 +7083,7 @@
         <v>9</v>
       </c>
       <c r="H91" s="13">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="I91" s="13" t="s">
         <v>1</v>
@@ -7112,7 +7112,7 @@
         <v>9</v>
       </c>
       <c r="H92" s="11">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="I92" s="11" t="s">
         <v>1</v>
@@ -7141,7 +7141,7 @@
         <v>9</v>
       </c>
       <c r="H93" s="13">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="I93" s="13" t="s">
         <v>1</v>
@@ -7170,7 +7170,7 @@
         <v>9</v>
       </c>
       <c r="H94" s="11">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>1</v>
@@ -7199,7 +7199,7 @@
         <v>9</v>
       </c>
       <c r="H95" s="13">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="I95" s="13" t="s">
         <v>1</v>
@@ -7228,7 +7228,7 @@
         <v>9</v>
       </c>
       <c r="H96" s="11">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>1</v>
@@ -7257,7 +7257,7 @@
         <v>9</v>
       </c>
       <c r="H97" s="13">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I97" s="13" t="s">
         <v>1</v>
@@ -7286,7 +7286,7 @@
         <v>9</v>
       </c>
       <c r="H98" s="11">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>1</v>
@@ -7315,7 +7315,7 @@
         <v>9</v>
       </c>
       <c r="H99" s="13">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I99" s="13" t="s">
         <v>1</v>
@@ -7344,7 +7344,7 @@
         <v>9</v>
       </c>
       <c r="H100" s="11">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>1</v>
@@ -7373,7 +7373,7 @@
         <v>9</v>
       </c>
       <c r="H101" s="13">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="I101" s="13" t="s">
         <v>1</v>
@@ -7402,7 +7402,7 @@
         <v>9</v>
       </c>
       <c r="H102" s="11">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>1</v>
@@ -7431,7 +7431,7 @@
         <v>9</v>
       </c>
       <c r="H103" s="13">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I103" s="13" t="s">
         <v>1</v>
@@ -7460,7 +7460,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="11">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>1</v>
@@ -7489,7 +7489,7 @@
         <v>9</v>
       </c>
       <c r="H105" s="13">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I105" s="13" t="s">
         <v>1</v>
@@ -7518,7 +7518,7 @@
         <v>9</v>
       </c>
       <c r="H106" s="11">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>1</v>
@@ -7547,7 +7547,7 @@
         <v>9</v>
       </c>
       <c r="H107" s="13">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="I107" s="13" t="s">
         <v>1</v>
@@ -7576,7 +7576,7 @@
         <v>9</v>
       </c>
       <c r="H108" s="11">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>1</v>
@@ -7605,7 +7605,7 @@
         <v>9</v>
       </c>
       <c r="H109" s="13">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I109" s="13" t="s">
         <v>1</v>
@@ -7634,7 +7634,7 @@
         <v>9</v>
       </c>
       <c r="H110" s="11">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>1</v>
@@ -7663,7 +7663,7 @@
         <v>9</v>
       </c>
       <c r="H111" s="13">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="I111" s="13" t="s">
         <v>1</v>
@@ -7692,7 +7692,7 @@
         <v>9</v>
       </c>
       <c r="H112" s="11">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="I112" s="11" t="s">
         <v>1</v>
@@ -7721,7 +7721,7 @@
         <v>9</v>
       </c>
       <c r="H113" s="13">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="I113" s="13" t="s">
         <v>1</v>
@@ -7750,7 +7750,7 @@
         <v>9</v>
       </c>
       <c r="H114" s="11">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="I114" s="11" t="s">
         <v>1</v>
@@ -7779,7 +7779,7 @@
         <v>9</v>
       </c>
       <c r="H115" s="13">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="I115" s="13" t="s">
         <v>1</v>
@@ -7808,7 +7808,7 @@
         <v>9</v>
       </c>
       <c r="H116" s="11">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="I116" s="11" t="s">
         <v>1</v>
@@ -7837,7 +7837,7 @@
         <v>9</v>
       </c>
       <c r="H117" s="13">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="I117" s="13" t="s">
         <v>1</v>
@@ -7866,7 +7866,7 @@
         <v>9</v>
       </c>
       <c r="H118" s="11">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>1</v>
@@ -7895,7 +7895,7 @@
         <v>9</v>
       </c>
       <c r="H119" s="13">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I119" s="13" t="s">
         <v>1</v>
@@ -7924,7 +7924,7 @@
         <v>9</v>
       </c>
       <c r="H120" s="11">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>1</v>
@@ -7953,7 +7953,7 @@
         <v>9</v>
       </c>
       <c r="H121" s="13">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>1</v>
@@ -7982,7 +7982,7 @@
         <v>9</v>
       </c>
       <c r="H122" s="11">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="I122" s="11" t="s">
         <v>1</v>
@@ -8011,7 +8011,7 @@
         <v>9</v>
       </c>
       <c r="H123" s="13">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>1</v>
@@ -8040,7 +8040,7 @@
         <v>9</v>
       </c>
       <c r="H124" s="11">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I124" s="11" t="s">
         <v>1</v>
@@ -8069,7 +8069,7 @@
         <v>9</v>
       </c>
       <c r="H125" s="13">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>1</v>
@@ -8098,7 +8098,7 @@
         <v>9</v>
       </c>
       <c r="H126" s="11">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="I126" s="11" t="s">
         <v>1</v>
@@ -8127,7 +8127,7 @@
         <v>9</v>
       </c>
       <c r="H127" s="13">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>1</v>
@@ -8156,7 +8156,7 @@
         <v>9</v>
       </c>
       <c r="H128" s="11">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>1</v>
@@ -8185,7 +8185,7 @@
         <v>9</v>
       </c>
       <c r="H129" s="13">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>1</v>
@@ -8214,7 +8214,7 @@
         <v>9</v>
       </c>
       <c r="H130" s="11">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="I130" s="11" t="s">
         <v>1</v>
@@ -8243,7 +8243,7 @@
         <v>9</v>
       </c>
       <c r="H131" s="13">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>1</v>
@@ -8272,7 +8272,7 @@
         <v>9</v>
       </c>
       <c r="H132" s="11">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I132" s="11" t="s">
         <v>1</v>
@@ -8301,7 +8301,7 @@
         <v>9</v>
       </c>
       <c r="H133" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>1</v>
@@ -8330,7 +8330,7 @@
         <v>9</v>
       </c>
       <c r="H134" s="11">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I134" s="11" t="s">
         <v>1</v>
@@ -8359,7 +8359,7 @@
         <v>9</v>
       </c>
       <c r="H135" s="13">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>1</v>
@@ -8388,7 +8388,7 @@
         <v>9</v>
       </c>
       <c r="H136" s="11">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="I136" s="11" t="s">
         <v>1</v>
@@ -8417,7 +8417,7 @@
         <v>9</v>
       </c>
       <c r="H137" s="13">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="I137" s="13" t="s">
         <v>1</v>
@@ -8446,7 +8446,7 @@
         <v>9</v>
       </c>
       <c r="H138" s="11">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="I138" s="11" t="s">
         <v>1</v>
@@ -8475,7 +8475,7 @@
         <v>9</v>
       </c>
       <c r="H139" s="13">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="I139" s="13" t="s">
         <v>1</v>
@@ -8504,7 +8504,7 @@
         <v>9</v>
       </c>
       <c r="H140" s="11">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="I140" s="11" t="s">
         <v>1</v>
@@ -8533,7 +8533,7 @@
         <v>9</v>
       </c>
       <c r="H141" s="13">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="I141" s="13" t="s">
         <v>1</v>
@@ -8562,7 +8562,7 @@
         <v>9</v>
       </c>
       <c r="H142" s="11">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="I142" s="11" t="s">
         <v>1</v>
@@ -8591,7 +8591,7 @@
         <v>9</v>
       </c>
       <c r="H143" s="13">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>9</v>
       </c>
       <c r="H144" s="11">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="I144" s="11" t="s">
         <v>1</v>
@@ -8649,7 +8649,7 @@
         <v>9</v>
       </c>
       <c r="H145" s="13">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="I145" s="13" t="s">
         <v>1</v>
@@ -8678,7 +8678,7 @@
         <v>9</v>
       </c>
       <c r="H146" s="11">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="I146" s="11" t="s">
         <v>1</v>
@@ -8707,7 +8707,7 @@
         <v>9</v>
       </c>
       <c r="H147" s="13">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="I147" s="13" t="s">
         <v>1</v>
@@ -8736,7 +8736,7 @@
         <v>9</v>
       </c>
       <c r="H148" s="11">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="I148" s="11" t="s">
         <v>1</v>
@@ -8765,7 +8765,7 @@
         <v>9</v>
       </c>
       <c r="H149" s="13">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="I149" s="13" t="s">
         <v>1</v>
@@ -8794,7 +8794,7 @@
         <v>9</v>
       </c>
       <c r="H150" s="11">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="I150" s="11" t="s">
         <v>1</v>
@@ -8823,7 +8823,7 @@
         <v>9</v>
       </c>
       <c r="H151" s="13">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="I151" s="13" t="s">
         <v>1</v>
@@ -8852,7 +8852,7 @@
         <v>9</v>
       </c>
       <c r="H152" s="11">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="I152" s="11" t="s">
         <v>1</v>
@@ -8881,7 +8881,7 @@
         <v>9</v>
       </c>
       <c r="H153" s="13">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I153" s="13" t="s">
         <v>1</v>
@@ -8910,7 +8910,7 @@
         <v>9</v>
       </c>
       <c r="H154" s="11">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I154" s="11" t="s">
         <v>1</v>
@@ -8939,7 +8939,7 @@
         <v>9</v>
       </c>
       <c r="H155" s="13">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I155" s="13" t="s">
         <v>1</v>
@@ -8968,7 +8968,7 @@
         <v>9</v>
       </c>
       <c r="H156" s="11">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I156" s="11" t="s">
         <v>1</v>
@@ -8997,7 +8997,7 @@
         <v>9</v>
       </c>
       <c r="H157" s="13">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>1</v>
@@ -9026,7 +9026,7 @@
         <v>9</v>
       </c>
       <c r="H158" s="11">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="I158" s="11" t="s">
         <v>1</v>
@@ -9055,7 +9055,7 @@
         <v>9</v>
       </c>
       <c r="H159" s="13">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="I159" s="13" t="s">
         <v>1</v>
@@ -9084,7 +9084,7 @@
         <v>9</v>
       </c>
       <c r="H160" s="11">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I160" s="11" t="s">
         <v>1</v>
@@ -9113,7 +9113,7 @@
         <v>9</v>
       </c>
       <c r="H161" s="13">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I161" s="13" t="s">
         <v>1</v>
@@ -9142,7 +9142,7 @@
         <v>9</v>
       </c>
       <c r="H162" s="11">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="I162" s="11" t="s">
         <v>1</v>
@@ -9171,7 +9171,7 @@
         <v>9</v>
       </c>
       <c r="H163" s="13">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>1</v>
@@ -9200,7 +9200,7 @@
         <v>9</v>
       </c>
       <c r="H164" s="11">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I164" s="11" t="s">
         <v>1</v>
@@ -9229,7 +9229,7 @@
         <v>9</v>
       </c>
       <c r="H165" s="13">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I165" s="13" t="s">
         <v>1</v>
@@ -9258,7 +9258,7 @@
         <v>9</v>
       </c>
       <c r="H166" s="11">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I166" s="11" t="s">
         <v>1</v>
@@ -9287,7 +9287,7 @@
         <v>9</v>
       </c>
       <c r="H167" s="13">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I167" s="13" t="s">
         <v>1</v>
@@ -9316,7 +9316,7 @@
         <v>9</v>
       </c>
       <c r="H168" s="11">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="I168" s="11" t="s">
         <v>1</v>
@@ -9345,7 +9345,7 @@
         <v>9</v>
       </c>
       <c r="H169" s="13">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="I169" s="13" t="s">
         <v>1</v>
@@ -9374,7 +9374,7 @@
         <v>9</v>
       </c>
       <c r="H170" s="11">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I170" s="11" t="s">
         <v>1</v>
@@ -9403,7 +9403,7 @@
         <v>9</v>
       </c>
       <c r="H171" s="13">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="I171" s="13" t="s">
         <v>1</v>
@@ -9432,7 +9432,7 @@
         <v>9</v>
       </c>
       <c r="H172" s="11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I172" s="11" t="s">
         <v>1</v>
@@ -9461,7 +9461,7 @@
         <v>9</v>
       </c>
       <c r="H173" s="13">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I173" s="13" t="s">
         <v>1</v>
@@ -9490,7 +9490,7 @@
         <v>9</v>
       </c>
       <c r="H174" s="11">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I174" s="11" t="s">
         <v>1</v>
@@ -9519,7 +9519,7 @@
         <v>9</v>
       </c>
       <c r="H175" s="13">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="I175" s="13" t="s">
         <v>1</v>
@@ -9548,7 +9548,7 @@
         <v>9</v>
       </c>
       <c r="H176" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I176" s="11" t="s">
         <v>1</v>
@@ -9577,7 +9577,7 @@
         <v>9</v>
       </c>
       <c r="H177" s="13">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="I177" s="13" t="s">
         <v>1</v>
@@ -9606,7 +9606,7 @@
         <v>9</v>
       </c>
       <c r="H178" s="11">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="I178" s="11" t="s">
         <v>1</v>
@@ -9635,7 +9635,7 @@
         <v>9</v>
       </c>
       <c r="H179" s="13">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="I179" s="13" t="s">
         <v>1</v>
@@ -9664,7 +9664,7 @@
         <v>9</v>
       </c>
       <c r="H180" s="11">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="I180" s="11" t="s">
         <v>1</v>
@@ -9693,7 +9693,7 @@
         <v>9</v>
       </c>
       <c r="H181" s="13">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="I181" s="13" t="s">
         <v>1</v>
@@ -9722,7 +9722,7 @@
         <v>9</v>
       </c>
       <c r="H182" s="11">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I182" s="11" t="s">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>9</v>
       </c>
       <c r="H183" s="13">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="I183" s="13" t="s">
         <v>1</v>
@@ -9780,7 +9780,7 @@
         <v>9</v>
       </c>
       <c r="H184" s="11">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I184" s="11" t="s">
         <v>1</v>
@@ -9809,7 +9809,7 @@
         <v>9</v>
       </c>
       <c r="H185" s="13">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="I185" s="13" t="s">
         <v>1</v>
@@ -9838,7 +9838,7 @@
         <v>9</v>
       </c>
       <c r="H186" s="11">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="I186" s="11" t="s">
         <v>1</v>
@@ -9867,7 +9867,7 @@
         <v>9</v>
       </c>
       <c r="H187" s="13">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="I187" s="13" t="s">
         <v>1</v>
@@ -9896,7 +9896,7 @@
         <v>9</v>
       </c>
       <c r="H188" s="11">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I188" s="11" t="s">
         <v>1</v>
@@ -9925,7 +9925,7 @@
         <v>9</v>
       </c>
       <c r="H189" s="13">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="I189" s="13" t="s">
         <v>1</v>
@@ -9954,7 +9954,7 @@
         <v>9</v>
       </c>
       <c r="H190" s="11">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="I190" s="11" t="s">
         <v>1</v>
@@ -9983,7 +9983,7 @@
         <v>9</v>
       </c>
       <c r="H191" s="13">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="I191" s="13" t="s">
         <v>1</v>
@@ -10012,7 +10012,7 @@
         <v>9</v>
       </c>
       <c r="H192" s="11">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I192" s="11" t="s">
         <v>1</v>
@@ -10041,7 +10041,7 @@
         <v>9</v>
       </c>
       <c r="H193" s="13">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I193" s="13" t="s">
         <v>1</v>
@@ -10070,7 +10070,7 @@
         <v>9</v>
       </c>
       <c r="H194" s="11">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="I194" s="11" t="s">
         <v>1</v>
@@ -10099,7 +10099,7 @@
         <v>9</v>
       </c>
       <c r="H195" s="13">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>1</v>
@@ -10128,7 +10128,7 @@
         <v>9</v>
       </c>
       <c r="H196" s="11">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I196" s="11" t="s">
         <v>1</v>
@@ -10157,7 +10157,7 @@
         <v>9</v>
       </c>
       <c r="H197" s="13">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>1</v>
@@ -10186,7 +10186,7 @@
         <v>9</v>
       </c>
       <c r="H198" s="11">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="I198" s="11" t="s">
         <v>1</v>
@@ -10215,7 +10215,7 @@
         <v>9</v>
       </c>
       <c r="H199" s="13">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="I199" s="13" t="s">
         <v>1</v>
@@ -10244,7 +10244,7 @@
         <v>9</v>
       </c>
       <c r="H200" s="11">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="I200" s="11" t="s">
         <v>1</v>
@@ -10302,7 +10302,7 @@
         <v>9</v>
       </c>
       <c r="H202" s="11">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="I202" s="11" t="s">
         <v>1</v>
@@ -10331,7 +10331,7 @@
         <v>9</v>
       </c>
       <c r="H203" s="13">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I203" s="13" t="s">
         <v>1</v>
@@ -10360,7 +10360,7 @@
         <v>9</v>
       </c>
       <c r="H204" s="11">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="I204" s="11" t="s">
         <v>1</v>
@@ -10389,7 +10389,7 @@
         <v>9</v>
       </c>
       <c r="H205" s="13">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="I205" s="13" t="s">
         <v>1</v>
@@ -10418,7 +10418,7 @@
         <v>9</v>
       </c>
       <c r="H206" s="11">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="I206" s="11" t="s">
         <v>1</v>
@@ -10447,7 +10447,7 @@
         <v>9</v>
       </c>
       <c r="H207" s="13">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="I207" s="13" t="s">
         <v>1</v>
@@ -10476,7 +10476,7 @@
         <v>9</v>
       </c>
       <c r="H208" s="11">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="I208" s="11" t="s">
         <v>1</v>
@@ -10505,7 +10505,7 @@
         <v>9</v>
       </c>
       <c r="H209" s="13">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I209" s="13" t="s">
         <v>1</v>
@@ -10534,7 +10534,7 @@
         <v>9</v>
       </c>
       <c r="H210" s="11">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="I210" s="11" t="s">
         <v>1</v>
@@ -10563,7 +10563,7 @@
         <v>9</v>
       </c>
       <c r="H211" s="13">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I211" s="13" t="s">
         <v>1</v>
@@ -10592,7 +10592,7 @@
         <v>9</v>
       </c>
       <c r="H212" s="11">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I212" s="11" t="s">
         <v>1</v>
@@ -10621,7 +10621,7 @@
         <v>9</v>
       </c>
       <c r="H213" s="13">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="I213" s="13" t="s">
         <v>1</v>
@@ -10650,7 +10650,7 @@
         <v>9</v>
       </c>
       <c r="H214" s="11">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="I214" s="11" t="s">
         <v>1</v>
@@ -10679,7 +10679,7 @@
         <v>9</v>
       </c>
       <c r="H215" s="13">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="I215" s="13" t="s">
         <v>1</v>
@@ -10708,7 +10708,7 @@
         <v>9</v>
       </c>
       <c r="H216" s="11">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="I216" s="11" t="s">
         <v>1</v>
@@ -10737,7 +10737,7 @@
         <v>9</v>
       </c>
       <c r="H217" s="13">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="I217" s="13" t="s">
         <v>1</v>
@@ -10766,7 +10766,7 @@
         <v>9</v>
       </c>
       <c r="H218" s="11">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I218" s="11" t="s">
         <v>1</v>
@@ -10795,7 +10795,7 @@
         <v>9</v>
       </c>
       <c r="H219" s="13">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="I219" s="13" t="s">
         <v>1</v>
@@ -10824,7 +10824,7 @@
         <v>9</v>
       </c>
       <c r="H220" s="11">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="I220" s="11" t="s">
         <v>1</v>
@@ -10853,7 +10853,7 @@
         <v>9</v>
       </c>
       <c r="H221" s="13">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="I221" s="13" t="s">
         <v>1</v>
@@ -10882,7 +10882,7 @@
         <v>9</v>
       </c>
       <c r="H222" s="11">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="I222" s="11" t="s">
         <v>1</v>
@@ -10911,7 +10911,7 @@
         <v>9</v>
       </c>
       <c r="H223" s="13">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="I223" s="13" t="s">
         <v>1</v>
@@ -10940,7 +10940,7 @@
         <v>9</v>
       </c>
       <c r="H224" s="11">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="I224" s="11" t="s">
         <v>1</v>
@@ -10969,7 +10969,7 @@
         <v>9</v>
       </c>
       <c r="H225" s="13">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="I225" s="13" t="s">
         <v>1</v>
@@ -10998,7 +10998,7 @@
         <v>9</v>
       </c>
       <c r="H226" s="11">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I226" s="11" t="s">
         <v>1</v>
@@ -11027,7 +11027,7 @@
         <v>9</v>
       </c>
       <c r="H227" s="13">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="I227" s="13" t="s">
         <v>1</v>
@@ -11056,7 +11056,7 @@
         <v>9</v>
       </c>
       <c r="H228" s="11">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="I228" s="11" t="s">
         <v>1</v>
@@ -11085,7 +11085,7 @@
         <v>9</v>
       </c>
       <c r="H229" s="13">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I229" s="13" t="s">
         <v>1</v>
@@ -11114,7 +11114,7 @@
         <v>9</v>
       </c>
       <c r="H230" s="11">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="I230" s="11" t="s">
         <v>1</v>
@@ -11143,7 +11143,7 @@
         <v>9</v>
       </c>
       <c r="H231" s="13">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I231" s="13" t="s">
         <v>1</v>
@@ -11172,7 +11172,7 @@
         <v>9</v>
       </c>
       <c r="H232" s="11">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I232" s="11" t="s">
         <v>1</v>
@@ -11201,7 +11201,7 @@
         <v>9</v>
       </c>
       <c r="H233" s="13">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="I233" s="13" t="s">
         <v>1</v>
@@ -11230,7 +11230,7 @@
         <v>9</v>
       </c>
       <c r="H234" s="11">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I234" s="11" t="s">
         <v>1</v>
@@ -11259,7 +11259,7 @@
         <v>9</v>
       </c>
       <c r="H235" s="13">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="I235" s="13" t="s">
         <v>1</v>
@@ -11288,7 +11288,7 @@
         <v>9</v>
       </c>
       <c r="H236" s="11">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I236" s="11" t="s">
         <v>1</v>
@@ -11317,7 +11317,7 @@
         <v>9</v>
       </c>
       <c r="H237" s="13">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I237" s="13" t="s">
         <v>1</v>
@@ -11346,7 +11346,7 @@
         <v>9</v>
       </c>
       <c r="H238" s="11">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>1</v>
@@ -11375,7 +11375,7 @@
         <v>9</v>
       </c>
       <c r="H239" s="13">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I239" s="13" t="s">
         <v>1</v>
@@ -11404,7 +11404,7 @@
         <v>9</v>
       </c>
       <c r="H240" s="11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>1</v>
@@ -11433,7 +11433,7 @@
         <v>9</v>
       </c>
       <c r="H241" s="13">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I241" s="13" t="s">
         <v>1</v>
@@ -11462,7 +11462,7 @@
         <v>9</v>
       </c>
       <c r="H242" s="11">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="I242" s="11" t="s">
         <v>1</v>
@@ -11491,7 +11491,7 @@
         <v>9</v>
       </c>
       <c r="H243" s="13">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I243" s="13" t="s">
         <v>1</v>
@@ -11520,7 +11520,7 @@
         <v>9</v>
       </c>
       <c r="H244" s="11">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="I244" s="11" t="s">
         <v>1</v>
@@ -11549,7 +11549,7 @@
         <v>9</v>
       </c>
       <c r="H245" s="13">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="I245" s="13" t="s">
         <v>1</v>
@@ -11578,7 +11578,7 @@
         <v>9</v>
       </c>
       <c r="H246" s="11">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="I246" s="11" t="s">
         <v>1</v>
@@ -11607,7 +11607,7 @@
         <v>9</v>
       </c>
       <c r="H247" s="13">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I247" s="13" t="s">
         <v>1</v>
@@ -11636,7 +11636,7 @@
         <v>9</v>
       </c>
       <c r="H248" s="11">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="I248" s="11" t="s">
         <v>1</v>
@@ -11665,7 +11665,7 @@
         <v>9</v>
       </c>
       <c r="H249" s="13">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="I249" s="13" t="s">
         <v>1</v>
@@ -11694,7 +11694,7 @@
         <v>9</v>
       </c>
       <c r="H250" s="11">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="I250" s="11" t="s">
         <v>1</v>
@@ -11723,7 +11723,7 @@
         <v>9</v>
       </c>
       <c r="H251" s="13">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I251" s="13" t="s">
         <v>1</v>
@@ -11752,7 +11752,7 @@
         <v>9</v>
       </c>
       <c r="H252" s="11">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="I252" s="11" t="s">
         <v>1</v>
@@ -11772,7 +11772,7 @@
         <v>960</v>
       </c>
       <c r="E253" s="13" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F253" s="13" t="s">
         <v>957</v>
@@ -11781,7 +11781,7 @@
         <v>9</v>
       </c>
       <c r="H253" s="13">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="I253" s="13" t="s">
         <v>1</v>
@@ -11789,19 +11789,19 @@
     </row>
     <row r="254" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B254" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C254" s="11" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D254" s="11" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="E254" s="11" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="F254" s="11" t="s">
         <v>957</v>
@@ -11810,7 +11810,7 @@
         <v>9</v>
       </c>
       <c r="H254" s="11">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I254" s="11" t="s">
         <v>1</v>
@@ -11839,7 +11839,7 @@
         <v>9</v>
       </c>
       <c r="H255" s="13">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I255" s="13" t="s">
         <v>1</v>
@@ -11859,7 +11859,7 @@
         <v>971</v>
       </c>
       <c r="E256" s="11" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="F256" s="11" t="s">
         <v>957</v>
@@ -11868,7 +11868,7 @@
         <v>9</v>
       </c>
       <c r="H256" s="11">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I256" s="11" t="s">
         <v>1</v>
@@ -11888,7 +11888,7 @@
         <v>974</v>
       </c>
       <c r="E257" s="13" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="F257" s="13" t="s">
         <v>957</v>
@@ -11897,7 +11897,7 @@
         <v>9</v>
       </c>
       <c r="H257" s="13">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="I257" s="13" t="s">
         <v>1</v>
@@ -11926,7 +11926,7 @@
         <v>9</v>
       </c>
       <c r="H258" s="11">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="I258" s="11" t="s">
         <v>1</v>
@@ -11943,10 +11943,10 @@
         <v>979</v>
       </c>
       <c r="D259" s="13" t="s">
-        <v>980</v>
+        <v>967</v>
       </c>
       <c r="E259" s="13" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="F259" s="13" t="s">
         <v>957</v>
@@ -11955,7 +11955,7 @@
         <v>9</v>
       </c>
       <c r="H259" s="13">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="I259" s="13" t="s">
         <v>1</v>
@@ -11963,19 +11963,19 @@
     </row>
     <row r="260" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="11" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B260" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C260" s="11" t="s">
+        <v>981</v>
+      </c>
+      <c r="D260" s="11" t="s">
         <v>982</v>
       </c>
-      <c r="D260" s="11" t="s">
-        <v>960</v>
-      </c>
       <c r="E260" s="11" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="F260" s="11" t="s">
         <v>957</v>
@@ -11984,7 +11984,7 @@
         <v>9</v>
       </c>
       <c r="H260" s="11">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="I260" s="11" t="s">
         <v>1</v>
@@ -12001,10 +12001,10 @@
         <v>984</v>
       </c>
       <c r="D261" s="13" t="s">
-        <v>960</v>
+        <v>985</v>
       </c>
       <c r="E261" s="13" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="F261" s="13" t="s">
         <v>957</v>
@@ -12013,7 +12013,7 @@
         <v>9</v>
       </c>
       <c r="H261" s="13">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I261" s="13" t="s">
         <v>1</v>
@@ -12021,19 +12021,19 @@
     </row>
     <row r="262" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="11" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C262" s="11" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D262" s="11" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="F262" s="11" t="s">
         <v>957</v>
@@ -12042,7 +12042,7 @@
         <v>9</v>
       </c>
       <c r="H262" s="11">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="I262" s="11" t="s">
         <v>1</v>
@@ -12050,19 +12050,19 @@
     </row>
     <row r="263" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="13" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B263" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C263" s="13" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D263" s="13" t="s">
-        <v>990</v>
+        <v>971</v>
       </c>
       <c r="E263" s="13" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="F263" s="13" t="s">
         <v>957</v>
@@ -12071,7 +12071,7 @@
         <v>9</v>
       </c>
       <c r="H263" s="13">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="I263" s="13" t="s">
         <v>1</v>
@@ -12100,7 +12100,7 @@
         <v>9</v>
       </c>
       <c r="H264" s="11">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="I264" s="11" t="s">
         <v>1</v>
@@ -12120,7 +12120,7 @@
         <v>996</v>
       </c>
       <c r="E265" s="13" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="F265" s="13" t="s">
         <v>957</v>
@@ -12129,7 +12129,7 @@
         <v>9</v>
       </c>
       <c r="H265" s="13">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="I265" s="13" t="s">
         <v>1</v>
@@ -12149,7 +12149,7 @@
         <v>999</v>
       </c>
       <c r="E266" s="11" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="F266" s="11" t="s">
         <v>957</v>
@@ -12158,7 +12158,7 @@
         <v>9</v>
       </c>
       <c r="H266" s="11">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I266" s="11" t="s">
         <v>1</v>
@@ -12178,7 +12178,7 @@
         <v>1002</v>
       </c>
       <c r="E267" s="13" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="F267" s="13" t="s">
         <v>957</v>
@@ -12187,7 +12187,7 @@
         <v>9</v>
       </c>
       <c r="H267" s="13">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I267" s="13" t="s">
         <v>1</v>
@@ -12216,7 +12216,7 @@
         <v>9</v>
       </c>
       <c r="H268" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I268" s="11" t="s">
         <v>1</v>
@@ -12245,7 +12245,7 @@
         <v>9</v>
       </c>
       <c r="H269" s="13">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="I269" s="13" t="s">
         <v>1</v>
@@ -12274,7 +12274,7 @@
         <v>9</v>
       </c>
       <c r="H270" s="11">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="I270" s="11" t="s">
         <v>1</v>
@@ -12303,7 +12303,7 @@
         <v>9</v>
       </c>
       <c r="H271" s="13">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="I271" s="13" t="s">
         <v>1</v>
@@ -12332,7 +12332,7 @@
         <v>9</v>
       </c>
       <c r="H272" s="11">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="I272" s="11" t="s">
         <v>1</v>
@@ -12361,7 +12361,7 @@
         <v>9</v>
       </c>
       <c r="H273" s="13">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="I273" s="13" t="s">
         <v>1</v>
@@ -12390,7 +12390,7 @@
         <v>9</v>
       </c>
       <c r="H274" s="11">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="I274" s="11" t="s">
         <v>1</v>
@@ -12419,7 +12419,7 @@
         <v>9</v>
       </c>
       <c r="H275" s="13">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I275" s="13" t="s">
         <v>1</v>
@@ -12448,7 +12448,7 @@
         <v>9</v>
       </c>
       <c r="H276" s="11">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="I276" s="11" t="s">
         <v>1</v>
@@ -12477,7 +12477,7 @@
         <v>9</v>
       </c>
       <c r="H277" s="13">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="I277" s="13" t="s">
         <v>1</v>
@@ -12506,7 +12506,7 @@
         <v>9</v>
       </c>
       <c r="H278" s="11">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="I278" s="11" t="s">
         <v>1</v>
@@ -12535,7 +12535,7 @@
         <v>9</v>
       </c>
       <c r="H279" s="13">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I279" s="13" t="s">
         <v>1</v>
@@ -12564,7 +12564,7 @@
         <v>9</v>
       </c>
       <c r="H280" s="11">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="I280" s="11" t="s">
         <v>1</v>
@@ -12593,7 +12593,7 @@
         <v>9</v>
       </c>
       <c r="H281" s="13">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="I281" s="13" t="s">
         <v>1</v>
@@ -12622,7 +12622,7 @@
         <v>9</v>
       </c>
       <c r="H282" s="11">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="I282" s="11" t="s">
         <v>1</v>
@@ -12651,7 +12651,7 @@
         <v>9</v>
       </c>
       <c r="H283" s="13">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I283" s="13" t="s">
         <v>1</v>
@@ -12680,7 +12680,7 @@
         <v>9</v>
       </c>
       <c r="H284" s="11">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I284" s="11" t="s">
         <v>1</v>
@@ -12709,7 +12709,7 @@
         <v>9</v>
       </c>
       <c r="H285" s="13">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I285" s="13" t="s">
         <v>1</v>
@@ -12738,7 +12738,7 @@
         <v>9</v>
       </c>
       <c r="H286" s="11">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="I286" s="11" t="s">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         <v>9</v>
       </c>
       <c r="H287" s="13">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="I287" s="13" t="s">
         <v>1</v>
@@ -12796,7 +12796,7 @@
         <v>9</v>
       </c>
       <c r="H288" s="11">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="I288" s="11" t="s">
         <v>1</v>
@@ -12825,7 +12825,7 @@
         <v>9</v>
       </c>
       <c r="H289" s="13">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I289" s="13" t="s">
         <v>1</v>
@@ -12854,7 +12854,7 @@
         <v>9</v>
       </c>
       <c r="H290" s="11">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="I290" s="11" t="s">
         <v>1</v>
@@ -12883,7 +12883,7 @@
         <v>9</v>
       </c>
       <c r="H291" s="13">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I291" s="13" t="s">
         <v>1</v>
@@ -12912,7 +12912,7 @@
         <v>9</v>
       </c>
       <c r="H292" s="11">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I292" s="11" t="s">
         <v>1</v>
@@ -12941,7 +12941,7 @@
         <v>9</v>
       </c>
       <c r="H293" s="13">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="I293" s="13" t="s">
         <v>1</v>
@@ -12970,7 +12970,7 @@
         <v>9</v>
       </c>
       <c r="H294" s="11">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="I294" s="11" t="s">
         <v>1</v>
@@ -12999,7 +12999,7 @@
         <v>9</v>
       </c>
       <c r="H295" s="13">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I295" s="13" t="s">
         <v>1</v>
@@ -13028,7 +13028,7 @@
         <v>9</v>
       </c>
       <c r="H296" s="11">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="I296" s="11" t="s">
         <v>1</v>
@@ -13057,7 +13057,7 @@
         <v>9</v>
       </c>
       <c r="H297" s="13">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I297" s="13" t="s">
         <v>1</v>
@@ -13086,7 +13086,7 @@
         <v>9</v>
       </c>
       <c r="H298" s="11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I298" s="11" t="s">
         <v>1</v>
@@ -13115,7 +13115,7 @@
         <v>9</v>
       </c>
       <c r="H299" s="13">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="I299" s="13" t="s">
         <v>1</v>
@@ -13144,7 +13144,7 @@
         <v>9</v>
       </c>
       <c r="H300" s="11">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="I300" s="11" t="s">
         <v>1</v>
@@ -13173,7 +13173,7 @@
         <v>9</v>
       </c>
       <c r="H301" s="13">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="I301" s="13" t="s">
         <v>1</v>

--- a/testing/appium-tests/Test_Report.xlsx
+++ b/testing/appium-tests/Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="1146">
   <si>
     <t>GROWMARK MOBILE APP - AUTOMATED TESTING REPORT</t>
   </si>
@@ -1391,7 +1391,7 @@
     <t>TestCase_Sales_15: Submit random sales variation 15</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 148, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 90, Date: Today</t>
   </si>
   <si>
     <t>Sales record saved and threshold check triggered</t>
@@ -1406,7 +1406,7 @@
     <t>TestCase_Sales_16: Submit random sales variation 16</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 79, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 108, Date: Today</t>
   </si>
   <si>
     <t>TC111</t>
@@ -1415,7 +1415,7 @@
     <t>TestCase_Sales_17: Submit random sales variation 17</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 153, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 142, Date: Today</t>
   </si>
   <si>
     <t>TC112</t>
@@ -1424,7 +1424,7 @@
     <t>TestCase_Sales_18: Submit random sales variation 18</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 105, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 31, Date: Today</t>
   </si>
   <si>
     <t>TC113</t>
@@ -1433,7 +1433,7 @@
     <t>TestCase_Sales_19: Submit random sales variation 19</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 192, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 77, Date: Today</t>
   </si>
   <si>
     <t>TC114</t>
@@ -1442,7 +1442,7 @@
     <t>TestCase_Sales_20: Submit random sales variation 20</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 191, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 199, Date: Today</t>
   </si>
   <si>
     <t>TC115</t>
@@ -1451,7 +1451,7 @@
     <t>TestCase_Sales_21: Submit random sales variation 21</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 113, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 195, Date: Today</t>
   </si>
   <si>
     <t>TC116</t>
@@ -1460,7 +1460,7 @@
     <t>TestCase_Sales_22: Submit random sales variation 22</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 78, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 191, Date: Today</t>
   </si>
   <si>
     <t>TC117</t>
@@ -1469,7 +1469,7 @@
     <t>TestCase_Sales_23: Submit random sales variation 23</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 161, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 157, Date: Today</t>
   </si>
   <si>
     <t>TC118</t>
@@ -1478,7 +1478,7 @@
     <t>TestCase_Sales_24: Submit random sales variation 24</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 182, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 184, Date: Today</t>
   </si>
   <si>
     <t>TC119</t>
@@ -1487,7 +1487,7 @@
     <t>TestCase_Sales_25: Submit random sales variation 25</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 194, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 70, Date: Today</t>
   </si>
   <si>
     <t>TC120</t>
@@ -1496,7 +1496,7 @@
     <t>TestCase_Sales_26: Submit random sales variation 26</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 139, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 90, Date: Today</t>
   </si>
   <si>
     <t>TC121</t>
@@ -1505,7 +1505,7 @@
     <t>TestCase_Sales_27: Submit random sales variation 27</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 20, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 70, Date: Today</t>
   </si>
   <si>
     <t>TC122</t>
@@ -1514,7 +1514,7 @@
     <t>TestCase_Sales_28: Submit random sales variation 28</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 110, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 139, Date: Today</t>
   </si>
   <si>
     <t>TC123</t>
@@ -1523,7 +1523,7 @@
     <t>TestCase_Sales_29: Submit random sales variation 29</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 93, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 37, Date: Today</t>
   </si>
   <si>
     <t>TC124</t>
@@ -1532,7 +1532,7 @@
     <t>TestCase_Sales_30: Submit random sales variation 30</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 105, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 184, Date: Today</t>
   </si>
   <si>
     <t>TC125</t>
@@ -1541,7 +1541,7 @@
     <t>TestCase_Sales_31: Submit random sales variation 31</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 23, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 5, Date: Today</t>
   </si>
   <si>
     <t>TC126</t>
@@ -1550,7 +1550,7 @@
     <t>TestCase_Sales_32: Submit random sales variation 32</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 65, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 101, Date: Today</t>
   </si>
   <si>
     <t>TC127</t>
@@ -1559,7 +1559,7 @@
     <t>TestCase_Sales_33: Submit random sales variation 33</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 135, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 13, Date: Today</t>
   </si>
   <si>
     <t>TC128</t>
@@ -1568,7 +1568,7 @@
     <t>TestCase_Sales_34: Submit random sales variation 34</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 156, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 63, Date: Today</t>
   </si>
   <si>
     <t>TC129</t>
@@ -1577,7 +1577,7 @@
     <t>TestCase_Sales_35: Submit random sales variation 35</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 70, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 49, Date: Today</t>
   </si>
   <si>
     <t>TC130</t>
@@ -1586,7 +1586,7 @@
     <t>TestCase_Sales_36: Submit random sales variation 36</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 143, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 111, Date: Today</t>
   </si>
   <si>
     <t>TC131</t>
@@ -1595,7 +1595,7 @@
     <t>TestCase_Sales_37: Submit random sales variation 37</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 105, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 100, Date: Today</t>
   </si>
   <si>
     <t>TC132</t>
@@ -1604,7 +1604,7 @@
     <t>TestCase_Sales_38: Submit random sales variation 38</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 198, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 19, Date: Today</t>
   </si>
   <si>
     <t>TC133</t>
@@ -1613,7 +1613,7 @@
     <t>TestCase_Sales_39: Submit random sales variation 39</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 108, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 174, Date: Today</t>
   </si>
   <si>
     <t>TC134</t>
@@ -1622,7 +1622,7 @@
     <t>TestCase_Sales_40: Submit random sales variation 40</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 5, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 144, Date: Today</t>
   </si>
   <si>
     <t>TC135</t>
@@ -1631,7 +1631,7 @@
     <t>TestCase_Sales_41: Submit random sales variation 41</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 25, Date: Today</t>
+    <t>Item: "Item 2", Quantity: 107, Date: Today</t>
   </si>
   <si>
     <t>TC136</t>
@@ -1640,7 +1640,7 @@
     <t>TestCase_Sales_42: Submit random sales variation 42</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 173, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 72, Date: Today</t>
   </si>
   <si>
     <t>TC137</t>
@@ -1649,7 +1649,7 @@
     <t>TestCase_Sales_43: Submit random sales variation 43</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 14, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 42, Date: Today</t>
   </si>
   <si>
     <t>TC138</t>
@@ -1658,7 +1658,7 @@
     <t>TestCase_Sales_44: Submit random sales variation 44</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 91, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 178, Date: Today</t>
   </si>
   <si>
     <t>TC139</t>
@@ -1667,7 +1667,7 @@
     <t>TestCase_Sales_45: Submit random sales variation 45</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 152, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 93, Date: Today</t>
   </si>
   <si>
     <t>TC140</t>
@@ -1676,16 +1676,13 @@
     <t>TestCase_Sales_46: Submit random sales variation 46</t>
   </si>
   <si>
-    <t>Item: "Item 2", Quantity: 47, Date: Today</t>
-  </si>
-  <si>
     <t>TC141</t>
   </si>
   <si>
     <t>TestCase_Sales_47: Submit random sales variation 47</t>
   </si>
   <si>
-    <t>Item: "Item 3", Quantity: 161, Date: Today</t>
+    <t>Item: "Item 3", Quantity: 115, Date: Today</t>
   </si>
   <si>
     <t>TC142</t>
@@ -1694,7 +1691,7 @@
     <t>TestCase_Sales_48: Submit random sales variation 48</t>
   </si>
   <si>
-    <t>Item: "Item 4", Quantity: 178, Date: Today</t>
+    <t>Item: "Item 4", Quantity: 114, Date: Today</t>
   </si>
   <si>
     <t>TC143</t>
@@ -1703,7 +1700,7 @@
     <t>TestCase_Sales_49: Submit random sales variation 49</t>
   </si>
   <si>
-    <t>Item: "Item 5", Quantity: 131, Date: Today</t>
+    <t>Item: "Item 5", Quantity: 130, Date: Today</t>
   </si>
   <si>
     <t>TC144</t>
@@ -1712,7 +1709,7 @@
     <t>TestCase_Sales_50: Submit random sales variation 50</t>
   </si>
   <si>
-    <t>Item: "Item 1", Quantity: 37, Date: Today</t>
+    <t>Item: "Item 1", Quantity: 200, Date: Today</t>
   </si>
   <si>
     <t>TC145</t>
@@ -2876,151 +2873,157 @@
     <t>TC251</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_09: Score 97 shows "Thriving" verdict</t>
+    <t>TestCase_HealthScore_09: Score 46 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 46</t>
+  </si>
+  <si>
+    <t>Verdict: "Immediate Action Needed" displayed</t>
+  </si>
+  <si>
+    <t>Verdict matched expected business logic</t>
+  </si>
+  <si>
+    <t>TC252</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_10: Score 78 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 78</t>
+  </si>
+  <si>
+    <t>Verdict: "Work in Progress" displayed</t>
+  </si>
+  <si>
+    <t>TC253</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_11: Score 40 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 40</t>
+  </si>
+  <si>
+    <t>TC254</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_12: Score 83 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 83</t>
+  </si>
+  <si>
+    <t>Verdict: "Thriving" displayed</t>
+  </si>
+  <si>
+    <t>TC255</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_13: Score 61 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 61</t>
+  </si>
+  <si>
+    <t>TC256</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_14: Score 77 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 77</t>
+  </si>
+  <si>
+    <t>TC257</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_15: Score 21 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 21</t>
+  </si>
+  <si>
+    <t>TC258</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_16: Score 92 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 92</t>
+  </si>
+  <si>
+    <t>TC259</t>
+  </si>
+  <si>
+    <t>TestCase_HealthScore_17: Score 97 shows "Thriving" verdict</t>
   </si>
   <si>
     <t>Simulated score: 97</t>
   </si>
   <si>
-    <t>Verdict: "Thriving" displayed</t>
-  </si>
-  <si>
-    <t>Verdict matched expected business logic</t>
-  </si>
-  <si>
-    <t>TC252</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_10: Score 75 shows "Work in Progress" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 75</t>
-  </si>
-  <si>
-    <t>Verdict: "Work in Progress" displayed</t>
-  </si>
-  <si>
-    <t>TC253</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_11: Score 92 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 92</t>
-  </si>
-  <si>
-    <t>TC254</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_12: Score 49 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 49</t>
-  </si>
-  <si>
-    <t>Verdict: "Immediate Action Needed" displayed</t>
-  </si>
-  <si>
-    <t>TC255</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_13: Score 82 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 82</t>
-  </si>
-  <si>
-    <t>TC256</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_14: Score 10 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 10</t>
-  </si>
-  <si>
-    <t>TC257</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_15: Score 42 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 42</t>
-  </si>
-  <si>
-    <t>TC258</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_16: Score 49 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>TC259</t>
-  </si>
-  <si>
-    <t>TestCase_HealthScore_17: Score 31 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 31</t>
-  </si>
-  <si>
     <t>TC260</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_18: Score 41 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 41</t>
+    <t>TestCase_HealthScore_18: Score 98 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 98</t>
   </si>
   <si>
     <t>TC261</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_19: Score 5 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 5</t>
+    <t>TestCase_HealthScore_19: Score 20 shows "Immediate Action Needed" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 20</t>
   </si>
   <si>
     <t>TC262</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_20: Score 82 shows "Thriving" verdict</t>
+    <t>TestCase_HealthScore_20: Score 94 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 94</t>
   </si>
   <si>
     <t>TC263</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_21: Score 83 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 83</t>
+    <t>TestCase_HealthScore_21: Score 90 shows "Thriving" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 90</t>
   </si>
   <si>
     <t>TC264</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_22: Score 89 shows "Thriving" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 89</t>
+    <t>TestCase_HealthScore_22: Score 71 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 71</t>
   </si>
   <si>
     <t>TC265</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_23: Score 14 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 14</t>
+    <t>TestCase_HealthScore_23: Score 60 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 60</t>
   </si>
   <si>
     <t>TC266</t>
   </si>
   <si>
-    <t>TestCase_HealthScore_24: Score 3 shows "Immediate Action Needed" verdict</t>
-  </si>
-  <si>
-    <t>Simulated score: 3</t>
+    <t>TestCase_HealthScore_24: Score 54 shows "Work in Progress" verdict</t>
+  </si>
+  <si>
+    <t>Simulated score: 54</t>
   </si>
   <si>
     <t>TC267</t>
@@ -4502,7 +4505,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="11">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>1</v>
@@ -4531,7 +4534,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="13">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>1</v>
@@ -4560,7 +4563,7 @@
         <v>9</v>
       </c>
       <c r="H4" s="11">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>1</v>
@@ -4589,7 +4592,7 @@
         <v>9</v>
       </c>
       <c r="H5" s="13">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>1</v>
@@ -4618,7 +4621,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="11">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>1</v>
@@ -4647,7 +4650,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="13">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>1</v>
@@ -4676,7 +4679,7 @@
         <v>9</v>
       </c>
       <c r="H8" s="11">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>1</v>
@@ -4705,7 +4708,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="13">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>1</v>
@@ -4734,7 +4737,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="11">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>1</v>
@@ -4763,7 +4766,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="13">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>1</v>
@@ -4792,7 +4795,7 @@
         <v>9</v>
       </c>
       <c r="H12" s="11">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>1</v>
@@ -4821,7 +4824,7 @@
         <v>9</v>
       </c>
       <c r="H13" s="13">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>1</v>
@@ -4850,7 +4853,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="11">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>1</v>
@@ -4879,7 +4882,7 @@
         <v>9</v>
       </c>
       <c r="H15" s="13">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>1</v>
@@ -4908,7 +4911,7 @@
         <v>9</v>
       </c>
       <c r="H16" s="11">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>1</v>
@@ -4937,7 +4940,7 @@
         <v>9</v>
       </c>
       <c r="H17" s="13">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>1</v>
@@ -4966,7 +4969,7 @@
         <v>9</v>
       </c>
       <c r="H18" s="11">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>1</v>
@@ -4995,7 +4998,7 @@
         <v>9</v>
       </c>
       <c r="H19" s="13">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>1</v>
@@ -5024,7 +5027,7 @@
         <v>9</v>
       </c>
       <c r="H20" s="11">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>1</v>
@@ -5053,7 +5056,7 @@
         <v>9</v>
       </c>
       <c r="H21" s="13">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>1</v>
@@ -5082,7 +5085,7 @@
         <v>9</v>
       </c>
       <c r="H22" s="11">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>1</v>
@@ -5111,7 +5114,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="13">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>1</v>
@@ -5140,7 +5143,7 @@
         <v>9</v>
       </c>
       <c r="H24" s="11">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>1</v>
@@ -5169,7 +5172,7 @@
         <v>9</v>
       </c>
       <c r="H25" s="13">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>1</v>
@@ -5198,7 +5201,7 @@
         <v>9</v>
       </c>
       <c r="H26" s="11">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>1</v>
@@ -5227,7 +5230,7 @@
         <v>9</v>
       </c>
       <c r="H27" s="13">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>1</v>
@@ -5256,7 +5259,7 @@
         <v>9</v>
       </c>
       <c r="H28" s="11">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>1</v>
@@ -5285,7 +5288,7 @@
         <v>9</v>
       </c>
       <c r="H29" s="13">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>1</v>
@@ -5314,7 +5317,7 @@
         <v>9</v>
       </c>
       <c r="H30" s="11">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>1</v>
@@ -5343,7 +5346,7 @@
         <v>9</v>
       </c>
       <c r="H31" s="13">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>1</v>
@@ -5372,7 +5375,7 @@
         <v>9</v>
       </c>
       <c r="H32" s="11">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>1</v>
@@ -5401,7 +5404,7 @@
         <v>9</v>
       </c>
       <c r="H33" s="13">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>1</v>
@@ -5430,7 +5433,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="11">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>1</v>
@@ -5459,7 +5462,7 @@
         <v>9</v>
       </c>
       <c r="H35" s="13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I35" s="13" t="s">
         <v>1</v>
@@ -5488,7 +5491,7 @@
         <v>9</v>
       </c>
       <c r="H36" s="11">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>1</v>
@@ -5517,7 +5520,7 @@
         <v>9</v>
       </c>
       <c r="H37" s="13">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>1</v>
@@ -5546,7 +5549,7 @@
         <v>9</v>
       </c>
       <c r="H38" s="11">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>1</v>
@@ -5575,7 +5578,7 @@
         <v>9</v>
       </c>
       <c r="H39" s="13">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>1</v>
@@ -5604,7 +5607,7 @@
         <v>9</v>
       </c>
       <c r="H40" s="11">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>1</v>
@@ -5633,7 +5636,7 @@
         <v>9</v>
       </c>
       <c r="H41" s="13">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>1</v>
@@ -5662,7 +5665,7 @@
         <v>9</v>
       </c>
       <c r="H42" s="11">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>1</v>
@@ -5691,7 +5694,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="13">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="I43" s="13" t="s">
         <v>1</v>
@@ -5720,7 +5723,7 @@
         <v>9</v>
       </c>
       <c r="H44" s="11">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>1</v>
@@ -5749,7 +5752,7 @@
         <v>9</v>
       </c>
       <c r="H45" s="13">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="I45" s="13" t="s">
         <v>1</v>
@@ -5778,7 +5781,7 @@
         <v>9</v>
       </c>
       <c r="H46" s="11">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>1</v>
@@ -5807,7 +5810,7 @@
         <v>9</v>
       </c>
       <c r="H47" s="13">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="I47" s="13" t="s">
         <v>1</v>
@@ -5836,7 +5839,7 @@
         <v>9</v>
       </c>
       <c r="H48" s="11">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="I48" s="11" t="s">
         <v>1</v>
@@ -5865,7 +5868,7 @@
         <v>9</v>
       </c>
       <c r="H49" s="13">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="I49" s="13" t="s">
         <v>1</v>
@@ -5894,7 +5897,7 @@
         <v>9</v>
       </c>
       <c r="H50" s="11">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="I50" s="11" t="s">
         <v>1</v>
@@ -5923,7 +5926,7 @@
         <v>9</v>
       </c>
       <c r="H51" s="13">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>1</v>
@@ -5952,7 +5955,7 @@
         <v>9</v>
       </c>
       <c r="H52" s="11">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I52" s="11" t="s">
         <v>1</v>
@@ -5981,7 +5984,7 @@
         <v>9</v>
       </c>
       <c r="H53" s="13">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="I53" s="13" t="s">
         <v>1</v>
@@ -6010,7 +6013,7 @@
         <v>9</v>
       </c>
       <c r="H54" s="11">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="I54" s="11" t="s">
         <v>1</v>
@@ -6039,7 +6042,7 @@
         <v>9</v>
       </c>
       <c r="H55" s="13">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="I55" s="13" t="s">
         <v>1</v>
@@ -6068,7 +6071,7 @@
         <v>9</v>
       </c>
       <c r="H56" s="11">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>1</v>
@@ -6097,7 +6100,7 @@
         <v>9</v>
       </c>
       <c r="H57" s="13">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I57" s="13" t="s">
         <v>1</v>
@@ -6126,7 +6129,7 @@
         <v>9</v>
       </c>
       <c r="H58" s="11">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I58" s="11" t="s">
         <v>1</v>
@@ -6155,7 +6158,7 @@
         <v>9</v>
       </c>
       <c r="H59" s="13">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="I59" s="13" t="s">
         <v>1</v>
@@ -6184,7 +6187,7 @@
         <v>9</v>
       </c>
       <c r="H60" s="11">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I60" s="11" t="s">
         <v>1</v>
@@ -6213,7 +6216,7 @@
         <v>9</v>
       </c>
       <c r="H61" s="13">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="I61" s="13" t="s">
         <v>1</v>
@@ -6242,7 +6245,7 @@
         <v>9</v>
       </c>
       <c r="H62" s="11">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="I62" s="11" t="s">
         <v>1</v>
@@ -6271,7 +6274,7 @@
         <v>9</v>
       </c>
       <c r="H63" s="13">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>1</v>
@@ -6300,7 +6303,7 @@
         <v>9</v>
       </c>
       <c r="H64" s="11">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="I64" s="11" t="s">
         <v>1</v>
@@ -6329,7 +6332,7 @@
         <v>9</v>
       </c>
       <c r="H65" s="13">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I65" s="13" t="s">
         <v>1</v>
@@ -6358,7 +6361,7 @@
         <v>9</v>
       </c>
       <c r="H66" s="11">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="I66" s="11" t="s">
         <v>1</v>
@@ -6387,7 +6390,7 @@
         <v>9</v>
       </c>
       <c r="H67" s="13">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>1</v>
@@ -6416,7 +6419,7 @@
         <v>9</v>
       </c>
       <c r="H68" s="11">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="I68" s="11" t="s">
         <v>1</v>
@@ -6445,7 +6448,7 @@
         <v>9</v>
       </c>
       <c r="H69" s="13">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>1</v>
@@ -6474,7 +6477,7 @@
         <v>9</v>
       </c>
       <c r="H70" s="11">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="I70" s="11" t="s">
         <v>1</v>
@@ -6503,7 +6506,7 @@
         <v>9</v>
       </c>
       <c r="H71" s="13">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>1</v>
@@ -6532,7 +6535,7 @@
         <v>9</v>
       </c>
       <c r="H72" s="11">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="I72" s="11" t="s">
         <v>1</v>
@@ -6561,7 +6564,7 @@
         <v>9</v>
       </c>
       <c r="H73" s="13">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>1</v>
@@ -6590,7 +6593,7 @@
         <v>9</v>
       </c>
       <c r="H74" s="11">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="I74" s="11" t="s">
         <v>1</v>
@@ -6619,7 +6622,7 @@
         <v>9</v>
       </c>
       <c r="H75" s="13">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>1</v>
@@ -6648,7 +6651,7 @@
         <v>9</v>
       </c>
       <c r="H76" s="11">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="I76" s="11" t="s">
         <v>1</v>
@@ -6677,7 +6680,7 @@
         <v>9</v>
       </c>
       <c r="H77" s="13">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>1</v>
@@ -6706,7 +6709,7 @@
         <v>9</v>
       </c>
       <c r="H78" s="11">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="I78" s="11" t="s">
         <v>1</v>
@@ -6735,7 +6738,7 @@
         <v>9</v>
       </c>
       <c r="H79" s="13">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>1</v>
@@ -6764,7 +6767,7 @@
         <v>9</v>
       </c>
       <c r="H80" s="11">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="I80" s="11" t="s">
         <v>1</v>
@@ -6793,7 +6796,7 @@
         <v>9</v>
       </c>
       <c r="H81" s="13">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I81" s="13" t="s">
         <v>1</v>
@@ -6822,7 +6825,7 @@
         <v>9</v>
       </c>
       <c r="H82" s="11">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I82" s="11" t="s">
         <v>1</v>
@@ -6851,7 +6854,7 @@
         <v>9</v>
       </c>
       <c r="H83" s="13">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I83" s="13" t="s">
         <v>1</v>
@@ -6880,7 +6883,7 @@
         <v>9</v>
       </c>
       <c r="H84" s="11">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="I84" s="11" t="s">
         <v>1</v>
@@ -6909,7 +6912,7 @@
         <v>9</v>
       </c>
       <c r="H85" s="13">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>1</v>
@@ -6938,7 +6941,7 @@
         <v>9</v>
       </c>
       <c r="H86" s="11">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="I86" s="11" t="s">
         <v>1</v>
@@ -6967,7 +6970,7 @@
         <v>9</v>
       </c>
       <c r="H87" s="13">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>1</v>
@@ -6996,7 +6999,7 @@
         <v>9</v>
       </c>
       <c r="H88" s="11">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I88" s="11" t="s">
         <v>1</v>
@@ -7025,7 +7028,7 @@
         <v>9</v>
       </c>
       <c r="H89" s="13">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="I89" s="13" t="s">
         <v>1</v>
@@ -7054,7 +7057,7 @@
         <v>9</v>
       </c>
       <c r="H90" s="11">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I90" s="11" t="s">
         <v>1</v>
@@ -7083,7 +7086,7 @@
         <v>9</v>
       </c>
       <c r="H91" s="13">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="I91" s="13" t="s">
         <v>1</v>
@@ -7112,7 +7115,7 @@
         <v>9</v>
       </c>
       <c r="H92" s="11">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I92" s="11" t="s">
         <v>1</v>
@@ -7141,7 +7144,7 @@
         <v>9</v>
       </c>
       <c r="H93" s="13">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I93" s="13" t="s">
         <v>1</v>
@@ -7170,7 +7173,7 @@
         <v>9</v>
       </c>
       <c r="H94" s="11">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="I94" s="11" t="s">
         <v>1</v>
@@ -7199,7 +7202,7 @@
         <v>9</v>
       </c>
       <c r="H95" s="13">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="I95" s="13" t="s">
         <v>1</v>
@@ -7228,7 +7231,7 @@
         <v>9</v>
       </c>
       <c r="H96" s="11">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="I96" s="11" t="s">
         <v>1</v>
@@ -7257,7 +7260,7 @@
         <v>9</v>
       </c>
       <c r="H97" s="13">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="I97" s="13" t="s">
         <v>1</v>
@@ -7286,7 +7289,7 @@
         <v>9</v>
       </c>
       <c r="H98" s="11">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="I98" s="11" t="s">
         <v>1</v>
@@ -7315,7 +7318,7 @@
         <v>9</v>
       </c>
       <c r="H99" s="13">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="I99" s="13" t="s">
         <v>1</v>
@@ -7344,7 +7347,7 @@
         <v>9</v>
       </c>
       <c r="H100" s="11">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="I100" s="11" t="s">
         <v>1</v>
@@ -7373,7 +7376,7 @@
         <v>9</v>
       </c>
       <c r="H101" s="13">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I101" s="13" t="s">
         <v>1</v>
@@ -7402,7 +7405,7 @@
         <v>9</v>
       </c>
       <c r="H102" s="11">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="I102" s="11" t="s">
         <v>1</v>
@@ -7431,7 +7434,7 @@
         <v>9</v>
       </c>
       <c r="H103" s="13">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="I103" s="13" t="s">
         <v>1</v>
@@ -7460,7 +7463,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="11">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I104" s="11" t="s">
         <v>1</v>
@@ -7489,7 +7492,7 @@
         <v>9</v>
       </c>
       <c r="H105" s="13">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I105" s="13" t="s">
         <v>1</v>
@@ -7518,7 +7521,7 @@
         <v>9</v>
       </c>
       <c r="H106" s="11">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="I106" s="11" t="s">
         <v>1</v>
@@ -7547,7 +7550,7 @@
         <v>9</v>
       </c>
       <c r="H107" s="13">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="I107" s="13" t="s">
         <v>1</v>
@@ -7576,7 +7579,7 @@
         <v>9</v>
       </c>
       <c r="H108" s="11">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="I108" s="11" t="s">
         <v>1</v>
@@ -7605,7 +7608,7 @@
         <v>9</v>
       </c>
       <c r="H109" s="13">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I109" s="13" t="s">
         <v>1</v>
@@ -7634,7 +7637,7 @@
         <v>9</v>
       </c>
       <c r="H110" s="11">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I110" s="11" t="s">
         <v>1</v>
@@ -7663,7 +7666,7 @@
         <v>9</v>
       </c>
       <c r="H111" s="13">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="I111" s="13" t="s">
         <v>1</v>
@@ -7692,7 +7695,7 @@
         <v>9</v>
       </c>
       <c r="H112" s="11">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="I112" s="11" t="s">
         <v>1</v>
@@ -7721,7 +7724,7 @@
         <v>9</v>
       </c>
       <c r="H113" s="13">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="I113" s="13" t="s">
         <v>1</v>
@@ -7750,7 +7753,7 @@
         <v>9</v>
       </c>
       <c r="H114" s="11">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="I114" s="11" t="s">
         <v>1</v>
@@ -7779,7 +7782,7 @@
         <v>9</v>
       </c>
       <c r="H115" s="13">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="I115" s="13" t="s">
         <v>1</v>
@@ -7808,7 +7811,7 @@
         <v>9</v>
       </c>
       <c r="H116" s="11">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="I116" s="11" t="s">
         <v>1</v>
@@ -7837,7 +7840,7 @@
         <v>9</v>
       </c>
       <c r="H117" s="13">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="I117" s="13" t="s">
         <v>1</v>
@@ -7866,7 +7869,7 @@
         <v>9</v>
       </c>
       <c r="H118" s="11">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="I118" s="11" t="s">
         <v>1</v>
@@ -7895,7 +7898,7 @@
         <v>9</v>
       </c>
       <c r="H119" s="13">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="I119" s="13" t="s">
         <v>1</v>
@@ -7924,7 +7927,7 @@
         <v>9</v>
       </c>
       <c r="H120" s="11">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="I120" s="11" t="s">
         <v>1</v>
@@ -7953,7 +7956,7 @@
         <v>9</v>
       </c>
       <c r="H121" s="13">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="I121" s="13" t="s">
         <v>1</v>
@@ -7982,7 +7985,7 @@
         <v>9</v>
       </c>
       <c r="H122" s="11">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I122" s="11" t="s">
         <v>1</v>
@@ -8011,7 +8014,7 @@
         <v>9</v>
       </c>
       <c r="H123" s="13">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I123" s="13" t="s">
         <v>1</v>
@@ -8040,7 +8043,7 @@
         <v>9</v>
       </c>
       <c r="H124" s="11">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I124" s="11" t="s">
         <v>1</v>
@@ -8069,7 +8072,7 @@
         <v>9</v>
       </c>
       <c r="H125" s="13">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="I125" s="13" t="s">
         <v>1</v>
@@ -8098,7 +8101,7 @@
         <v>9</v>
       </c>
       <c r="H126" s="11">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="I126" s="11" t="s">
         <v>1</v>
@@ -8127,7 +8130,7 @@
         <v>9</v>
       </c>
       <c r="H127" s="13">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="I127" s="13" t="s">
         <v>1</v>
@@ -8156,7 +8159,7 @@
         <v>9</v>
       </c>
       <c r="H128" s="11">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="I128" s="11" t="s">
         <v>1</v>
@@ -8185,7 +8188,7 @@
         <v>9</v>
       </c>
       <c r="H129" s="13">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="I129" s="13" t="s">
         <v>1</v>
@@ -8243,7 +8246,7 @@
         <v>9</v>
       </c>
       <c r="H131" s="13">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="I131" s="13" t="s">
         <v>1</v>
@@ -8272,7 +8275,7 @@
         <v>9</v>
       </c>
       <c r="H132" s="11">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I132" s="11" t="s">
         <v>1</v>
@@ -8301,7 +8304,7 @@
         <v>9</v>
       </c>
       <c r="H133" s="13">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="I133" s="13" t="s">
         <v>1</v>
@@ -8330,7 +8333,7 @@
         <v>9</v>
       </c>
       <c r="H134" s="11">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="I134" s="11" t="s">
         <v>1</v>
@@ -8359,7 +8362,7 @@
         <v>9</v>
       </c>
       <c r="H135" s="13">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="I135" s="13" t="s">
         <v>1</v>
@@ -8388,7 +8391,7 @@
         <v>9</v>
       </c>
       <c r="H136" s="11">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="I136" s="11" t="s">
         <v>1</v>
@@ -8417,7 +8420,7 @@
         <v>9</v>
       </c>
       <c r="H137" s="13">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I137" s="13" t="s">
         <v>1</v>
@@ -8446,7 +8449,7 @@
         <v>9</v>
       </c>
       <c r="H138" s="11">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="I138" s="11" t="s">
         <v>1</v>
@@ -8475,7 +8478,7 @@
         <v>9</v>
       </c>
       <c r="H139" s="13">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="I139" s="13" t="s">
         <v>1</v>
@@ -8504,7 +8507,7 @@
         <v>9</v>
       </c>
       <c r="H140" s="11">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I140" s="11" t="s">
         <v>1</v>
@@ -8521,7 +8524,7 @@
         <v>553</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>554</v>
+        <v>524</v>
       </c>
       <c r="E141" s="13" t="s">
         <v>460</v>
@@ -8533,7 +8536,7 @@
         <v>9</v>
       </c>
       <c r="H141" s="13">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="I141" s="13" t="s">
         <v>1</v>
@@ -8541,16 +8544,16 @@
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B142" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C142" s="11" t="s">
+        <v>555</v>
+      </c>
+      <c r="D142" s="11" t="s">
         <v>556</v>
-      </c>
-      <c r="D142" s="11" t="s">
-        <v>557</v>
       </c>
       <c r="E142" s="11" t="s">
         <v>460</v>
@@ -8562,7 +8565,7 @@
         <v>9</v>
       </c>
       <c r="H142" s="11">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="I142" s="11" t="s">
         <v>1</v>
@@ -8570,16 +8573,16 @@
     </row>
     <row r="143" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B143" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C143" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="D143" s="13" t="s">
         <v>559</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>560</v>
       </c>
       <c r="E143" s="13" t="s">
         <v>460</v>
@@ -8591,7 +8594,7 @@
         <v>9</v>
       </c>
       <c r="H143" s="13">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>1</v>
@@ -8599,16 +8602,16 @@
     </row>
     <row r="144" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B144" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C144" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D144" s="11" t="s">
         <v>562</v>
-      </c>
-      <c r="D144" s="11" t="s">
-        <v>563</v>
       </c>
       <c r="E144" s="11" t="s">
         <v>460</v>
@@ -8620,7 +8623,7 @@
         <v>9</v>
       </c>
       <c r="H144" s="11">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="I144" s="11" t="s">
         <v>1</v>
@@ -8628,16 +8631,16 @@
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="13" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B145" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C145" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="D145" s="13" t="s">
         <v>565</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>566</v>
       </c>
       <c r="E145" s="13" t="s">
         <v>460</v>
@@ -8649,7 +8652,7 @@
         <v>9</v>
       </c>
       <c r="H145" s="13">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I145" s="13" t="s">
         <v>1</v>
@@ -8657,28 +8660,28 @@
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C146" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="D146" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="D146" s="11" t="s">
+      <c r="E146" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="E146" s="11" t="s">
+      <c r="F146" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="F146" s="11" t="s">
-        <v>571</v>
-      </c>
       <c r="G146" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H146" s="11">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I146" s="11" t="s">
         <v>1</v>
@@ -8686,28 +8689,28 @@
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B147" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C147" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="D147" s="13" t="s">
         <v>573</v>
       </c>
-      <c r="D147" s="13" t="s">
+      <c r="E147" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="E147" s="13" t="s">
+      <c r="F147" s="13" t="s">
         <v>575</v>
       </c>
-      <c r="F147" s="13" t="s">
-        <v>576</v>
-      </c>
       <c r="G147" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H147" s="13">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="I147" s="13" t="s">
         <v>1</v>
@@ -8715,28 +8718,28 @@
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B148" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C148" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="D148" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="D148" s="11" t="s">
+      <c r="E148" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="E148" s="11" t="s">
+      <c r="F148" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="F148" s="11" t="s">
-        <v>581</v>
-      </c>
       <c r="G148" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H148" s="11">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="I148" s="11" t="s">
         <v>1</v>
@@ -8744,28 +8747,28 @@
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="13" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B149" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C149" s="13" t="s">
+        <v>582</v>
+      </c>
+      <c r="D149" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="D149" s="13" t="s">
+      <c r="E149" s="13" t="s">
         <v>584</v>
       </c>
-      <c r="E149" s="13" t="s">
+      <c r="F149" s="13" t="s">
         <v>585</v>
       </c>
-      <c r="F149" s="13" t="s">
-        <v>586</v>
-      </c>
       <c r="G149" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H149" s="13">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I149" s="13" t="s">
         <v>1</v>
@@ -8773,28 +8776,28 @@
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C150" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="D150" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="D150" s="11" t="s">
+      <c r="E150" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="E150" s="11" t="s">
+      <c r="F150" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="F150" s="11" t="s">
-        <v>591</v>
-      </c>
       <c r="G150" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H150" s="11">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="I150" s="11" t="s">
         <v>1</v>
@@ -8802,28 +8805,28 @@
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="13" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B151" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C151" s="13" t="s">
+        <v>592</v>
+      </c>
+      <c r="D151" s="13" t="s">
         <v>593</v>
       </c>
-      <c r="D151" s="13" t="s">
+      <c r="E151" s="13" t="s">
         <v>594</v>
       </c>
-      <c r="E151" s="13" t="s">
+      <c r="F151" s="13" t="s">
         <v>595</v>
       </c>
-      <c r="F151" s="13" t="s">
-        <v>596</v>
-      </c>
       <c r="G151" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H151" s="13">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I151" s="13" t="s">
         <v>1</v>
@@ -8831,28 +8834,28 @@
     </row>
     <row r="152" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B152" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C152" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="D152" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="D152" s="11" t="s">
+      <c r="E152" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="E152" s="11" t="s">
+      <c r="F152" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="F152" s="11" t="s">
-        <v>601</v>
-      </c>
       <c r="G152" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H152" s="11">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="I152" s="11" t="s">
         <v>1</v>
@@ -8860,28 +8863,28 @@
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B153" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C153" s="13" t="s">
+        <v>602</v>
+      </c>
+      <c r="D153" s="13" t="s">
         <v>603</v>
       </c>
-      <c r="D153" s="13" t="s">
+      <c r="E153" s="13" t="s">
         <v>604</v>
       </c>
-      <c r="E153" s="13" t="s">
+      <c r="F153" s="13" t="s">
         <v>605</v>
       </c>
-      <c r="F153" s="13" t="s">
-        <v>606</v>
-      </c>
       <c r="G153" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H153" s="13">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I153" s="13" t="s">
         <v>1</v>
@@ -8889,28 +8892,28 @@
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B154" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C154" s="11" t="s">
+        <v>607</v>
+      </c>
+      <c r="D154" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="D154" s="11" t="s">
+      <c r="E154" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="E154" s="11" t="s">
+      <c r="F154" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F154" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G154" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H154" s="11">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I154" s="11" t="s">
         <v>1</v>
@@ -8918,28 +8921,28 @@
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="13" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B155" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C155" s="13" t="s">
+        <v>612</v>
+      </c>
+      <c r="D155" s="13" t="s">
         <v>613</v>
       </c>
-      <c r="D155" s="13" t="s">
-        <v>614</v>
-      </c>
       <c r="E155" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F155" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F155" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G155" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H155" s="13">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="I155" s="13" t="s">
         <v>1</v>
@@ -8947,28 +8950,28 @@
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B156" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C156" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="D156" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="D156" s="11" t="s">
-        <v>617</v>
-      </c>
       <c r="E156" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F156" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F156" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G156" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H156" s="11">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="I156" s="11" t="s">
         <v>1</v>
@@ -8976,28 +8979,28 @@
     </row>
     <row r="157" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="13" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B157" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C157" s="13" t="s">
+        <v>618</v>
+      </c>
+      <c r="D157" s="13" t="s">
         <v>619</v>
       </c>
-      <c r="D157" s="13" t="s">
-        <v>620</v>
-      </c>
       <c r="E157" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F157" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F157" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G157" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H157" s="13">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>1</v>
@@ -9005,28 +9008,28 @@
     </row>
     <row r="158" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B158" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C158" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="D158" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="D158" s="11" t="s">
-        <v>623</v>
-      </c>
       <c r="E158" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F158" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F158" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G158" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H158" s="11">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="I158" s="11" t="s">
         <v>1</v>
@@ -9034,28 +9037,28 @@
     </row>
     <row r="159" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="13" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B159" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C159" s="13" t="s">
+        <v>624</v>
+      </c>
+      <c r="D159" s="13" t="s">
         <v>625</v>
       </c>
-      <c r="D159" s="13" t="s">
-        <v>626</v>
-      </c>
       <c r="E159" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F159" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F159" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G159" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H159" s="13">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="I159" s="13" t="s">
         <v>1</v>
@@ -9063,28 +9066,28 @@
     </row>
     <row r="160" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B160" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C160" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="D160" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="D160" s="11" t="s">
-        <v>629</v>
-      </c>
       <c r="E160" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F160" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F160" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G160" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H160" s="11">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="I160" s="11" t="s">
         <v>1</v>
@@ -9092,28 +9095,28 @@
     </row>
     <row r="161" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="13" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B161" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C161" s="13" t="s">
+        <v>630</v>
+      </c>
+      <c r="D161" s="13" t="s">
         <v>631</v>
       </c>
-      <c r="D161" s="13" t="s">
-        <v>632</v>
-      </c>
       <c r="E161" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F161" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F161" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G161" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H161" s="13">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="I161" s="13" t="s">
         <v>1</v>
@@ -9121,28 +9124,28 @@
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B162" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C162" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="D162" s="11" t="s">
         <v>634</v>
       </c>
-      <c r="D162" s="11" t="s">
-        <v>635</v>
-      </c>
       <c r="E162" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F162" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F162" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G162" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H162" s="11">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I162" s="11" t="s">
         <v>1</v>
@@ -9150,28 +9153,28 @@
     </row>
     <row r="163" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="13" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B163" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C163" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="D163" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="D163" s="13" t="s">
-        <v>638</v>
-      </c>
       <c r="E163" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F163" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F163" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G163" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H163" s="13">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>1</v>
@@ -9179,28 +9182,28 @@
     </row>
     <row r="164" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B164" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C164" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="D164" s="11" t="s">
         <v>640</v>
       </c>
-      <c r="D164" s="11" t="s">
-        <v>641</v>
-      </c>
       <c r="E164" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F164" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F164" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G164" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H164" s="11">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="I164" s="11" t="s">
         <v>1</v>
@@ -9208,28 +9211,28 @@
     </row>
     <row r="165" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="13" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B165" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C165" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="D165" s="13" t="s">
         <v>643</v>
       </c>
-      <c r="D165" s="13" t="s">
-        <v>644</v>
-      </c>
       <c r="E165" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F165" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F165" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G165" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H165" s="13">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="I165" s="13" t="s">
         <v>1</v>
@@ -9237,28 +9240,28 @@
     </row>
     <row r="166" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B166" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C166" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="D166" s="11" t="s">
         <v>646</v>
       </c>
-      <c r="D166" s="11" t="s">
-        <v>647</v>
-      </c>
       <c r="E166" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F166" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F166" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G166" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H166" s="11">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="I166" s="11" t="s">
         <v>1</v>
@@ -9266,28 +9269,28 @@
     </row>
     <row r="167" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B167" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C167" s="13" t="s">
+        <v>648</v>
+      </c>
+      <c r="D167" s="13" t="s">
         <v>649</v>
       </c>
-      <c r="D167" s="13" t="s">
-        <v>650</v>
-      </c>
       <c r="E167" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F167" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F167" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G167" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H167" s="13">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="I167" s="13" t="s">
         <v>1</v>
@@ -9295,28 +9298,28 @@
     </row>
     <row r="168" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C168" s="11" t="s">
+        <v>651</v>
+      </c>
+      <c r="D168" s="11" t="s">
         <v>652</v>
       </c>
-      <c r="D168" s="11" t="s">
-        <v>653</v>
-      </c>
       <c r="E168" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F168" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F168" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G168" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H168" s="11">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="I168" s="11" t="s">
         <v>1</v>
@@ -9324,28 +9327,28 @@
     </row>
     <row r="169" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B169" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C169" s="13" t="s">
+        <v>654</v>
+      </c>
+      <c r="D169" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="D169" s="13" t="s">
-        <v>656</v>
-      </c>
       <c r="E169" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F169" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F169" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G169" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H169" s="13">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I169" s="13" t="s">
         <v>1</v>
@@ -9353,28 +9356,28 @@
     </row>
     <row r="170" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C170" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="D170" s="11" t="s">
         <v>658</v>
       </c>
-      <c r="D170" s="11" t="s">
-        <v>659</v>
-      </c>
       <c r="E170" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F170" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F170" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G170" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H170" s="11">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="I170" s="11" t="s">
         <v>1</v>
@@ -9382,28 +9385,28 @@
     </row>
     <row r="171" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B171" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C171" s="13" t="s">
+        <v>660</v>
+      </c>
+      <c r="D171" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="D171" s="13" t="s">
-        <v>662</v>
-      </c>
       <c r="E171" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F171" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F171" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G171" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H171" s="13">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="I171" s="13" t="s">
         <v>1</v>
@@ -9411,28 +9414,28 @@
     </row>
     <row r="172" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="11" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B172" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C172" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="D172" s="11" t="s">
         <v>664</v>
       </c>
-      <c r="D172" s="11" t="s">
-        <v>665</v>
-      </c>
       <c r="E172" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F172" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F172" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G172" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H172" s="11">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I172" s="11" t="s">
         <v>1</v>
@@ -9440,28 +9443,28 @@
     </row>
     <row r="173" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="13" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B173" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C173" s="13" t="s">
+        <v>666</v>
+      </c>
+      <c r="D173" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="D173" s="13" t="s">
-        <v>668</v>
-      </c>
       <c r="E173" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F173" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F173" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G173" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H173" s="13">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I173" s="13" t="s">
         <v>1</v>
@@ -9469,28 +9472,28 @@
     </row>
     <row r="174" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="11" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B174" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C174" s="11" t="s">
+        <v>669</v>
+      </c>
+      <c r="D174" s="11" t="s">
         <v>670</v>
       </c>
-      <c r="D174" s="11" t="s">
-        <v>671</v>
-      </c>
       <c r="E174" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F174" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F174" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G174" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H174" s="11">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I174" s="11" t="s">
         <v>1</v>
@@ -9498,28 +9501,28 @@
     </row>
     <row r="175" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="13" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B175" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C175" s="13" t="s">
+        <v>672</v>
+      </c>
+      <c r="D175" s="13" t="s">
         <v>673</v>
       </c>
-      <c r="D175" s="13" t="s">
-        <v>674</v>
-      </c>
       <c r="E175" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F175" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F175" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G175" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H175" s="13">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="I175" s="13" t="s">
         <v>1</v>
@@ -9527,28 +9530,28 @@
     </row>
     <row r="176" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="11" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B176" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C176" s="11" t="s">
+        <v>675</v>
+      </c>
+      <c r="D176" s="11" t="s">
         <v>676</v>
       </c>
-      <c r="D176" s="11" t="s">
-        <v>677</v>
-      </c>
       <c r="E176" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F176" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F176" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G176" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H176" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I176" s="11" t="s">
         <v>1</v>
@@ -9556,28 +9559,28 @@
     </row>
     <row r="177" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="13" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B177" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C177" s="13" t="s">
+        <v>678</v>
+      </c>
+      <c r="D177" s="13" t="s">
         <v>679</v>
       </c>
-      <c r="D177" s="13" t="s">
-        <v>680</v>
-      </c>
       <c r="E177" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F177" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F177" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G177" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H177" s="13">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="I177" s="13" t="s">
         <v>1</v>
@@ -9585,28 +9588,28 @@
     </row>
     <row r="178" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B178" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C178" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="D178" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="D178" s="11" t="s">
-        <v>683</v>
-      </c>
       <c r="E178" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F178" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F178" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G178" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H178" s="11">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I178" s="11" t="s">
         <v>1</v>
@@ -9614,28 +9617,28 @@
     </row>
     <row r="179" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="13" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B179" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C179" s="13" t="s">
+        <v>684</v>
+      </c>
+      <c r="D179" s="13" t="s">
         <v>685</v>
       </c>
-      <c r="D179" s="13" t="s">
-        <v>686</v>
-      </c>
       <c r="E179" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F179" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F179" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G179" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H179" s="13">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="I179" s="13" t="s">
         <v>1</v>
@@ -9643,28 +9646,28 @@
     </row>
     <row r="180" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B180" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C180" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="D180" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="D180" s="11" t="s">
-        <v>689</v>
-      </c>
       <c r="E180" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F180" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F180" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G180" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H180" s="11">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="I180" s="11" t="s">
         <v>1</v>
@@ -9672,28 +9675,28 @@
     </row>
     <row r="181" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="13" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B181" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C181" s="13" t="s">
+        <v>690</v>
+      </c>
+      <c r="D181" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="D181" s="13" t="s">
-        <v>692</v>
-      </c>
       <c r="E181" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F181" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F181" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G181" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H181" s="13">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="I181" s="13" t="s">
         <v>1</v>
@@ -9701,28 +9704,28 @@
     </row>
     <row r="182" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B182" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C182" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="D182" s="11" t="s">
         <v>694</v>
       </c>
-      <c r="D182" s="11" t="s">
-        <v>695</v>
-      </c>
       <c r="E182" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F182" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F182" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G182" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H182" s="11">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="I182" s="11" t="s">
         <v>1</v>
@@ -9730,28 +9733,28 @@
     </row>
     <row r="183" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="13" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B183" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C183" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="D183" s="13" t="s">
         <v>697</v>
       </c>
-      <c r="D183" s="13" t="s">
-        <v>698</v>
-      </c>
       <c r="E183" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F183" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F183" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G183" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H183" s="13">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="I183" s="13" t="s">
         <v>1</v>
@@ -9759,28 +9762,28 @@
     </row>
     <row r="184" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="11" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C184" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="D184" s="11" t="s">
         <v>700</v>
       </c>
-      <c r="D184" s="11" t="s">
-        <v>701</v>
-      </c>
       <c r="E184" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="F184" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="F184" s="11" t="s">
-        <v>611</v>
-      </c>
       <c r="G184" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H184" s="11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I184" s="11" t="s">
         <v>1</v>
@@ -9788,28 +9791,28 @@
     </row>
     <row r="185" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B185" s="13" t="s">
         <v>20</v>
       </c>
       <c r="C185" s="13" t="s">
+        <v>702</v>
+      </c>
+      <c r="D185" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="D185" s="13" t="s">
-        <v>704</v>
-      </c>
       <c r="E185" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F185" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F185" s="13" t="s">
-        <v>611</v>
-      </c>
       <c r="G185" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H185" s="13">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="I185" s="13" t="s">
         <v>1</v>
@@ -9817,28 +9820,28 @@
     </row>
     <row r="186" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B186" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C186" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="D186" s="11" t="s">
         <v>706</v>
       </c>
-      <c r="D186" s="11" t="s">
+      <c r="E186" s="11" t="s">
         <v>707</v>
       </c>
-      <c r="E186" s="11" t="s">
+      <c r="F186" s="11" t="s">
         <v>708</v>
       </c>
-      <c r="F186" s="11" t="s">
-        <v>709</v>
-      </c>
       <c r="G186" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H186" s="11">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="I186" s="11" t="s">
         <v>1</v>
@@ -9846,28 +9849,28 @@
     </row>
     <row r="187" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="13" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B187" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C187" s="13" t="s">
+        <v>710</v>
+      </c>
+      <c r="D187" s="13" t="s">
         <v>711</v>
       </c>
-      <c r="D187" s="13" t="s">
+      <c r="E187" s="13" t="s">
         <v>712</v>
       </c>
-      <c r="E187" s="13" t="s">
+      <c r="F187" s="13" t="s">
         <v>713</v>
       </c>
-      <c r="F187" s="13" t="s">
-        <v>714</v>
-      </c>
       <c r="G187" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H187" s="13">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="I187" s="13" t="s">
         <v>1</v>
@@ -9875,28 +9878,28 @@
     </row>
     <row r="188" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B188" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C188" s="11" t="s">
+        <v>715</v>
+      </c>
+      <c r="D188" s="11" t="s">
         <v>716</v>
       </c>
-      <c r="D188" s="11" t="s">
+      <c r="E188" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="E188" s="11" t="s">
+      <c r="F188" s="11" t="s">
         <v>718</v>
       </c>
-      <c r="F188" s="11" t="s">
-        <v>719</v>
-      </c>
       <c r="G188" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H188" s="11">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="I188" s="11" t="s">
         <v>1</v>
@@ -9904,28 +9907,28 @@
     </row>
     <row r="189" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B189" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C189" s="13" t="s">
+        <v>720</v>
+      </c>
+      <c r="D189" s="13" t="s">
         <v>721</v>
       </c>
-      <c r="D189" s="13" t="s">
+      <c r="E189" s="13" t="s">
         <v>722</v>
       </c>
-      <c r="E189" s="13" t="s">
+      <c r="F189" s="13" t="s">
         <v>723</v>
       </c>
-      <c r="F189" s="13" t="s">
-        <v>724</v>
-      </c>
       <c r="G189" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H189" s="13">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="I189" s="13" t="s">
         <v>1</v>
@@ -9933,28 +9936,28 @@
     </row>
     <row r="190" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B190" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C190" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="D190" s="11" t="s">
         <v>726</v>
       </c>
-      <c r="D190" s="11" t="s">
+      <c r="E190" s="11" t="s">
         <v>727</v>
       </c>
-      <c r="E190" s="11" t="s">
+      <c r="F190" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F190" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G190" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H190" s="11">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I190" s="11" t="s">
         <v>1</v>
@@ -9962,28 +9965,28 @@
     </row>
     <row r="191" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B191" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C191" s="13" t="s">
+        <v>730</v>
+      </c>
+      <c r="D191" s="13" t="s">
         <v>731</v>
       </c>
-      <c r="D191" s="13" t="s">
-        <v>732</v>
-      </c>
       <c r="E191" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F191" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F191" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G191" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H191" s="13">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="I191" s="13" t="s">
         <v>1</v>
@@ -9991,28 +9994,28 @@
     </row>
     <row r="192" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B192" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C192" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="D192" s="11" t="s">
         <v>734</v>
       </c>
-      <c r="D192" s="11" t="s">
-        <v>735</v>
-      </c>
       <c r="E192" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F192" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F192" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G192" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H192" s="11">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="I192" s="11" t="s">
         <v>1</v>
@@ -10020,28 +10023,28 @@
     </row>
     <row r="193" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B193" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C193" s="13" t="s">
+        <v>736</v>
+      </c>
+      <c r="D193" s="13" t="s">
         <v>737</v>
       </c>
-      <c r="D193" s="13" t="s">
-        <v>738</v>
-      </c>
       <c r="E193" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F193" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F193" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G193" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H193" s="13">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="I193" s="13" t="s">
         <v>1</v>
@@ -10049,28 +10052,28 @@
     </row>
     <row r="194" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B194" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C194" s="11" t="s">
+        <v>739</v>
+      </c>
+      <c r="D194" s="11" t="s">
         <v>740</v>
       </c>
-      <c r="D194" s="11" t="s">
-        <v>741</v>
-      </c>
       <c r="E194" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F194" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F194" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G194" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H194" s="11">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="I194" s="11" t="s">
         <v>1</v>
@@ -10078,28 +10081,28 @@
     </row>
     <row r="195" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B195" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C195" s="13" t="s">
+        <v>742</v>
+      </c>
+      <c r="D195" s="13" t="s">
         <v>743</v>
       </c>
-      <c r="D195" s="13" t="s">
-        <v>744</v>
-      </c>
       <c r="E195" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F195" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F195" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G195" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H195" s="13">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>1</v>
@@ -10107,28 +10110,28 @@
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="11" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B196" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C196" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="D196" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="D196" s="11" t="s">
-        <v>747</v>
-      </c>
       <c r="E196" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F196" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F196" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G196" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H196" s="11">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="I196" s="11" t="s">
         <v>1</v>
@@ -10136,28 +10139,28 @@
     </row>
     <row r="197" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="13" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B197" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C197" s="13" t="s">
+        <v>748</v>
+      </c>
+      <c r="D197" s="13" t="s">
         <v>749</v>
       </c>
-      <c r="D197" s="13" t="s">
-        <v>750</v>
-      </c>
       <c r="E197" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F197" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F197" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G197" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H197" s="13">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>1</v>
@@ -10165,28 +10168,28 @@
     </row>
     <row r="198" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B198" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C198" s="11" t="s">
+        <v>751</v>
+      </c>
+      <c r="D198" s="11" t="s">
         <v>752</v>
       </c>
-      <c r="D198" s="11" t="s">
-        <v>753</v>
-      </c>
       <c r="E198" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F198" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F198" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G198" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H198" s="11">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I198" s="11" t="s">
         <v>1</v>
@@ -10194,28 +10197,28 @@
     </row>
     <row r="199" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="13" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B199" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C199" s="13" t="s">
+        <v>754</v>
+      </c>
+      <c r="D199" s="13" t="s">
         <v>755</v>
       </c>
-      <c r="D199" s="13" t="s">
-        <v>756</v>
-      </c>
       <c r="E199" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F199" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F199" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G199" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H199" s="13">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="I199" s="13" t="s">
         <v>1</v>
@@ -10223,28 +10226,28 @@
     </row>
     <row r="200" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B200" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C200" s="11" t="s">
+        <v>757</v>
+      </c>
+      <c r="D200" s="11" t="s">
         <v>758</v>
       </c>
-      <c r="D200" s="11" t="s">
-        <v>759</v>
-      </c>
       <c r="E200" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F200" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F200" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G200" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H200" s="11">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="I200" s="11" t="s">
         <v>1</v>
@@ -10252,28 +10255,28 @@
     </row>
     <row r="201" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="13" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B201" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C201" s="13" t="s">
+        <v>760</v>
+      </c>
+      <c r="D201" s="13" t="s">
         <v>761</v>
       </c>
-      <c r="D201" s="13" t="s">
-        <v>762</v>
-      </c>
       <c r="E201" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F201" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F201" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G201" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H201" s="13">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="I201" s="13" t="s">
         <v>1</v>
@@ -10281,28 +10284,28 @@
     </row>
     <row r="202" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B202" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C202" s="11" t="s">
+        <v>763</v>
+      </c>
+      <c r="D202" s="11" t="s">
         <v>764</v>
       </c>
-      <c r="D202" s="11" t="s">
-        <v>765</v>
-      </c>
       <c r="E202" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F202" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F202" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G202" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H202" s="11">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="I202" s="11" t="s">
         <v>1</v>
@@ -10310,28 +10313,28 @@
     </row>
     <row r="203" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="13" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B203" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C203" s="13" t="s">
+        <v>766</v>
+      </c>
+      <c r="D203" s="13" t="s">
         <v>767</v>
       </c>
-      <c r="D203" s="13" t="s">
-        <v>768</v>
-      </c>
       <c r="E203" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F203" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F203" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G203" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H203" s="13">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="I203" s="13" t="s">
         <v>1</v>
@@ -10339,28 +10342,28 @@
     </row>
     <row r="204" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="11" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B204" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C204" s="11" t="s">
+        <v>769</v>
+      </c>
+      <c r="D204" s="11" t="s">
         <v>770</v>
       </c>
-      <c r="D204" s="11" t="s">
-        <v>771</v>
-      </c>
       <c r="E204" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F204" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F204" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G204" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H204" s="11">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="I204" s="11" t="s">
         <v>1</v>
@@ -10368,28 +10371,28 @@
     </row>
     <row r="205" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="13" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B205" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C205" s="13" t="s">
+        <v>772</v>
+      </c>
+      <c r="D205" s="13" t="s">
         <v>773</v>
       </c>
-      <c r="D205" s="13" t="s">
-        <v>774</v>
-      </c>
       <c r="E205" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F205" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F205" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G205" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H205" s="13">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I205" s="13" t="s">
         <v>1</v>
@@ -10397,28 +10400,28 @@
     </row>
     <row r="206" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="11" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C206" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="D206" s="11" t="s">
         <v>776</v>
       </c>
-      <c r="D206" s="11" t="s">
-        <v>777</v>
-      </c>
       <c r="E206" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F206" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F206" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G206" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H206" s="11">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="I206" s="11" t="s">
         <v>1</v>
@@ -10426,28 +10429,28 @@
     </row>
     <row r="207" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="13" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B207" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C207" s="13" t="s">
+        <v>778</v>
+      </c>
+      <c r="D207" s="13" t="s">
         <v>779</v>
       </c>
-      <c r="D207" s="13" t="s">
-        <v>780</v>
-      </c>
       <c r="E207" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F207" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F207" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G207" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H207" s="13">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I207" s="13" t="s">
         <v>1</v>
@@ -10455,28 +10458,28 @@
     </row>
     <row r="208" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B208" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C208" s="11" t="s">
+        <v>781</v>
+      </c>
+      <c r="D208" s="11" t="s">
         <v>782</v>
       </c>
-      <c r="D208" s="11" t="s">
-        <v>783</v>
-      </c>
       <c r="E208" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F208" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F208" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G208" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H208" s="11">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="I208" s="11" t="s">
         <v>1</v>
@@ -10484,28 +10487,28 @@
     </row>
     <row r="209" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="13" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B209" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C209" s="13" t="s">
+        <v>784</v>
+      </c>
+      <c r="D209" s="13" t="s">
         <v>785</v>
       </c>
-      <c r="D209" s="13" t="s">
-        <v>786</v>
-      </c>
       <c r="E209" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F209" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F209" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G209" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H209" s="13">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="I209" s="13" t="s">
         <v>1</v>
@@ -10513,28 +10516,28 @@
     </row>
     <row r="210" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B210" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C210" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="D210" s="11" t="s">
         <v>788</v>
       </c>
-      <c r="D210" s="11" t="s">
-        <v>789</v>
-      </c>
       <c r="E210" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F210" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F210" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G210" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H210" s="11">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="I210" s="11" t="s">
         <v>1</v>
@@ -10542,28 +10545,28 @@
     </row>
     <row r="211" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="13" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B211" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C211" s="13" t="s">
+        <v>790</v>
+      </c>
+      <c r="D211" s="13" t="s">
         <v>791</v>
       </c>
-      <c r="D211" s="13" t="s">
-        <v>792</v>
-      </c>
       <c r="E211" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F211" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F211" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G211" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H211" s="13">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I211" s="13" t="s">
         <v>1</v>
@@ -10571,28 +10574,28 @@
     </row>
     <row r="212" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B212" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C212" s="11" t="s">
+        <v>793</v>
+      </c>
+      <c r="D212" s="11" t="s">
         <v>794</v>
       </c>
-      <c r="D212" s="11" t="s">
-        <v>795</v>
-      </c>
       <c r="E212" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F212" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F212" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G212" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H212" s="11">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="I212" s="11" t="s">
         <v>1</v>
@@ -10600,28 +10603,28 @@
     </row>
     <row r="213" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="13" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B213" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C213" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="D213" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="D213" s="13" t="s">
-        <v>798</v>
-      </c>
       <c r="E213" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F213" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F213" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G213" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H213" s="13">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I213" s="13" t="s">
         <v>1</v>
@@ -10629,28 +10632,28 @@
     </row>
     <row r="214" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B214" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C214" s="11" t="s">
+        <v>799</v>
+      </c>
+      <c r="D214" s="11" t="s">
         <v>800</v>
       </c>
-      <c r="D214" s="11" t="s">
-        <v>801</v>
-      </c>
       <c r="E214" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="F214" s="11" t="s">
         <v>728</v>
       </c>
-      <c r="F214" s="11" t="s">
-        <v>729</v>
-      </c>
       <c r="G214" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H214" s="11">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="I214" s="11" t="s">
         <v>1</v>
@@ -10658,28 +10661,28 @@
     </row>
     <row r="215" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="13" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B215" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C215" s="13" t="s">
+        <v>802</v>
+      </c>
+      <c r="D215" s="13" t="s">
         <v>803</v>
       </c>
-      <c r="D215" s="13" t="s">
-        <v>804</v>
-      </c>
       <c r="E215" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="F215" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="F215" s="13" t="s">
-        <v>729</v>
-      </c>
       <c r="G215" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H215" s="13">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I215" s="13" t="s">
         <v>1</v>
@@ -10687,28 +10690,28 @@
     </row>
     <row r="216" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C216" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="D216" s="11" t="s">
         <v>806</v>
       </c>
-      <c r="D216" s="11" t="s">
+      <c r="E216" s="11" t="s">
         <v>807</v>
       </c>
-      <c r="E216" s="11" t="s">
-        <v>808</v>
-      </c>
       <c r="F216" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G216" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H216" s="11">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="I216" s="11" t="s">
         <v>1</v>
@@ -10716,28 +10719,28 @@
     </row>
     <row r="217" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="13" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B217" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C217" s="13" t="s">
+        <v>809</v>
+      </c>
+      <c r="D217" s="13" t="s">
         <v>810</v>
       </c>
-      <c r="D217" s="13" t="s">
+      <c r="E217" s="13" t="s">
         <v>811</v>
       </c>
-      <c r="E217" s="13" t="s">
+      <c r="F217" s="13" t="s">
         <v>812</v>
       </c>
-      <c r="F217" s="13" t="s">
-        <v>813</v>
-      </c>
       <c r="G217" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H217" s="13">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="I217" s="13" t="s">
         <v>1</v>
@@ -10745,28 +10748,28 @@
     </row>
     <row r="218" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="11" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C218" s="11" t="s">
+        <v>814</v>
+      </c>
+      <c r="D218" s="11" t="s">
         <v>815</v>
       </c>
-      <c r="D218" s="11" t="s">
+      <c r="E218" s="11" t="s">
         <v>816</v>
       </c>
-      <c r="E218" s="11" t="s">
+      <c r="F218" s="11" t="s">
         <v>817</v>
       </c>
-      <c r="F218" s="11" t="s">
-        <v>818</v>
-      </c>
       <c r="G218" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H218" s="11">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I218" s="11" t="s">
         <v>1</v>
@@ -10774,28 +10777,28 @@
     </row>
     <row r="219" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="13" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B219" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C219" s="13" t="s">
+        <v>819</v>
+      </c>
+      <c r="D219" s="13" t="s">
         <v>820</v>
       </c>
-      <c r="D219" s="13" t="s">
+      <c r="E219" s="13" t="s">
         <v>821</v>
       </c>
-      <c r="E219" s="13" t="s">
+      <c r="F219" s="13" t="s">
         <v>822</v>
       </c>
-      <c r="F219" s="13" t="s">
-        <v>823</v>
-      </c>
       <c r="G219" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H219" s="13">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="I219" s="13" t="s">
         <v>1</v>
@@ -10803,28 +10806,28 @@
     </row>
     <row r="220" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B220" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C220" s="11" t="s">
+        <v>824</v>
+      </c>
+      <c r="D220" s="11" t="s">
         <v>825</v>
       </c>
-      <c r="D220" s="11" t="s">
+      <c r="E220" s="11" t="s">
         <v>826</v>
       </c>
-      <c r="E220" s="11" t="s">
+      <c r="F220" s="11" t="s">
         <v>827</v>
       </c>
-      <c r="F220" s="11" t="s">
-        <v>828</v>
-      </c>
       <c r="G220" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H220" s="11">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="I220" s="11" t="s">
         <v>1</v>
@@ -10832,28 +10835,28 @@
     </row>
     <row r="221" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="13" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B221" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C221" s="13" t="s">
+        <v>829</v>
+      </c>
+      <c r="D221" s="13" t="s">
         <v>830</v>
       </c>
-      <c r="D221" s="13" t="s">
-        <v>831</v>
-      </c>
       <c r="E221" s="13" t="s">
+        <v>826</v>
+      </c>
+      <c r="F221" s="13" t="s">
         <v>827</v>
       </c>
-      <c r="F221" s="13" t="s">
-        <v>828</v>
-      </c>
       <c r="G221" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H221" s="13">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="I221" s="13" t="s">
         <v>1</v>
@@ -10861,28 +10864,28 @@
     </row>
     <row r="222" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C222" s="11" t="s">
+        <v>832</v>
+      </c>
+      <c r="D222" s="11" t="s">
         <v>833</v>
       </c>
-      <c r="D222" s="11" t="s">
-        <v>834</v>
-      </c>
       <c r="E222" s="11" t="s">
+        <v>826</v>
+      </c>
+      <c r="F222" s="11" t="s">
         <v>827</v>
       </c>
-      <c r="F222" s="11" t="s">
-        <v>828</v>
-      </c>
       <c r="G222" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H222" s="11">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="I222" s="11" t="s">
         <v>1</v>
@@ -10890,28 +10893,28 @@
     </row>
     <row r="223" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="13" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B223" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C223" s="13" t="s">
+        <v>835</v>
+      </c>
+      <c r="D223" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="D223" s="13" t="s">
-        <v>837</v>
-      </c>
       <c r="E223" s="13" t="s">
+        <v>826</v>
+      </c>
+      <c r="F223" s="13" t="s">
         <v>827</v>
       </c>
-      <c r="F223" s="13" t="s">
-        <v>828</v>
-      </c>
       <c r="G223" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H223" s="13">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="I223" s="13" t="s">
         <v>1</v>
@@ -10919,28 +10922,28 @@
     </row>
     <row r="224" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C224" s="11" t="s">
+        <v>838</v>
+      </c>
+      <c r="D224" s="11" t="s">
         <v>839</v>
       </c>
-      <c r="D224" s="11" t="s">
-        <v>840</v>
-      </c>
       <c r="E224" s="11" t="s">
+        <v>826</v>
+      </c>
+      <c r="F224" s="11" t="s">
         <v>827</v>
       </c>
-      <c r="F224" s="11" t="s">
-        <v>828</v>
-      </c>
       <c r="G224" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H224" s="11">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="I224" s="11" t="s">
         <v>1</v>
@@ -10948,28 +10951,28 @@
     </row>
     <row r="225" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="13" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B225" s="13" t="s">
         <v>22</v>
       </c>
       <c r="C225" s="13" t="s">
+        <v>841</v>
+      </c>
+      <c r="D225" s="13" t="s">
         <v>842</v>
       </c>
-      <c r="D225" s="13" t="s">
-        <v>843</v>
-      </c>
       <c r="E225" s="13" t="s">
+        <v>826</v>
+      </c>
+      <c r="F225" s="13" t="s">
         <v>827</v>
       </c>
-      <c r="F225" s="13" t="s">
-        <v>828</v>
-      </c>
       <c r="G225" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H225" s="13">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I225" s="13" t="s">
         <v>1</v>
@@ -10977,28 +10980,28 @@
     </row>
     <row r="226" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B226" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C226" s="11" t="s">
+        <v>844</v>
+      </c>
+      <c r="D226" s="11" t="s">
         <v>845</v>
       </c>
-      <c r="D226" s="11" t="s">
+      <c r="E226" s="11" t="s">
         <v>846</v>
       </c>
-      <c r="E226" s="11" t="s">
+      <c r="F226" s="11" t="s">
         <v>847</v>
       </c>
-      <c r="F226" s="11" t="s">
-        <v>848</v>
-      </c>
       <c r="G226" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H226" s="11">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I226" s="11" t="s">
         <v>1</v>
@@ -11006,28 +11009,28 @@
     </row>
     <row r="227" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B227" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C227" s="13" t="s">
+        <v>849</v>
+      </c>
+      <c r="D227" s="13" t="s">
         <v>850</v>
       </c>
-      <c r="D227" s="13" t="s">
+      <c r="E227" s="13" t="s">
         <v>851</v>
       </c>
-      <c r="E227" s="13" t="s">
+      <c r="F227" s="13" t="s">
         <v>852</v>
       </c>
-      <c r="F227" s="13" t="s">
-        <v>853</v>
-      </c>
       <c r="G227" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H227" s="13">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="I227" s="13" t="s">
         <v>1</v>
@@ -11035,28 +11038,28 @@
     </row>
     <row r="228" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="11" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B228" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C228" s="11" t="s">
+        <v>854</v>
+      </c>
+      <c r="D228" s="11" t="s">
         <v>855</v>
       </c>
-      <c r="D228" s="11" t="s">
+      <c r="E228" s="11" t="s">
         <v>856</v>
       </c>
-      <c r="E228" s="11" t="s">
+      <c r="F228" s="11" t="s">
         <v>857</v>
       </c>
-      <c r="F228" s="11" t="s">
-        <v>858</v>
-      </c>
       <c r="G228" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H228" s="11">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="I228" s="11" t="s">
         <v>1</v>
@@ -11064,28 +11067,28 @@
     </row>
     <row r="229" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="13" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B229" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C229" s="13" t="s">
+        <v>859</v>
+      </c>
+      <c r="D229" s="13" t="s">
         <v>860</v>
       </c>
-      <c r="D229" s="13" t="s">
+      <c r="E229" s="13" t="s">
         <v>861</v>
       </c>
-      <c r="E229" s="13" t="s">
+      <c r="F229" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="F229" s="13" t="s">
-        <v>863</v>
-      </c>
       <c r="G229" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H229" s="13">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="I229" s="13" t="s">
         <v>1</v>
@@ -11093,28 +11096,28 @@
     </row>
     <row r="230" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C230" s="11" t="s">
+        <v>864</v>
+      </c>
+      <c r="D230" s="11" t="s">
         <v>865</v>
       </c>
-      <c r="D230" s="11" t="s">
+      <c r="E230" s="11" t="s">
         <v>866</v>
       </c>
-      <c r="E230" s="11" t="s">
+      <c r="F230" s="11" t="s">
         <v>867</v>
       </c>
-      <c r="F230" s="11" t="s">
-        <v>868</v>
-      </c>
       <c r="G230" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H230" s="11">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="I230" s="11" t="s">
         <v>1</v>
@@ -11122,28 +11125,28 @@
     </row>
     <row r="231" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B231" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C231" s="13" t="s">
+        <v>869</v>
+      </c>
+      <c r="D231" s="13" t="s">
         <v>870</v>
       </c>
-      <c r="D231" s="13" t="s">
+      <c r="E231" s="13" t="s">
         <v>871</v>
       </c>
-      <c r="E231" s="13" t="s">
+      <c r="F231" s="13" t="s">
         <v>872</v>
       </c>
-      <c r="F231" s="13" t="s">
-        <v>873</v>
-      </c>
       <c r="G231" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H231" s="13">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I231" s="13" t="s">
         <v>1</v>
@@ -11151,28 +11154,28 @@
     </row>
     <row r="232" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="11" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C232" s="11" t="s">
+        <v>874</v>
+      </c>
+      <c r="D232" s="11" t="s">
         <v>875</v>
       </c>
-      <c r="D232" s="11" t="s">
+      <c r="E232" s="11" t="s">
         <v>876</v>
       </c>
-      <c r="E232" s="11" t="s">
+      <c r="F232" s="11" t="s">
         <v>877</v>
       </c>
-      <c r="F232" s="11" t="s">
-        <v>878</v>
-      </c>
       <c r="G232" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H232" s="11">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="I232" s="11" t="s">
         <v>1</v>
@@ -11180,28 +11183,28 @@
     </row>
     <row r="233" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="13" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B233" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C233" s="13" t="s">
+        <v>879</v>
+      </c>
+      <c r="D233" s="13" t="s">
         <v>880</v>
       </c>
-      <c r="D233" s="13" t="s">
-        <v>881</v>
-      </c>
       <c r="E233" s="13" t="s">
+        <v>876</v>
+      </c>
+      <c r="F233" s="13" t="s">
         <v>877</v>
       </c>
-      <c r="F233" s="13" t="s">
-        <v>878</v>
-      </c>
       <c r="G233" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H233" s="13">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="I233" s="13" t="s">
         <v>1</v>
@@ -11209,28 +11212,28 @@
     </row>
     <row r="234" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B234" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C234" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="D234" s="11" t="s">
         <v>883</v>
       </c>
-      <c r="D234" s="11" t="s">
-        <v>884</v>
-      </c>
       <c r="E234" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="F234" s="11" t="s">
         <v>877</v>
       </c>
-      <c r="F234" s="11" t="s">
-        <v>878</v>
-      </c>
       <c r="G234" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H234" s="11">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="I234" s="11" t="s">
         <v>1</v>
@@ -11238,28 +11241,28 @@
     </row>
     <row r="235" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="13" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B235" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C235" s="13" t="s">
+        <v>885</v>
+      </c>
+      <c r="D235" s="13" t="s">
         <v>886</v>
       </c>
-      <c r="D235" s="13" t="s">
-        <v>887</v>
-      </c>
       <c r="E235" s="13" t="s">
+        <v>876</v>
+      </c>
+      <c r="F235" s="13" t="s">
         <v>877</v>
       </c>
-      <c r="F235" s="13" t="s">
-        <v>878</v>
-      </c>
       <c r="G235" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H235" s="13">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="I235" s="13" t="s">
         <v>1</v>
@@ -11267,28 +11270,28 @@
     </row>
     <row r="236" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B236" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C236" s="11" t="s">
+        <v>888</v>
+      </c>
+      <c r="D236" s="11" t="s">
         <v>889</v>
       </c>
-      <c r="D236" s="11" t="s">
+      <c r="E236" s="11" t="s">
         <v>890</v>
       </c>
-      <c r="E236" s="11" t="s">
-        <v>891</v>
-      </c>
       <c r="F236" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G236" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H236" s="11">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="I236" s="11" t="s">
         <v>1</v>
@@ -11296,28 +11299,28 @@
     </row>
     <row r="237" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B237" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C237" s="13" t="s">
+        <v>892</v>
+      </c>
+      <c r="D237" s="13" t="s">
         <v>893</v>
       </c>
-      <c r="D237" s="13" t="s">
-        <v>894</v>
-      </c>
       <c r="E237" s="13" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F237" s="13" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G237" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H237" s="13">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I237" s="13" t="s">
         <v>1</v>
@@ -11325,28 +11328,28 @@
     </row>
     <row r="238" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B238" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C238" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="D238" s="11" t="s">
         <v>896</v>
       </c>
-      <c r="D238" s="11" t="s">
-        <v>897</v>
-      </c>
       <c r="E238" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G238" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H238" s="11">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="I238" s="11" t="s">
         <v>1</v>
@@ -11354,28 +11357,28 @@
     </row>
     <row r="239" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="13" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B239" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C239" s="13" t="s">
+        <v>898</v>
+      </c>
+      <c r="D239" s="13" t="s">
         <v>899</v>
       </c>
-      <c r="D239" s="13" t="s">
-        <v>900</v>
-      </c>
       <c r="E239" s="13" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F239" s="13" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G239" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H239" s="13">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I239" s="13" t="s">
         <v>1</v>
@@ -11383,28 +11386,28 @@
     </row>
     <row r="240" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B240" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C240" s="11" t="s">
+        <v>901</v>
+      </c>
+      <c r="D240" s="11" t="s">
         <v>902</v>
       </c>
-      <c r="D240" s="11" t="s">
-        <v>903</v>
-      </c>
       <c r="E240" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G240" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H240" s="11">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="I240" s="11" t="s">
         <v>1</v>
@@ -11412,28 +11415,28 @@
     </row>
     <row r="241" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="13" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B241" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C241" s="13" t="s">
+        <v>904</v>
+      </c>
+      <c r="D241" s="13" t="s">
         <v>905</v>
       </c>
-      <c r="D241" s="13" t="s">
-        <v>906</v>
-      </c>
       <c r="E241" s="13" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F241" s="13" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G241" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H241" s="13">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="I241" s="13" t="s">
         <v>1</v>
@@ -11441,28 +11444,28 @@
     </row>
     <row r="242" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="11" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B242" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C242" s="11" t="s">
+        <v>907</v>
+      </c>
+      <c r="D242" s="11" t="s">
         <v>908</v>
       </c>
-      <c r="D242" s="11" t="s">
-        <v>909</v>
-      </c>
       <c r="E242" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G242" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H242" s="11">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I242" s="11" t="s">
         <v>1</v>
@@ -11470,28 +11473,28 @@
     </row>
     <row r="243" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="13" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B243" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C243" s="13" t="s">
+        <v>910</v>
+      </c>
+      <c r="D243" s="13" t="s">
         <v>911</v>
       </c>
-      <c r="D243" s="13" t="s">
-        <v>912</v>
-      </c>
       <c r="E243" s="13" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F243" s="13" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G243" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H243" s="13">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="I243" s="13" t="s">
         <v>1</v>
@@ -11499,28 +11502,28 @@
     </row>
     <row r="244" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B244" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C244" s="11" t="s">
+        <v>913</v>
+      </c>
+      <c r="D244" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="D244" s="11" t="s">
+      <c r="E244" s="11" t="s">
         <v>915</v>
       </c>
-      <c r="E244" s="11" t="s">
+      <c r="F244" s="11" t="s">
         <v>916</v>
       </c>
-      <c r="F244" s="11" t="s">
-        <v>917</v>
-      </c>
       <c r="G244" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H244" s="11">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="I244" s="11" t="s">
         <v>1</v>
@@ -11528,28 +11531,28 @@
     </row>
     <row r="245" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="13" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B245" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C245" s="13" t="s">
+        <v>918</v>
+      </c>
+      <c r="D245" s="13" t="s">
         <v>919</v>
       </c>
-      <c r="D245" s="13" t="s">
+      <c r="E245" s="13" t="s">
         <v>920</v>
       </c>
-      <c r="E245" s="13" t="s">
+      <c r="F245" s="13" t="s">
         <v>921</v>
       </c>
-      <c r="F245" s="13" t="s">
-        <v>922</v>
-      </c>
       <c r="G245" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H245" s="13">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="I245" s="13" t="s">
         <v>1</v>
@@ -11557,28 +11560,28 @@
     </row>
     <row r="246" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="11" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B246" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C246" s="11" t="s">
+        <v>923</v>
+      </c>
+      <c r="D246" s="11" t="s">
         <v>924</v>
       </c>
-      <c r="D246" s="11" t="s">
+      <c r="E246" s="11" t="s">
         <v>925</v>
       </c>
-      <c r="E246" s="11" t="s">
+      <c r="F246" s="11" t="s">
         <v>926</v>
       </c>
-      <c r="F246" s="11" t="s">
-        <v>927</v>
-      </c>
       <c r="G246" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H246" s="11">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="I246" s="11" t="s">
         <v>1</v>
@@ -11586,28 +11589,28 @@
     </row>
     <row r="247" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="13" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B247" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C247" s="13" t="s">
+        <v>928</v>
+      </c>
+      <c r="D247" s="13" t="s">
         <v>929</v>
       </c>
-      <c r="D247" s="13" t="s">
+      <c r="E247" s="13" t="s">
         <v>930</v>
       </c>
-      <c r="E247" s="13" t="s">
+      <c r="F247" s="13" t="s">
         <v>931</v>
       </c>
-      <c r="F247" s="13" t="s">
-        <v>932</v>
-      </c>
       <c r="G247" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H247" s="13">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="I247" s="13" t="s">
         <v>1</v>
@@ -11615,28 +11618,28 @@
     </row>
     <row r="248" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B248" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C248" s="11" t="s">
+        <v>933</v>
+      </c>
+      <c r="D248" s="11" t="s">
         <v>934</v>
       </c>
-      <c r="D248" s="11" t="s">
+      <c r="E248" s="11" t="s">
         <v>935</v>
       </c>
-      <c r="E248" s="11" t="s">
+      <c r="F248" s="11" t="s">
         <v>936</v>
       </c>
-      <c r="F248" s="11" t="s">
-        <v>937</v>
-      </c>
       <c r="G248" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H248" s="11">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="I248" s="11" t="s">
         <v>1</v>
@@ -11644,28 +11647,28 @@
     </row>
     <row r="249" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B249" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C249" s="13" t="s">
+        <v>938</v>
+      </c>
+      <c r="D249" s="13" t="s">
         <v>939</v>
       </c>
-      <c r="D249" s="13" t="s">
+      <c r="E249" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="E249" s="13" t="s">
+      <c r="F249" s="13" t="s">
         <v>941</v>
       </c>
-      <c r="F249" s="13" t="s">
-        <v>942</v>
-      </c>
       <c r="G249" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H249" s="13">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="I249" s="13" t="s">
         <v>1</v>
@@ -11673,22 +11676,22 @@
     </row>
     <row r="250" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B250" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C250" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="D250" s="11" t="s">
         <v>944</v>
       </c>
-      <c r="D250" s="11" t="s">
+      <c r="E250" s="11" t="s">
         <v>945</v>
       </c>
-      <c r="E250" s="11" t="s">
+      <c r="F250" s="11" t="s">
         <v>946</v>
-      </c>
-      <c r="F250" s="11" t="s">
-        <v>947</v>
       </c>
       <c r="G250" s="12" t="s">
         <v>9</v>
@@ -11702,28 +11705,28 @@
     </row>
     <row r="251" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="13" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B251" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C251" s="13" t="s">
+        <v>948</v>
+      </c>
+      <c r="D251" s="13" t="s">
         <v>949</v>
       </c>
-      <c r="D251" s="13" t="s">
+      <c r="E251" s="13" t="s">
         <v>950</v>
       </c>
-      <c r="E251" s="13" t="s">
+      <c r="F251" s="13" t="s">
         <v>951</v>
       </c>
-      <c r="F251" s="13" t="s">
-        <v>952</v>
-      </c>
       <c r="G251" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H251" s="13">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="I251" s="13" t="s">
         <v>1</v>
@@ -11731,28 +11734,28 @@
     </row>
     <row r="252" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B252" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C252" s="11" t="s">
+        <v>953</v>
+      </c>
+      <c r="D252" s="11" t="s">
         <v>954</v>
       </c>
-      <c r="D252" s="11" t="s">
+      <c r="E252" s="11" t="s">
         <v>955</v>
       </c>
-      <c r="E252" s="11" t="s">
+      <c r="F252" s="11" t="s">
         <v>956</v>
       </c>
-      <c r="F252" s="11" t="s">
-        <v>957</v>
-      </c>
       <c r="G252" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H252" s="11">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="I252" s="11" t="s">
         <v>1</v>
@@ -11760,28 +11763,28 @@
     </row>
     <row r="253" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="13" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B253" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C253" s="13" t="s">
+        <v>958</v>
+      </c>
+      <c r="D253" s="13" t="s">
         <v>959</v>
       </c>
-      <c r="D253" s="13" t="s">
+      <c r="E253" s="13" t="s">
         <v>960</v>
       </c>
-      <c r="E253" s="13" t="s">
-        <v>961</v>
-      </c>
       <c r="F253" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G253" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H253" s="13">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="I253" s="13" t="s">
         <v>1</v>
@@ -11789,28 +11792,28 @@
     </row>
     <row r="254" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="11" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B254" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C254" s="11" t="s">
+        <v>962</v>
+      </c>
+      <c r="D254" s="11" t="s">
         <v>963</v>
       </c>
-      <c r="D254" s="11" t="s">
-        <v>964</v>
-      </c>
       <c r="E254" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="F254" s="11" t="s">
         <v>956</v>
       </c>
-      <c r="F254" s="11" t="s">
-        <v>957</v>
-      </c>
       <c r="G254" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H254" s="11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I254" s="11" t="s">
         <v>1</v>
@@ -11818,28 +11821,28 @@
     </row>
     <row r="255" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="13" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B255" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C255" s="13" t="s">
+        <v>965</v>
+      </c>
+      <c r="D255" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="D255" s="13" t="s">
+      <c r="E255" s="13" t="s">
         <v>967</v>
       </c>
-      <c r="E255" s="13" t="s">
-        <v>968</v>
-      </c>
       <c r="F255" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G255" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H255" s="13">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I255" s="13" t="s">
         <v>1</v>
@@ -11847,28 +11850,28 @@
     </row>
     <row r="256" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B256" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C256" s="11" t="s">
+        <v>969</v>
+      </c>
+      <c r="D256" s="11" t="s">
         <v>970</v>
       </c>
-      <c r="D256" s="11" t="s">
-        <v>971</v>
-      </c>
       <c r="E256" s="11" t="s">
+        <v>960</v>
+      </c>
+      <c r="F256" s="11" t="s">
         <v>956</v>
       </c>
-      <c r="F256" s="11" t="s">
-        <v>957</v>
-      </c>
       <c r="G256" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H256" s="11">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I256" s="11" t="s">
         <v>1</v>
@@ -11876,28 +11879,28 @@
     </row>
     <row r="257" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="13" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B257" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C257" s="13" t="s">
+        <v>972</v>
+      </c>
+      <c r="D257" s="13" t="s">
         <v>973</v>
       </c>
-      <c r="D257" s="13" t="s">
-        <v>974</v>
-      </c>
       <c r="E257" s="13" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="F257" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G257" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H257" s="13">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I257" s="13" t="s">
         <v>1</v>
@@ -11905,28 +11908,28 @@
     </row>
     <row r="258" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="11" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B258" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C258" s="11" t="s">
+        <v>975</v>
+      </c>
+      <c r="D258" s="11" t="s">
         <v>976</v>
       </c>
-      <c r="D258" s="11" t="s">
-        <v>977</v>
-      </c>
       <c r="E258" s="11" t="s">
-        <v>968</v>
+        <v>955</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G258" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H258" s="11">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="I258" s="11" t="s">
         <v>1</v>
@@ -11934,28 +11937,28 @@
     </row>
     <row r="259" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="13" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B259" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C259" s="13" t="s">
+        <v>978</v>
+      </c>
+      <c r="D259" s="13" t="s">
         <v>979</v>
       </c>
-      <c r="D259" s="13" t="s">
+      <c r="E259" s="13" t="s">
         <v>967</v>
       </c>
-      <c r="E259" s="13" t="s">
-        <v>968</v>
-      </c>
       <c r="F259" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G259" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H259" s="13">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="I259" s="13" t="s">
         <v>1</v>
@@ -11975,16 +11978,16 @@
         <v>982</v>
       </c>
       <c r="E260" s="11" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G260" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H260" s="11">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="I260" s="11" t="s">
         <v>1</v>
@@ -12004,16 +12007,16 @@
         <v>985</v>
       </c>
       <c r="E261" s="13" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F261" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G261" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H261" s="13">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="I261" s="13" t="s">
         <v>1</v>
@@ -12033,16 +12036,16 @@
         <v>988</v>
       </c>
       <c r="E262" s="11" t="s">
-        <v>968</v>
+        <v>955</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G262" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H262" s="11">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="I262" s="11" t="s">
         <v>1</v>
@@ -12059,19 +12062,19 @@
         <v>990</v>
       </c>
       <c r="D263" s="13" t="s">
-        <v>971</v>
+        <v>991</v>
       </c>
       <c r="E263" s="13" t="s">
+        <v>967</v>
+      </c>
+      <c r="F263" s="13" t="s">
         <v>956</v>
       </c>
-      <c r="F263" s="13" t="s">
-        <v>957</v>
-      </c>
       <c r="G263" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H263" s="13">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="I263" s="13" t="s">
         <v>1</v>
@@ -12079,28 +12082,28 @@
     </row>
     <row r="264" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B264" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C264" s="11" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D264" s="11" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="E264" s="11" t="s">
+        <v>967</v>
+      </c>
+      <c r="F264" s="11" t="s">
         <v>956</v>
       </c>
-      <c r="F264" s="11" t="s">
-        <v>957</v>
-      </c>
       <c r="G264" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H264" s="11">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="I264" s="11" t="s">
         <v>1</v>
@@ -12108,28 +12111,28 @@
     </row>
     <row r="265" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="13" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B265" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C265" s="13" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D265" s="13" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E265" s="13" t="s">
+        <v>960</v>
+      </c>
+      <c r="F265" s="13" t="s">
         <v>956</v>
       </c>
-      <c r="F265" s="13" t="s">
-        <v>957</v>
-      </c>
       <c r="G265" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H265" s="13">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="I265" s="13" t="s">
         <v>1</v>
@@ -12137,28 +12140,28 @@
     </row>
     <row r="266" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C266" s="11" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D266" s="11" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E266" s="11" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G266" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H266" s="11">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="I266" s="11" t="s">
         <v>1</v>
@@ -12166,28 +12169,28 @@
     </row>
     <row r="267" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="13" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B267" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C267" s="13" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D267" s="13" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E267" s="13" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="F267" s="13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G267" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H267" s="13">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I267" s="13" t="s">
         <v>1</v>
@@ -12195,28 +12198,28 @@
     </row>
     <row r="268" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="11" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C268" s="11" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E268" s="11" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="G268" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H268" s="11">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="I268" s="11" t="s">
         <v>1</v>
@@ -12224,28 +12227,28 @@
     </row>
     <row r="269" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="13" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B269" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C269" s="13" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D269" s="13" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E269" s="13" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F269" s="13" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G269" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H269" s="13">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I269" s="13" t="s">
         <v>1</v>
@@ -12253,28 +12256,28 @@
     </row>
     <row r="270" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="11" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B270" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C270" s="11" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D270" s="11" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E270" s="11" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G270" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H270" s="11">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="I270" s="11" t="s">
         <v>1</v>
@@ -12282,28 +12285,28 @@
     </row>
     <row r="271" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="13" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B271" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C271" s="13" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D271" s="13" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E271" s="13" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F271" s="13" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="G271" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H271" s="13">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="I271" s="13" t="s">
         <v>1</v>
@@ -12311,28 +12314,28 @@
     </row>
     <row r="272" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C272" s="11" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E272" s="11" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G272" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H272" s="11">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I272" s="11" t="s">
         <v>1</v>
@@ -12340,28 +12343,28 @@
     </row>
     <row r="273" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="13" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B273" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C273" s="13" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D273" s="13" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E273" s="13" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F273" s="13" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="G273" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H273" s="13">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="I273" s="13" t="s">
         <v>1</v>
@@ -12369,28 +12372,28 @@
     </row>
     <row r="274" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="11" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C274" s="11" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E274" s="11" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G274" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H274" s="11">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I274" s="11" t="s">
         <v>1</v>
@@ -12398,28 +12401,28 @@
     </row>
     <row r="275" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="13" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B275" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C275" s="13" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D275" s="13" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E275" s="13" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F275" s="13" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="G275" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H275" s="13">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I275" s="13" t="s">
         <v>1</v>
@@ -12427,19 +12430,19 @@
     </row>
     <row r="276" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="11" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C276" s="11" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D276" s="11" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="E276" s="11" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F276" s="11" t="s">
         <v>48</v>
@@ -12448,7 +12451,7 @@
         <v>9</v>
       </c>
       <c r="H276" s="11">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="I276" s="11" t="s">
         <v>1</v>
@@ -12456,28 +12459,28 @@
     </row>
     <row r="277" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="13" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B277" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C277" s="13" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D277" s="13" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E277" s="13" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F277" s="13" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G277" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H277" s="13">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I277" s="13" t="s">
         <v>1</v>
@@ -12485,28 +12488,28 @@
     </row>
     <row r="278" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D278" s="11" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E278" s="11" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G278" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H278" s="11">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="I278" s="11" t="s">
         <v>1</v>
@@ -12514,28 +12517,28 @@
     </row>
     <row r="279" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="13" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B279" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C279" s="13" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D279" s="13" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E279" s="13" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F279" s="13" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G279" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H279" s="13">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="I279" s="13" t="s">
         <v>1</v>
@@ -12543,28 +12546,28 @@
     </row>
     <row r="280" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C280" s="11" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D280" s="11" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E280" s="11" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G280" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H280" s="11">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="I280" s="11" t="s">
         <v>1</v>
@@ -12572,28 +12575,28 @@
     </row>
     <row r="281" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="13" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B281" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C281" s="13" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D281" s="13" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E281" s="13" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F281" s="13" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G281" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H281" s="13">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="I281" s="13" t="s">
         <v>1</v>
@@ -12601,28 +12604,28 @@
     </row>
     <row r="282" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="11" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B282" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C282" s="11" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D282" s="11" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E282" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G282" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H282" s="11">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I282" s="11" t="s">
         <v>1</v>
@@ -12630,28 +12633,28 @@
     </row>
     <row r="283" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="13" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B283" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C283" s="13" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D283" s="13" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E283" s="13" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F283" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G283" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H283" s="13">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="I283" s="13" t="s">
         <v>1</v>
@@ -12659,28 +12662,28 @@
     </row>
     <row r="284" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B284" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C284" s="11" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E284" s="11" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G284" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H284" s="11">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="I284" s="11" t="s">
         <v>1</v>
@@ -12688,28 +12691,28 @@
     </row>
     <row r="285" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="13" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B285" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C285" s="13" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D285" s="13" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E285" s="13" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F285" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G285" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H285" s="13">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="I285" s="13" t="s">
         <v>1</v>
@@ -12717,28 +12720,28 @@
     </row>
     <row r="286" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="11" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C286" s="11" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D286" s="11" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="E286" s="11" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G286" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H286" s="11">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="I286" s="11" t="s">
         <v>1</v>
@@ -12746,28 +12749,28 @@
     </row>
     <row r="287" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="13" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B287" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C287" s="13" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D287" s="13" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="E287" s="13" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F287" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G287" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H287" s="13">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="I287" s="13" t="s">
         <v>1</v>
@@ -12775,28 +12778,28 @@
     </row>
     <row r="288" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" s="11" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B288" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C288" s="11" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D288" s="11" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E288" s="11" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G288" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H288" s="11">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="I288" s="11" t="s">
         <v>1</v>
@@ -12804,28 +12807,28 @@
     </row>
     <row r="289" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" s="13" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B289" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C289" s="13" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D289" s="13" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="E289" s="13" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F289" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G289" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H289" s="13">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I289" s="13" t="s">
         <v>1</v>
@@ -12833,28 +12836,28 @@
     </row>
     <row r="290" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C290" s="11" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D290" s="11" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="E290" s="11" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G290" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H290" s="11">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="I290" s="11" t="s">
         <v>1</v>
@@ -12862,28 +12865,28 @@
     </row>
     <row r="291" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="13" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B291" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C291" s="13" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D291" s="13" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E291" s="13" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F291" s="13" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G291" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H291" s="13">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I291" s="13" t="s">
         <v>1</v>
@@ -12891,28 +12894,28 @@
     </row>
     <row r="292" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" s="11" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B292" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C292" s="11" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D292" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E292" s="11" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="G292" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H292" s="11">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I292" s="11" t="s">
         <v>1</v>
@@ -12920,28 +12923,28 @@
     </row>
     <row r="293" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" s="13" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B293" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C293" s="13" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D293" s="13" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E293" s="13" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F293" s="13" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="G293" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H293" s="13">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I293" s="13" t="s">
         <v>1</v>
@@ -12949,28 +12952,28 @@
     </row>
     <row r="294" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" s="11" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B294" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C294" s="11" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D294" s="11" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="E294" s="11" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="G294" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H294" s="11">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="I294" s="11" t="s">
         <v>1</v>
@@ -12978,28 +12981,28 @@
     </row>
     <row r="295" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" s="13" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B295" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C295" s="13" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D295" s="13" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E295" s="13" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F295" s="13" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G295" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H295" s="13">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="I295" s="13" t="s">
         <v>1</v>
@@ -13007,28 +13010,28 @@
     </row>
     <row r="296" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" s="11" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D296" s="11" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E296" s="11" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G296" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H296" s="11">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I296" s="11" t="s">
         <v>1</v>
@@ -13036,28 +13039,28 @@
     </row>
     <row r="297" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" s="13" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B297" s="13" t="s">
         <v>28</v>
       </c>
       <c r="C297" s="13" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D297" s="13" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="E297" s="13" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="F297" s="13" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="G297" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H297" s="13">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="I297" s="13" t="s">
         <v>1</v>
@@ -13065,28 +13068,28 @@
     </row>
     <row r="298" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" s="11" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D298" s="11" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="E298" s="11" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="G298" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H298" s="11">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I298" s="11" t="s">
         <v>1</v>
@@ -13094,28 +13097,28 @@
     </row>
     <row r="299" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="13" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B299" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C299" s="13" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D299" s="13" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E299" s="13" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F299" s="13" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G299" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H299" s="13">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="I299" s="13" t="s">
         <v>1</v>
@@ -13123,28 +13126,28 @@
     </row>
     <row r="300" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>29</v>
       </c>
       <c r="C300" s="11" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D300" s="11" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="E300" s="11" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="G300" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H300" s="11">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="I300" s="11" t="s">
         <v>1</v>
@@ -13152,28 +13155,28 @@
     </row>
     <row r="301" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" s="13" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B301" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C301" s="13" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D301" s="13" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="E301" s="13" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="F301" s="13" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="G301" s="12" t="s">
         <v>9</v>
       </c>
       <c r="H301" s="13">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I301" s="13" t="s">
         <v>1</v>
